--- a/research/traditional_assets/database/data/vietnam/vietnam_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_telecom_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hnx_pot" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,91 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.5600000000000001</v>
+        <v>-0.1673</v>
+      </c>
+      <c r="E2">
+        <v>-0.186</v>
       </c>
       <c r="G2">
-        <v>85.75000000000001</v>
+        <v>0.102696087953071</v>
       </c>
       <c r="H2">
-        <v>85.75000000000001</v>
+        <v>0.102696087953071</v>
       </c>
       <c r="I2">
-        <v>-3.166666666666667</v>
+        <v>0.04836641933102832</v>
       </c>
       <c r="J2">
-        <v>-3.166666666666667</v>
+        <v>0.03996367144097003</v>
       </c>
       <c r="K2">
-        <v>-0.044</v>
+        <v>0.467</v>
       </c>
       <c r="L2">
-        <v>-3.666666666666667</v>
+        <v>0.009071131657666757</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02405867970660147</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>1.053533190578158</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02405867970660147</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>1.053533190578158</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.132</v>
+        <v>2.93</v>
       </c>
       <c r="V2">
-        <v>0.01471571906354515</v>
+        <v>0.1432762836185819</v>
+      </c>
+      <c r="W2">
+        <v>0.004860088365243004</v>
       </c>
       <c r="X2">
-        <v>0.3513850145564999</v>
+        <v>0.3248961436045109</v>
+      </c>
+      <c r="Y2">
+        <v>-0.3200360552392679</v>
       </c>
       <c r="Z2">
-        <v>0.00208659363588941</v>
+        <v>0.7864530025511374</v>
+      </c>
+      <c r="AA2">
+        <v>0.001685145822561805</v>
       </c>
       <c r="AB2">
-        <v>0.1768758972880066</v>
+        <v>0.1505577347945257</v>
+      </c>
+      <c r="AC2">
+        <v>-0.148872588971964</v>
       </c>
       <c r="AD2">
-        <v>16.69</v>
+        <v>43.17</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.69</v>
+        <v>43.17</v>
       </c>
       <c r="AG2">
-        <v>16.558</v>
+        <v>40.24</v>
       </c>
       <c r="AH2">
-        <v>0.6504286827747466</v>
+        <v>0.6785602011945929</v>
       </c>
       <c r="AI2">
-        <v>0.6154129793510325</v>
+        <v>0.6602936677883146</v>
       </c>
       <c r="AJ2">
-        <v>0.6486211219053588</v>
+        <v>0.6630416872631406</v>
       </c>
       <c r="AK2">
-        <v>0.6135319401215354</v>
+        <v>0.64435548438751</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>2.196</v>
+      </c>
+      <c r="AN2">
+        <v>10.71747765640517</v>
+      </c>
+      <c r="AO2">
+        <v>1.106666666666667</v>
+      </c>
+      <c r="AP2">
+        <v>9.990069513406159</v>
+      </c>
+      <c r="AQ2">
+        <v>1.133879781420765</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VTC Telecommunications Joint Stock Company (HNX:VTC)</t>
+          <t>Post and Telecommunication Equipment JSC (HNX:POT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -691,80 +723,122 @@
           <t>Telecom. Equipment</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0526</v>
+      </c>
+      <c r="E3">
+        <v>-0.186</v>
+      </c>
+      <c r="G3">
+        <v>0.08326848249027238</v>
+      </c>
+      <c r="H3">
+        <v>0.08326848249027238</v>
+      </c>
+      <c r="I3">
+        <v>0.04766536964980545</v>
+      </c>
+      <c r="J3">
+        <v>0.03015564202334631</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.434</v>
+      </c>
+      <c r="L3">
+        <v>0.008443579766536966</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.492</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03644444444444445</v>
+      </c>
+      <c r="O3">
+        <v>1.133640552995392</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.492</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03644444444444445</v>
+      </c>
+      <c r="R3">
+        <v>1.133640552995392</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.127</v>
+        <v>2.77</v>
       </c>
       <c r="V3">
-        <v>0.05570175438596492</v>
+        <v>0.2051851851851852</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>0.03238805970149253</v>
       </c>
       <c r="X3">
-        <v>0.3251639981010779</v>
+        <v>0.3194376560190375</v>
       </c>
       <c r="Y3">
-        <v>-0.3251639981010779</v>
+        <v>-0.287049596317545</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.392953929539295</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.04200542005420055</v>
       </c>
       <c r="AB3">
-        <v>0.1764869355987248</v>
+        <v>0.1490558971026253</v>
       </c>
       <c r="AC3">
-        <v>-0.1764869355987248</v>
+        <v>-0.1070504770484247</v>
       </c>
       <c r="AD3">
-        <v>3.39</v>
+        <v>28</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.39</v>
+        <v>28</v>
       </c>
       <c r="AG3">
-        <v>3.263</v>
+        <v>25.23</v>
       </c>
       <c r="AH3">
-        <v>0.5978835978835979</v>
+        <v>0.6746987951807228</v>
       </c>
       <c r="AI3">
-        <v>0.4822190611664296</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="AJ3">
-        <v>0.5886703950929101</v>
+        <v>0.65143299767622</v>
       </c>
       <c r="AK3">
-        <v>0.4726930320150659</v>
+        <v>0.6634236129371549</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2.196</v>
+      </c>
+      <c r="AN3">
+        <v>7.035175879396985</v>
+      </c>
+      <c r="AO3">
+        <v>1.088888888888889</v>
+      </c>
+      <c r="AP3">
+        <v>6.339195979899498</v>
+      </c>
+      <c r="AQ3">
+        <v>1.115664845173042</v>
       </c>
     </row>
     <row r="4">
@@ -784,25 +858,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.5600000000000001</v>
+        <v>-0.282</v>
       </c>
       <c r="G4">
-        <v>-0.08333333333333333</v>
+        <v>-0.2804878048780488</v>
       </c>
       <c r="H4">
-        <v>-0.08333333333333333</v>
+        <v>-0.2804878048780488</v>
       </c>
       <c r="I4">
-        <v>-3.166666666666667</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="J4">
-        <v>-3.166666666666667</v>
+        <v>0.4127579737335835</v>
       </c>
       <c r="K4">
-        <v>-0.044</v>
+        <v>0.033</v>
       </c>
       <c r="L4">
-        <v>-3.666666666666667</v>
+        <v>0.4024390243902439</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -811,7 +885,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -820,51 +894,8936 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.005</v>
+        <v>0.039</v>
       </c>
       <c r="V4">
-        <v>0.0007473841554559044</v>
+        <v>0.007514450867052023</v>
+      </c>
+      <c r="W4">
+        <v>0.004860088365243004</v>
       </c>
       <c r="X4">
-        <v>0.3776060310119219</v>
+        <v>0.3248961436045109</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3200360552392679</v>
+      </c>
+      <c r="Z4">
+        <v>0.004082648742842918</v>
+      </c>
+      <c r="AA4">
+        <v>0.001685145822561805</v>
       </c>
       <c r="AB4">
-        <v>0.1772648589772884</v>
+        <v>0.1505577347945257</v>
+      </c>
+      <c r="AC4">
+        <v>-0.148872588971964</v>
       </c>
       <c r="AD4">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="AG4">
-        <v>13.295</v>
+        <v>11.061</v>
       </c>
       <c r="AH4">
-        <v>0.6653326663331666</v>
+        <v>0.6813996316758748</v>
       </c>
       <c r="AI4">
-        <v>0.6620209059233449</v>
+        <v>0.6218487394957982</v>
       </c>
       <c r="AJ4">
-        <v>0.6652489367025269</v>
+        <v>0.680635037843825</v>
       </c>
       <c r="AK4">
-        <v>0.6619367687328852</v>
+        <v>0.6210207175341081</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>231.25</v>
+      </c>
+      <c r="AP4">
+        <v>230.4375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VTC Telecommunications Joint Stock Company (HNX:VTC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.121</v>
+      </c>
+      <c r="V5">
+        <v>0.06874999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0.3395669586443585</v>
+      </c>
+      <c r="Y5">
+        <v>-0.3395669586443585</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.1507104349678197</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1507104349678197</v>
+      </c>
+      <c r="AD5">
+        <v>4.07</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>4.07</v>
+      </c>
+      <c r="AG5">
+        <v>3.949</v>
+      </c>
+      <c r="AH5">
+        <v>0.6981132075471699</v>
+      </c>
+      <c r="AI5">
+        <v>0.6047548291233283</v>
+      </c>
+      <c r="AJ5">
+        <v>0.6917148362235067</v>
+      </c>
+      <c r="AK5">
+        <v>0.5975185353306098</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Post and Telecommunication Equipment JSC (HNX:POT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HNX:POT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.08888888888889</v>
+      </c>
+      <c r="F2">
+        <v>4.55839743300592</v>
+      </c>
+      <c r="G2">
+        <v>7.03517587939698</v>
+      </c>
+      <c r="H2">
+        <v>5.52638190954774</v>
+      </c>
+      <c r="I2">
+        <v>0.674698795180723</v>
+      </c>
+      <c r="J2">
+        <v>0.53</v>
+      </c>
+      <c r="K2">
+        <v>13.5</v>
+      </c>
+      <c r="L2">
+        <v>25.5532779988365</v>
+      </c>
+      <c r="M2">
+        <v>38.73</v>
+      </c>
+      <c r="N2">
+        <v>44.7782779988365</v>
+      </c>
+      <c r="O2">
+        <v>28</v>
+      </c>
+      <c r="P2">
+        <v>21.995</v>
+      </c>
+      <c r="Q2">
+        <v>0.149055897102625</v>
+      </c>
+      <c r="R2">
+        <v>0.134163445974757</v>
+      </c>
+      <c r="S2">
+        <v>0.0669075490536408</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.319437656019038</v>
+      </c>
+      <c r="X2">
+        <v>0.239535842499482</v>
+      </c>
+      <c r="Y2">
+        <v>3.11804329172304</v>
+      </c>
+      <c r="Z2">
+        <v>2.23028889277576</v>
+      </c>
+      <c r="AA2">
+        <v>28</v>
+      </c>
+      <c r="AB2">
+        <v>0.083634436317051</v>
+      </c>
+      <c r="AC2">
+        <v>1.088888888888889</v>
+      </c>
+      <c r="AD2">
+        <v>28</v>
+      </c>
+      <c r="AE2">
+        <v>2.25</v>
+      </c>
+      <c r="AF2">
+        <v>1.53</v>
+      </c>
+      <c r="AG2">
+        <v>3.98</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>13.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.0900044129483385</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.592</v>
+      </c>
+      <c r="AR2">
+        <v>2.25</v>
+      </c>
+      <c r="AS2">
+        <v>28</v>
+      </c>
+      <c r="AT2">
+        <v>2.77</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.144332266191003</v>
+      </c>
+      <c r="C2">
+        <v>43.23355725040546</v>
+      </c>
+      <c r="D2">
+        <v>40.46355725040546</v>
+      </c>
+      <c r="E2">
+        <v>-28</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.77</v>
+      </c>
+      <c r="H2">
+        <v>13.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K2">
+        <v>1.53</v>
+      </c>
+      <c r="L2">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="O2">
+        <v>1.020666666666667</v>
+      </c>
+      <c r="P2">
+        <v>4.082666666666666</v>
+      </c>
+      <c r="Q2">
+        <v>5.612666666666666</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.144332266191003</v>
+      </c>
+      <c r="T2">
+        <v>1.172523243405601</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.144090801658621</v>
+      </c>
+      <c r="C3">
+        <v>42.91135276317646</v>
+      </c>
+      <c r="D3">
+        <v>40.55635276317646</v>
+      </c>
+      <c r="E3">
+        <v>-27.585</v>
+      </c>
+      <c r="F3">
+        <v>0.415</v>
+      </c>
+      <c r="G3">
+        <v>2.77</v>
+      </c>
+      <c r="H3">
+        <v>13.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K3">
+        <v>1.53</v>
+      </c>
+      <c r="L3">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.0185505</v>
+      </c>
+      <c r="N3">
+        <v>5.084782833333334</v>
+      </c>
+      <c r="O3">
+        <v>1.016956566666667</v>
+      </c>
+      <c r="P3">
+        <v>4.067826266666667</v>
+      </c>
+      <c r="Q3">
+        <v>5.597826266666667</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1451850521804252</v>
+      </c>
+      <c r="T3">
+        <v>1.181998178705849</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>275.1048938483239</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.143849337126239</v>
+      </c>
+      <c r="C4">
+        <v>42.58957487216809</v>
+      </c>
+      <c r="D4">
+        <v>40.64957487216808</v>
+      </c>
+      <c r="E4">
+        <v>-27.16999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="G4">
+        <v>2.77</v>
+      </c>
+      <c r="H4">
+        <v>13.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K4">
+        <v>1.53</v>
+      </c>
+      <c r="L4">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.03710100000000001</v>
+      </c>
+      <c r="N4">
+        <v>5.066232333333334</v>
+      </c>
+      <c r="O4">
+        <v>1.013246466666667</v>
+      </c>
+      <c r="P4">
+        <v>4.052985866666667</v>
+      </c>
+      <c r="Q4">
+        <v>5.582985866666666</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1460552419655499</v>
+      </c>
+      <c r="T4">
+        <v>1.191666480032632</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>137.552446924162</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1436078725938569</v>
+      </c>
+      <c r="C5">
+        <v>42.26822652585705</v>
+      </c>
+      <c r="D5">
+        <v>40.74322652585705</v>
+      </c>
+      <c r="E5">
+        <v>-26.755</v>
+      </c>
+      <c r="F5">
+        <v>1.245</v>
+      </c>
+      <c r="G5">
+        <v>2.77</v>
+      </c>
+      <c r="H5">
+        <v>13.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K5">
+        <v>1.53</v>
+      </c>
+      <c r="L5">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.0556515</v>
+      </c>
+      <c r="N5">
+        <v>5.047681833333334</v>
+      </c>
+      <c r="O5">
+        <v>1.009536366666667</v>
+      </c>
+      <c r="P5">
+        <v>4.038145466666667</v>
+      </c>
+      <c r="Q5">
+        <v>5.568145466666667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1469433738080999</v>
+      </c>
+      <c r="T5">
+        <v>1.201534127778523</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>91.70163128277466</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.143366408061475</v>
+      </c>
+      <c r="C6">
+        <v>41.94731069995447</v>
+      </c>
+      <c r="D6">
+        <v>40.83731069995447</v>
+      </c>
+      <c r="E6">
+        <v>-26.34</v>
+      </c>
+      <c r="F6">
+        <v>1.66</v>
+      </c>
+      <c r="G6">
+        <v>2.77</v>
+      </c>
+      <c r="H6">
+        <v>13.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K6">
+        <v>1.53</v>
+      </c>
+      <c r="L6">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.07420200000000002</v>
+      </c>
+      <c r="N6">
+        <v>5.029131333333334</v>
+      </c>
+      <c r="O6">
+        <v>1.005826266666667</v>
+      </c>
+      <c r="P6">
+        <v>4.023305066666667</v>
+      </c>
+      <c r="Q6">
+        <v>5.553305066666667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1478500083973698</v>
+      </c>
+      <c r="T6">
+        <v>1.211607351519122</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>68.77622346208098</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1431249435290929</v>
+      </c>
+      <c r="C7">
+        <v>41.62683039772124</v>
+      </c>
+      <c r="D7">
+        <v>40.93183039772124</v>
+      </c>
+      <c r="E7">
+        <v>-25.925</v>
+      </c>
+      <c r="F7">
+        <v>2.075</v>
+      </c>
+      <c r="G7">
+        <v>2.77</v>
+      </c>
+      <c r="H7">
+        <v>13.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K7">
+        <v>1.53</v>
+      </c>
+      <c r="L7">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.09275250000000002</v>
+      </c>
+      <c r="N7">
+        <v>5.010580833333334</v>
+      </c>
+      <c r="O7">
+        <v>1.002116166666667</v>
+      </c>
+      <c r="P7">
+        <v>4.008464666666667</v>
+      </c>
+      <c r="Q7">
+        <v>5.538464666666666</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1487757300306241</v>
+      </c>
+      <c r="T7">
+        <v>1.221892643127942</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>55.02097876966479</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1428834789967109</v>
+      </c>
+      <c r="C8">
+        <v>41.30678865028731</v>
+      </c>
+      <c r="D8">
+        <v>41.02678865028731</v>
+      </c>
+      <c r="E8">
+        <v>-25.51</v>
+      </c>
+      <c r="F8">
+        <v>2.49</v>
+      </c>
+      <c r="G8">
+        <v>2.77</v>
+      </c>
+      <c r="H8">
+        <v>13.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K8">
+        <v>1.53</v>
+      </c>
+      <c r="L8">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.111303</v>
+      </c>
+      <c r="N8">
+        <v>4.992030333333333</v>
+      </c>
+      <c r="O8">
+        <v>0.9984060666666666</v>
+      </c>
+      <c r="P8">
+        <v>3.993624266666667</v>
+      </c>
+      <c r="Q8">
+        <v>5.523624266666666</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1497211478688414</v>
+      </c>
+      <c r="T8">
+        <v>1.232396770728441</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>45.85081564138732</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1426420144643289</v>
+      </c>
+      <c r="C9">
+        <v>40.98718851697595</v>
+      </c>
+      <c r="D9">
+        <v>41.12218851697595</v>
+      </c>
+      <c r="E9">
+        <v>-25.095</v>
+      </c>
+      <c r="F9">
+        <v>2.905</v>
+      </c>
+      <c r="G9">
+        <v>2.77</v>
+      </c>
+      <c r="H9">
+        <v>13.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K9">
+        <v>1.53</v>
+      </c>
+      <c r="L9">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.1298535</v>
+      </c>
+      <c r="N9">
+        <v>4.973479833333333</v>
+      </c>
+      <c r="O9">
+        <v>0.9946959666666667</v>
+      </c>
+      <c r="P9">
+        <v>3.978783866666666</v>
+      </c>
+      <c r="Q9">
+        <v>5.508783866666667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.150686897273472</v>
+      </c>
+      <c r="T9">
+        <v>1.243126793546154</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>39.30069912118913</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1424005499319469</v>
+      </c>
+      <c r="C10">
+        <v>40.66803308563218</v>
+      </c>
+      <c r="D10">
+        <v>41.21803308563218</v>
+      </c>
+      <c r="E10">
+        <v>-24.68</v>
+      </c>
+      <c r="F10">
+        <v>3.32</v>
+      </c>
+      <c r="G10">
+        <v>2.77</v>
+      </c>
+      <c r="H10">
+        <v>13.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K10">
+        <v>1.53</v>
+      </c>
+      <c r="L10">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.148404</v>
+      </c>
+      <c r="N10">
+        <v>4.954929333333333</v>
+      </c>
+      <c r="O10">
+        <v>0.9909858666666667</v>
+      </c>
+      <c r="P10">
+        <v>3.963943466666667</v>
+      </c>
+      <c r="Q10">
+        <v>5.493943466666666</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1516736412303771</v>
+      </c>
+      <c r="T10">
+        <v>1.254090077729469</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>34.38811173104048</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1421590853995649</v>
+      </c>
+      <c r="C11">
+        <v>40.34932547295598</v>
+      </c>
+      <c r="D11">
+        <v>41.31432547295598</v>
+      </c>
+      <c r="E11">
+        <v>-24.265</v>
+      </c>
+      <c r="F11">
+        <v>3.735</v>
+      </c>
+      <c r="G11">
+        <v>2.77</v>
+      </c>
+      <c r="H11">
+        <v>13.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K11">
+        <v>1.53</v>
+      </c>
+      <c r="L11">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M11">
+        <v>0.1669545</v>
+      </c>
+      <c r="N11">
+        <v>4.936378833333333</v>
+      </c>
+      <c r="O11">
+        <v>0.9872757666666667</v>
+      </c>
+      <c r="P11">
+        <v>3.949103066666667</v>
+      </c>
+      <c r="Q11">
+        <v>5.479103066666667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1526820718676538</v>
+      </c>
+      <c r="T11">
+        <v>1.265294313213517</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>30.56721042759155</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1419176208671829</v>
+      </c>
+      <c r="C12">
+        <v>40.03106882484009</v>
+      </c>
+      <c r="D12">
+        <v>41.41106882484009</v>
+      </c>
+      <c r="E12">
+        <v>-23.84999999999999</v>
+      </c>
+      <c r="F12">
+        <v>4.15</v>
+      </c>
+      <c r="G12">
+        <v>2.77</v>
+      </c>
+      <c r="H12">
+        <v>13.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K12">
+        <v>1.53</v>
+      </c>
+      <c r="L12">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M12">
+        <v>0.185505</v>
+      </c>
+      <c r="N12">
+        <v>4.917828333333333</v>
+      </c>
+      <c r="O12">
+        <v>0.9835656666666668</v>
+      </c>
+      <c r="P12">
+        <v>3.934262666666667</v>
+      </c>
+      <c r="Q12">
+        <v>5.464262666666666</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1537129120746477</v>
+      </c>
+      <c r="T12">
+        <v>1.276747531708322</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>27.51048938483239</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1416761563348009</v>
+      </c>
+      <c r="C13">
+        <v>39.71326631671262</v>
+      </c>
+      <c r="D13">
+        <v>41.50826631671261</v>
+      </c>
+      <c r="E13">
+        <v>-23.435</v>
+      </c>
+      <c r="F13">
+        <v>4.565</v>
+      </c>
+      <c r="G13">
+        <v>2.77</v>
+      </c>
+      <c r="H13">
+        <v>13.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K13">
+        <v>1.53</v>
+      </c>
+      <c r="L13">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M13">
+        <v>0.2040555</v>
+      </c>
+      <c r="N13">
+        <v>4.899277833333334</v>
+      </c>
+      <c r="O13">
+        <v>0.9798555666666667</v>
+      </c>
+      <c r="P13">
+        <v>3.919422266666667</v>
+      </c>
+      <c r="Q13">
+        <v>5.449422266666667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1547669172301134</v>
+      </c>
+      <c r="T13">
+        <v>1.288458125899638</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>25.00953580439309</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1414346918024189</v>
+      </c>
+      <c r="C14">
+        <v>39.39592115388452</v>
+      </c>
+      <c r="D14">
+        <v>41.60592115388451</v>
+      </c>
+      <c r="E14">
+        <v>-23.02</v>
+      </c>
+      <c r="F14">
+        <v>4.98</v>
+      </c>
+      <c r="G14">
+        <v>2.77</v>
+      </c>
+      <c r="H14">
+        <v>13.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K14">
+        <v>1.53</v>
+      </c>
+      <c r="L14">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M14">
+        <v>0.222606</v>
+      </c>
+      <c r="N14">
+        <v>4.880727333333334</v>
+      </c>
+      <c r="O14">
+        <v>0.9761454666666668</v>
+      </c>
+      <c r="P14">
+        <v>3.904581866666667</v>
+      </c>
+      <c r="Q14">
+        <v>5.434581866666667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1558448770482033</v>
+      </c>
+      <c r="T14">
+        <v>1.30043486995894</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>22.92540782069366</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1411932272700369</v>
+      </c>
+      <c r="C15">
+        <v>39.07903657190186</v>
+      </c>
+      <c r="D15">
+        <v>41.70403657190186</v>
+      </c>
+      <c r="E15">
+        <v>-22.605</v>
+      </c>
+      <c r="F15">
+        <v>5.395</v>
+      </c>
+      <c r="G15">
+        <v>2.77</v>
+      </c>
+      <c r="H15">
+        <v>13.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K15">
+        <v>1.53</v>
+      </c>
+      <c r="L15">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M15">
+        <v>0.2411565000000001</v>
+      </c>
+      <c r="N15">
+        <v>4.862176833333334</v>
+      </c>
+      <c r="O15">
+        <v>0.9724353666666667</v>
+      </c>
+      <c r="P15">
+        <v>3.889741466666667</v>
+      </c>
+      <c r="Q15">
+        <v>5.419741466666666</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1569476175517665</v>
+      </c>
+      <c r="T15">
+        <v>1.31268694146788</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>21.16191491140953</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1409517627376549</v>
+      </c>
+      <c r="C16">
+        <v>38.76261583690328</v>
+      </c>
+      <c r="D16">
+        <v>41.80261583690328</v>
+      </c>
+      <c r="E16">
+        <v>-22.19</v>
+      </c>
+      <c r="F16">
+        <v>5.81</v>
+      </c>
+      <c r="G16">
+        <v>2.77</v>
+      </c>
+      <c r="H16">
+        <v>13.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K16">
+        <v>1.53</v>
+      </c>
+      <c r="L16">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M16">
+        <v>0.259707</v>
+      </c>
+      <c r="N16">
+        <v>4.843626333333334</v>
+      </c>
+      <c r="O16">
+        <v>0.9687252666666668</v>
+      </c>
+      <c r="P16">
+        <v>3.874901066666667</v>
+      </c>
+      <c r="Q16">
+        <v>5.404901066666667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1580760031833196</v>
+      </c>
+      <c r="T16">
+        <v>1.325223944872377</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>19.65034956059457</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1407102982052729</v>
+      </c>
+      <c r="C17">
+        <v>38.44666224598226</v>
+      </c>
+      <c r="D17">
+        <v>41.90166224598226</v>
+      </c>
+      <c r="E17">
+        <v>-21.775</v>
+      </c>
+      <c r="F17">
+        <v>6.225</v>
+      </c>
+      <c r="G17">
+        <v>2.77</v>
+      </c>
+      <c r="H17">
+        <v>13.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K17">
+        <v>1.53</v>
+      </c>
+      <c r="L17">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M17">
+        <v>0.2782575</v>
+      </c>
+      <c r="N17">
+        <v>4.825075833333334</v>
+      </c>
+      <c r="O17">
+        <v>0.9650151666666669</v>
+      </c>
+      <c r="P17">
+        <v>3.860060666666667</v>
+      </c>
+      <c r="Q17">
+        <v>5.390060666666667</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1592309390650269</v>
+      </c>
+      <c r="T17">
+        <v>1.338055936592275</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>18.34032625655493</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1404688336728908</v>
+      </c>
+      <c r="C18">
+        <v>38.13117912755494</v>
+      </c>
+      <c r="D18">
+        <v>42.00117912755493</v>
+      </c>
+      <c r="E18">
+        <v>-21.36</v>
+      </c>
+      <c r="F18">
+        <v>6.640000000000001</v>
+      </c>
+      <c r="G18">
+        <v>2.77</v>
+      </c>
+      <c r="H18">
+        <v>13.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K18">
+        <v>1.53</v>
+      </c>
+      <c r="L18">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M18">
+        <v>0.2968080000000001</v>
+      </c>
+      <c r="N18">
+        <v>4.806525333333333</v>
+      </c>
+      <c r="O18">
+        <v>0.9613050666666667</v>
+      </c>
+      <c r="P18">
+        <v>3.845220266666666</v>
+      </c>
+      <c r="Q18">
+        <v>5.375220266666666</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1604133734201082</v>
+      </c>
+      <c r="T18">
+        <v>1.35119345192455</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>17.19405586552024</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1402273691405088</v>
+      </c>
+      <c r="C19">
+        <v>37.81616984173267</v>
+      </c>
+      <c r="D19">
+        <v>42.10116984173266</v>
+      </c>
+      <c r="E19">
+        <v>-20.945</v>
+      </c>
+      <c r="F19">
+        <v>7.055000000000001</v>
+      </c>
+      <c r="G19">
+        <v>2.77</v>
+      </c>
+      <c r="H19">
+        <v>13.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K19">
+        <v>1.53</v>
+      </c>
+      <c r="L19">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M19">
+        <v>0.3153585</v>
+      </c>
+      <c r="N19">
+        <v>4.787974833333333</v>
+      </c>
+      <c r="O19">
+        <v>0.9575949666666667</v>
+      </c>
+      <c r="P19">
+        <v>3.830379866666667</v>
+      </c>
+      <c r="Q19">
+        <v>5.360379866666666</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1616243001692878</v>
+      </c>
+      <c r="T19">
+        <v>1.364647533891338</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>16.18264081460729</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1399859046081268</v>
+      </c>
+      <c r="C20">
+        <v>37.50163778070045</v>
+      </c>
+      <c r="D20">
+        <v>42.20163778070044</v>
+      </c>
+      <c r="E20">
+        <v>-20.53</v>
+      </c>
+      <c r="F20">
+        <v>7.47</v>
+      </c>
+      <c r="G20">
+        <v>2.77</v>
+      </c>
+      <c r="H20">
+        <v>13.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K20">
+        <v>1.53</v>
+      </c>
+      <c r="L20">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M20">
+        <v>0.333909</v>
+      </c>
+      <c r="N20">
+        <v>4.769424333333333</v>
+      </c>
+      <c r="O20">
+        <v>0.9538848666666667</v>
+      </c>
+      <c r="P20">
+        <v>3.815539466666666</v>
+      </c>
+      <c r="Q20">
+        <v>5.345539466666667</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1628647617172279</v>
+      </c>
+      <c r="T20">
+        <v>1.37842976419878</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>15.28360521379577</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1397444400757449</v>
+      </c>
+      <c r="C21">
+        <v>37.1875863691004</v>
+      </c>
+      <c r="D21">
+        <v>42.3025863691004</v>
+      </c>
+      <c r="E21">
+        <v>-20.11499999999999</v>
+      </c>
+      <c r="F21">
+        <v>7.885</v>
+      </c>
+      <c r="G21">
+        <v>2.77</v>
+      </c>
+      <c r="H21">
+        <v>13.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K21">
+        <v>1.53</v>
+      </c>
+      <c r="L21">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M21">
+        <v>0.3524595</v>
+      </c>
+      <c r="N21">
+        <v>4.750873833333333</v>
+      </c>
+      <c r="O21">
+        <v>0.9501747666666667</v>
+      </c>
+      <c r="P21">
+        <v>3.800699066666667</v>
+      </c>
+      <c r="Q21">
+        <v>5.330699066666666</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.164135851945364</v>
+      </c>
+      <c r="T21">
+        <v>1.392552296489122</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>14.47920493938547</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1395029755433628</v>
+      </c>
+      <c r="C22">
+        <v>36.87401906442098</v>
+      </c>
+      <c r="D22">
+        <v>42.40401906442098</v>
+      </c>
+      <c r="E22">
+        <v>-19.7</v>
+      </c>
+      <c r="F22">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G22">
+        <v>2.77</v>
+      </c>
+      <c r="H22">
+        <v>13.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K22">
+        <v>1.53</v>
+      </c>
+      <c r="L22">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M22">
+        <v>0.3710100000000001</v>
+      </c>
+      <c r="N22">
+        <v>4.732323333333333</v>
+      </c>
+      <c r="O22">
+        <v>0.9464646666666667</v>
+      </c>
+      <c r="P22">
+        <v>3.785858666666667</v>
+      </c>
+      <c r="Q22">
+        <v>5.315858666666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1654387194292035</v>
+      </c>
+      <c r="T22">
+        <v>1.407027892086722</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>13.75524469241619</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1392615110109809</v>
+      </c>
+      <c r="C23">
+        <v>36.56093935739156</v>
+      </c>
+      <c r="D23">
+        <v>42.50593935739156</v>
+      </c>
+      <c r="E23">
+        <v>-19.285</v>
+      </c>
+      <c r="F23">
+        <v>8.715</v>
+      </c>
+      <c r="G23">
+        <v>2.77</v>
+      </c>
+      <c r="H23">
+        <v>13.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K23">
+        <v>1.53</v>
+      </c>
+      <c r="L23">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M23">
+        <v>0.3895605</v>
+      </c>
+      <c r="N23">
+        <v>4.713772833333334</v>
+      </c>
+      <c r="O23">
+        <v>0.9427545666666668</v>
+      </c>
+      <c r="P23">
+        <v>3.771018266666667</v>
+      </c>
+      <c r="Q23">
+        <v>5.301018266666667</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1667745708999757</v>
+      </c>
+      <c r="T23">
+        <v>1.421869958458944</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>13.10023304039638</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1392136464785989</v>
+      </c>
+      <c r="C24">
+        <v>36.16620081569079</v>
+      </c>
+      <c r="D24">
+        <v>42.52620081569079</v>
+      </c>
+      <c r="E24">
+        <v>-18.87</v>
+      </c>
+      <c r="F24">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G24">
+        <v>2.77</v>
+      </c>
+      <c r="H24">
+        <v>13.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K24">
+        <v>1.53</v>
+      </c>
+      <c r="L24">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M24">
+        <v>0.418154</v>
+      </c>
+      <c r="N24">
+        <v>4.685179333333333</v>
+      </c>
+      <c r="O24">
+        <v>0.9370358666666667</v>
+      </c>
+      <c r="P24">
+        <v>3.748143466666666</v>
+      </c>
+      <c r="Q24">
+        <v>5.278143466666666</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1681446749725626</v>
+      </c>
+      <c r="T24">
+        <v>1.437092590635583</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03664</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>12.20443504865034</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1389809819462168</v>
+      </c>
+      <c r="C25">
+        <v>35.84996545579063</v>
+      </c>
+      <c r="D25">
+        <v>42.62496545579063</v>
+      </c>
+      <c r="E25">
+        <v>-18.455</v>
+      </c>
+      <c r="F25">
+        <v>9.545</v>
+      </c>
+      <c r="G25">
+        <v>2.77</v>
+      </c>
+      <c r="H25">
+        <v>13.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K25">
+        <v>1.53</v>
+      </c>
+      <c r="L25">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M25">
+        <v>0.437161</v>
+      </c>
+      <c r="N25">
+        <v>4.666172333333334</v>
+      </c>
+      <c r="O25">
+        <v>0.9332344666666668</v>
+      </c>
+      <c r="P25">
+        <v>3.732937866666667</v>
+      </c>
+      <c r="Q25">
+        <v>5.262937866666666</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.169550366163918</v>
+      </c>
+      <c r="T25">
+        <v>1.452710615855771</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.03664</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>11.67380743783945</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1387483174138348</v>
+      </c>
+      <c r="C26">
+        <v>35.53418991411252</v>
+      </c>
+      <c r="D26">
+        <v>42.72418991411251</v>
+      </c>
+      <c r="E26">
+        <v>-18.04</v>
+      </c>
+      <c r="F26">
+        <v>9.959999999999999</v>
+      </c>
+      <c r="G26">
+        <v>2.77</v>
+      </c>
+      <c r="H26">
+        <v>13.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K26">
+        <v>1.53</v>
+      </c>
+      <c r="L26">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M26">
+        <v>0.456168</v>
+      </c>
+      <c r="N26">
+        <v>4.647165333333334</v>
+      </c>
+      <c r="O26">
+        <v>0.9294330666666668</v>
+      </c>
+      <c r="P26">
+        <v>3.717732266666667</v>
+      </c>
+      <c r="Q26">
+        <v>5.247732266666667</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.17099304922873</v>
+      </c>
+      <c r="T26">
+        <v>1.468739641739648</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.03664</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.18739879459614</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1385156528814528</v>
+      </c>
+      <c r="C27">
+        <v>35.21887740931034</v>
+      </c>
+      <c r="D27">
+        <v>42.82387740931033</v>
+      </c>
+      <c r="E27">
+        <v>-17.625</v>
+      </c>
+      <c r="F27">
+        <v>10.375</v>
+      </c>
+      <c r="G27">
+        <v>2.77</v>
+      </c>
+      <c r="H27">
+        <v>13.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K27">
+        <v>1.53</v>
+      </c>
+      <c r="L27">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M27">
+        <v>0.475175</v>
+      </c>
+      <c r="N27">
+        <v>4.628158333333333</v>
+      </c>
+      <c r="O27">
+        <v>0.9256316666666667</v>
+      </c>
+      <c r="P27">
+        <v>3.702526666666667</v>
+      </c>
+      <c r="Q27">
+        <v>5.232526666666667</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1724742038419371</v>
+      </c>
+      <c r="T27">
+        <v>1.485196108313762</v>
+      </c>
+      <c r="U27">
+        <v>0.0458</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.03664</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.7399028428123</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1382829883490708</v>
+      </c>
+      <c r="C28">
+        <v>34.90403119014833</v>
+      </c>
+      <c r="D28">
+        <v>42.92403119014833</v>
+      </c>
+      <c r="E28">
+        <v>-17.20999999999999</v>
+      </c>
+      <c r="F28">
+        <v>10.79</v>
+      </c>
+      <c r="G28">
+        <v>2.77</v>
+      </c>
+      <c r="H28">
+        <v>13.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K28">
+        <v>1.53</v>
+      </c>
+      <c r="L28">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M28">
+        <v>0.4941820000000001</v>
+      </c>
+      <c r="N28">
+        <v>4.609151333333333</v>
+      </c>
+      <c r="O28">
+        <v>0.9218302666666667</v>
+      </c>
+      <c r="P28">
+        <v>3.687321066666667</v>
+      </c>
+      <c r="Q28">
+        <v>5.217321066666667</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1739953896609065</v>
+      </c>
+      <c r="T28">
+        <v>1.502097344254743</v>
+      </c>
+      <c r="U28">
+        <v>0.0458</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.03664</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.32682965655028</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1385255238166888</v>
+      </c>
+      <c r="C29">
+        <v>34.38463865774219</v>
+      </c>
+      <c r="D29">
+        <v>42.81963865774218</v>
+      </c>
+      <c r="E29">
+        <v>-16.79499999999999</v>
+      </c>
+      <c r="F29">
+        <v>11.205</v>
+      </c>
+      <c r="G29">
+        <v>2.77</v>
+      </c>
+      <c r="H29">
+        <v>13.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K29">
+        <v>1.53</v>
+      </c>
+      <c r="L29">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M29">
+        <v>0.53784</v>
+      </c>
+      <c r="N29">
+        <v>4.565493333333333</v>
+      </c>
+      <c r="O29">
+        <v>0.9130986666666667</v>
+      </c>
+      <c r="P29">
+        <v>3.652394666666667</v>
+      </c>
+      <c r="Q29">
+        <v>5.182394666666667</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1755582518036833</v>
+      </c>
+      <c r="T29">
+        <v>1.519461627755752</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.0384</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>9.488571570231544</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1383104592843068</v>
+      </c>
+      <c r="C30">
+        <v>34.06218154851895</v>
+      </c>
+      <c r="D30">
+        <v>42.91218154851895</v>
+      </c>
+      <c r="E30">
+        <v>-16.38</v>
+      </c>
+      <c r="F30">
+        <v>11.62</v>
+      </c>
+      <c r="G30">
+        <v>2.77</v>
+      </c>
+      <c r="H30">
+        <v>13.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K30">
+        <v>1.53</v>
+      </c>
+      <c r="L30">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M30">
+        <v>0.55776</v>
+      </c>
+      <c r="N30">
+        <v>4.545573333333333</v>
+      </c>
+      <c r="O30">
+        <v>0.9091146666666667</v>
+      </c>
+      <c r="P30">
+        <v>3.636458666666667</v>
+      </c>
+      <c r="Q30">
+        <v>5.166458666666667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1771645267837594</v>
+      </c>
+      <c r="T30">
+        <v>1.537308252465122</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.0384</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.149694014151844</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1380953947519248</v>
+      </c>
+      <c r="C31">
+        <v>33.74012531777714</v>
+      </c>
+      <c r="D31">
+        <v>43.00512531777714</v>
+      </c>
+      <c r="E31">
+        <v>-15.965</v>
+      </c>
+      <c r="F31">
+        <v>12.035</v>
+      </c>
+      <c r="G31">
+        <v>2.77</v>
+      </c>
+      <c r="H31">
+        <v>13.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K31">
+        <v>1.53</v>
+      </c>
+      <c r="L31">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M31">
+        <v>0.57768</v>
+      </c>
+      <c r="N31">
+        <v>4.525653333333334</v>
+      </c>
+      <c r="O31">
+        <v>0.9051306666666667</v>
+      </c>
+      <c r="P31">
+        <v>3.620522666666667</v>
+      </c>
+      <c r="Q31">
+        <v>5.150522666666667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.178816048946373</v>
+      </c>
+      <c r="T31">
+        <v>1.555657598997291</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.0384</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>8.834187324008679</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1378803302195428</v>
+      </c>
+      <c r="C32">
+        <v>33.41847257596658</v>
+      </c>
+      <c r="D32">
+        <v>43.09847257596657</v>
+      </c>
+      <c r="E32">
+        <v>-15.55</v>
+      </c>
+      <c r="F32">
+        <v>12.45</v>
+      </c>
+      <c r="G32">
+        <v>2.77</v>
+      </c>
+      <c r="H32">
+        <v>13.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K32">
+        <v>1.53</v>
+      </c>
+      <c r="L32">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M32">
+        <v>0.5976</v>
+      </c>
+      <c r="N32">
+        <v>4.505733333333334</v>
+      </c>
+      <c r="O32">
+        <v>0.9011466666666668</v>
+      </c>
+      <c r="P32">
+        <v>3.604586666666667</v>
+      </c>
+      <c r="Q32">
+        <v>5.134586666666667</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1805147574564897</v>
+      </c>
+      <c r="T32">
+        <v>1.574531212573236</v>
+      </c>
+      <c r="U32">
+        <v>0.048</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.0384</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.53971441320839</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1376652656871608</v>
+      </c>
+      <c r="C33">
+        <v>33.0972259562514</v>
+      </c>
+      <c r="D33">
+        <v>43.1922259562514</v>
+      </c>
+      <c r="E33">
+        <v>-15.135</v>
+      </c>
+      <c r="F33">
+        <v>12.865</v>
+      </c>
+      <c r="G33">
+        <v>2.77</v>
+      </c>
+      <c r="H33">
+        <v>13.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K33">
+        <v>1.53</v>
+      </c>
+      <c r="L33">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M33">
+        <v>0.6175200000000001</v>
+      </c>
+      <c r="N33">
+        <v>4.485813333333334</v>
+      </c>
+      <c r="O33">
+        <v>0.8971626666666668</v>
+      </c>
+      <c r="P33">
+        <v>3.588650666666667</v>
+      </c>
+      <c r="Q33">
+        <v>5.118650666666667</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1822627038944359</v>
+      </c>
+      <c r="T33">
+        <v>1.593951887412252</v>
+      </c>
+      <c r="U33">
+        <v>0.048</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.0384</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.264239754717796</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1374502011547788</v>
+      </c>
+      <c r="C34">
+        <v>32.77638811475775</v>
+      </c>
+      <c r="D34">
+        <v>43.28638811475775</v>
+      </c>
+      <c r="E34">
+        <v>-14.72</v>
+      </c>
+      <c r="F34">
+        <v>13.28</v>
+      </c>
+      <c r="G34">
+        <v>2.77</v>
+      </c>
+      <c r="H34">
+        <v>13.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K34">
+        <v>1.53</v>
+      </c>
+      <c r="L34">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M34">
+        <v>0.6374400000000001</v>
+      </c>
+      <c r="N34">
+        <v>4.465893333333334</v>
+      </c>
+      <c r="O34">
+        <v>0.8931786666666668</v>
+      </c>
+      <c r="P34">
+        <v>3.572714666666667</v>
+      </c>
+      <c r="Q34">
+        <v>5.102714666666667</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1840620605217335</v>
+      </c>
+      <c r="T34">
+        <v>1.613943758570063</v>
+      </c>
+      <c r="U34">
+        <v>0.048</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.0384</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.005982262382865</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1372351366223968</v>
+      </c>
+      <c r="C35">
+        <v>32.45596173082453</v>
+      </c>
+      <c r="D35">
+        <v>43.38096173082452</v>
+      </c>
+      <c r="E35">
+        <v>-14.305</v>
+      </c>
+      <c r="F35">
+        <v>13.695</v>
+      </c>
+      <c r="G35">
+        <v>2.77</v>
+      </c>
+      <c r="H35">
+        <v>13.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K35">
+        <v>1.53</v>
+      </c>
+      <c r="L35">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M35">
+        <v>0.6573600000000001</v>
+      </c>
+      <c r="N35">
+        <v>4.445973333333334</v>
+      </c>
+      <c r="O35">
+        <v>0.8891946666666668</v>
+      </c>
+      <c r="P35">
+        <v>3.556778666666667</v>
+      </c>
+      <c r="Q35">
+        <v>5.086778666666667</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1859151292871594</v>
+      </c>
+      <c r="T35">
+        <v>1.634532402001242</v>
+      </c>
+      <c r="U35">
+        <v>0.048</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.0384</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.763376739280353</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1374280720900148</v>
+      </c>
+      <c r="C36">
+        <v>31.95610023084898</v>
+      </c>
+      <c r="D36">
+        <v>43.29610023084898</v>
+      </c>
+      <c r="E36">
+        <v>-13.89</v>
+      </c>
+      <c r="F36">
+        <v>14.11</v>
+      </c>
+      <c r="G36">
+        <v>2.77</v>
+      </c>
+      <c r="H36">
+        <v>13.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K36">
+        <v>1.53</v>
+      </c>
+      <c r="L36">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M36">
+        <v>0.6984450000000001</v>
+      </c>
+      <c r="N36">
+        <v>4.404888333333333</v>
+      </c>
+      <c r="O36">
+        <v>0.8809776666666667</v>
+      </c>
+      <c r="P36">
+        <v>3.523910666666667</v>
+      </c>
+      <c r="Q36">
+        <v>5.053910666666667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1878243516515375</v>
+      </c>
+      <c r="T36">
+        <v>1.655744943718213</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.0396</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.306707519322685</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1372250075576328</v>
+      </c>
+      <c r="C37">
+        <v>31.63042613049083</v>
+      </c>
+      <c r="D37">
+        <v>43.38542613049083</v>
+      </c>
+      <c r="E37">
+        <v>-13.47499999999999</v>
+      </c>
+      <c r="F37">
+        <v>14.525</v>
+      </c>
+      <c r="G37">
+        <v>2.77</v>
+      </c>
+      <c r="H37">
+        <v>13.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K37">
+        <v>1.53</v>
+      </c>
+      <c r="L37">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M37">
+        <v>0.7189875000000001</v>
+      </c>
+      <c r="N37">
+        <v>4.384345833333334</v>
+      </c>
+      <c r="O37">
+        <v>0.8768691666666668</v>
+      </c>
+      <c r="P37">
+        <v>3.507476666666667</v>
+      </c>
+      <c r="Q37">
+        <v>5.037476666666667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.189792319319435</v>
+      </c>
+      <c r="T37">
+        <v>1.677610179026476</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.0396</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>7.097944447342037</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1370219430252508</v>
+      </c>
+      <c r="C38">
+        <v>31.30512137574898</v>
+      </c>
+      <c r="D38">
+        <v>43.47512137574898</v>
+      </c>
+      <c r="E38">
+        <v>-13.06</v>
+      </c>
+      <c r="F38">
+        <v>14.94</v>
+      </c>
+      <c r="G38">
+        <v>2.77</v>
+      </c>
+      <c r="H38">
+        <v>13.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K38">
+        <v>1.53</v>
+      </c>
+      <c r="L38">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M38">
+        <v>0.73953</v>
+      </c>
+      <c r="N38">
+        <v>4.363803333333333</v>
+      </c>
+      <c r="O38">
+        <v>0.8727606666666667</v>
+      </c>
+      <c r="P38">
+        <v>3.491042666666667</v>
+      </c>
+      <c r="Q38">
+        <v>5.021042666666666</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1918217859769543</v>
+      </c>
+      <c r="T38">
+        <v>1.700158702938122</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.0396</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.900779323804759</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1368188784928688</v>
+      </c>
+      <c r="C39">
+        <v>30.98018826213004</v>
+      </c>
+      <c r="D39">
+        <v>43.56518826213004</v>
+      </c>
+      <c r="E39">
+        <v>-12.645</v>
+      </c>
+      <c r="F39">
+        <v>15.355</v>
+      </c>
+      <c r="G39">
+        <v>2.77</v>
+      </c>
+      <c r="H39">
+        <v>13.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K39">
+        <v>1.53</v>
+      </c>
+      <c r="L39">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M39">
+        <v>0.7600725</v>
+      </c>
+      <c r="N39">
+        <v>4.343260833333334</v>
+      </c>
+      <c r="O39">
+        <v>0.8686521666666668</v>
+      </c>
+      <c r="P39">
+        <v>3.474608666666667</v>
+      </c>
+      <c r="Q39">
+        <v>5.004608666666667</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1939156801474107</v>
+      </c>
+      <c r="T39">
+        <v>1.723423053005694</v>
+      </c>
+      <c r="U39">
+        <v>0.0495</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.0396</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.714271774512738</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1366158139604867</v>
+      </c>
+      <c r="C40">
+        <v>30.65562910420246</v>
+      </c>
+      <c r="D40">
+        <v>43.65562910420246</v>
+      </c>
+      <c r="E40">
+        <v>-12.23</v>
+      </c>
+      <c r="F40">
+        <v>15.77</v>
+      </c>
+      <c r="G40">
+        <v>2.77</v>
+      </c>
+      <c r="H40">
+        <v>13.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K40">
+        <v>1.53</v>
+      </c>
+      <c r="L40">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M40">
+        <v>0.7806150000000001</v>
+      </c>
+      <c r="N40">
+        <v>4.322718333333333</v>
+      </c>
+      <c r="O40">
+        <v>0.8645436666666667</v>
+      </c>
+      <c r="P40">
+        <v>3.458174666666667</v>
+      </c>
+      <c r="Q40">
+        <v>4.988174666666667</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1960771192911076</v>
+      </c>
+      <c r="T40">
+        <v>1.74743786597867</v>
+      </c>
+      <c r="U40">
+        <v>0.0495</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.0396</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.537580412025561</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1364127494281047</v>
+      </c>
+      <c r="C41">
+        <v>30.33144623579464</v>
+      </c>
+      <c r="D41">
+        <v>43.74644623579464</v>
+      </c>
+      <c r="E41">
+        <v>-11.81499999999999</v>
+      </c>
+      <c r="F41">
+        <v>16.185</v>
+      </c>
+      <c r="G41">
+        <v>2.77</v>
+      </c>
+      <c r="H41">
+        <v>13.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K41">
+        <v>1.53</v>
+      </c>
+      <c r="L41">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M41">
+        <v>0.8011575000000002</v>
+      </c>
+      <c r="N41">
+        <v>4.302175833333333</v>
+      </c>
+      <c r="O41">
+        <v>0.8604351666666666</v>
+      </c>
+      <c r="P41">
+        <v>3.441740666666667</v>
+      </c>
+      <c r="Q41">
+        <v>4.971740666666666</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.198309425291975</v>
+      </c>
+      <c r="T41">
+        <v>1.772240049868794</v>
+      </c>
+      <c r="U41">
+        <v>0.0495</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.0396</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.369950145050545</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1362096848957227</v>
+      </c>
+      <c r="C42">
+        <v>30.00764201019587</v>
+      </c>
+      <c r="D42">
+        <v>43.83764201019586</v>
+      </c>
+      <c r="E42">
+        <v>-11.4</v>
+      </c>
+      <c r="F42">
+        <v>16.6</v>
+      </c>
+      <c r="G42">
+        <v>2.77</v>
+      </c>
+      <c r="H42">
+        <v>13.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K42">
+        <v>1.53</v>
+      </c>
+      <c r="L42">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M42">
+        <v>0.8217000000000001</v>
+      </c>
+      <c r="N42">
+        <v>4.281633333333334</v>
+      </c>
+      <c r="O42">
+        <v>0.8563266666666668</v>
+      </c>
+      <c r="P42">
+        <v>3.425306666666667</v>
+      </c>
+      <c r="Q42">
+        <v>4.955306666666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2006161414928712</v>
+      </c>
+      <c r="T42">
+        <v>1.797868973221922</v>
+      </c>
+      <c r="U42">
+        <v>0.0495</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.0396</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.210701391424283</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1364658203633407</v>
+      </c>
+      <c r="C43">
+        <v>29.47767471771034</v>
+      </c>
+      <c r="D43">
+        <v>43.72267471771034</v>
+      </c>
+      <c r="E43">
+        <v>-10.985</v>
+      </c>
+      <c r="F43">
+        <v>17.015</v>
+      </c>
+      <c r="G43">
+        <v>2.77</v>
+      </c>
+      <c r="H43">
+        <v>13.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K43">
+        <v>1.53</v>
+      </c>
+      <c r="L43">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M43">
+        <v>0.8660635000000001</v>
+      </c>
+      <c r="N43">
+        <v>4.237269833333333</v>
+      </c>
+      <c r="O43">
+        <v>0.8474539666666667</v>
+      </c>
+      <c r="P43">
+        <v>3.389815866666667</v>
+      </c>
+      <c r="Q43">
+        <v>4.919815866666667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2030010514632894</v>
+      </c>
+      <c r="T43">
+        <v>1.824366673637868</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.89256253534912</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1362739558309587</v>
+      </c>
+      <c r="C44">
+        <v>29.1487369942199</v>
+      </c>
+      <c r="D44">
+        <v>43.80873699421989</v>
+      </c>
+      <c r="E44">
+        <v>-10.57</v>
+      </c>
+      <c r="F44">
+        <v>17.43</v>
+      </c>
+      <c r="G44">
+        <v>2.77</v>
+      </c>
+      <c r="H44">
+        <v>13.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K44">
+        <v>1.53</v>
+      </c>
+      <c r="L44">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M44">
+        <v>0.8871869999999999</v>
+      </c>
+      <c r="N44">
+        <v>4.216146333333334</v>
+      </c>
+      <c r="O44">
+        <v>0.8432292666666668</v>
+      </c>
+      <c r="P44">
+        <v>3.372917066666667</v>
+      </c>
+      <c r="Q44">
+        <v>4.902917066666667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2054681997085495</v>
+      </c>
+      <c r="T44">
+        <v>1.85177808786126</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.752263427364618</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1360820912985767</v>
+      </c>
+      <c r="C45">
+        <v>28.82013874325142</v>
+      </c>
+      <c r="D45">
+        <v>43.89513874325142</v>
+      </c>
+      <c r="E45">
+        <v>-10.155</v>
+      </c>
+      <c r="F45">
+        <v>17.845</v>
+      </c>
+      <c r="G45">
+        <v>2.77</v>
+      </c>
+      <c r="H45">
+        <v>13.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K45">
+        <v>1.53</v>
+      </c>
+      <c r="L45">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M45">
+        <v>0.9083104999999999</v>
+      </c>
+      <c r="N45">
+        <v>4.195022833333334</v>
+      </c>
+      <c r="O45">
+        <v>0.8390045666666668</v>
+      </c>
+      <c r="P45">
+        <v>3.356018266666667</v>
+      </c>
+      <c r="Q45">
+        <v>4.886018266666667</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2080219145589065</v>
+      </c>
+      <c r="T45">
+        <v>1.880151306092491</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.618489859286372</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1358902267661947</v>
+      </c>
+      <c r="C46">
+        <v>28.49188197734746</v>
+      </c>
+      <c r="D46">
+        <v>43.98188197734746</v>
+      </c>
+      <c r="E46">
+        <v>-9.739999999999995</v>
+      </c>
+      <c r="F46">
+        <v>18.26</v>
+      </c>
+      <c r="G46">
+        <v>2.77</v>
+      </c>
+      <c r="H46">
+        <v>13.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K46">
+        <v>1.53</v>
+      </c>
+      <c r="L46">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M46">
+        <v>0.9294340000000001</v>
+      </c>
+      <c r="N46">
+        <v>4.173899333333333</v>
+      </c>
+      <c r="O46">
+        <v>0.8347798666666666</v>
+      </c>
+      <c r="P46">
+        <v>3.339119466666666</v>
+      </c>
+      <c r="Q46">
+        <v>4.869119466666666</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.210666833511062</v>
+      </c>
+      <c r="T46">
+        <v>1.909537853546265</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.490796907938953</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1356983622338127</v>
+      </c>
+      <c r="C47">
+        <v>28.16396872499034</v>
+      </c>
+      <c r="D47">
+        <v>44.06896872499033</v>
+      </c>
+      <c r="E47">
+        <v>-9.324999999999996</v>
+      </c>
+      <c r="F47">
+        <v>18.675</v>
+      </c>
+      <c r="G47">
+        <v>2.77</v>
+      </c>
+      <c r="H47">
+        <v>13.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K47">
+        <v>1.53</v>
+      </c>
+      <c r="L47">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M47">
+        <v>0.9505575000000001</v>
+      </c>
+      <c r="N47">
+        <v>4.152775833333333</v>
+      </c>
+      <c r="O47">
+        <v>0.8305551666666666</v>
+      </c>
+      <c r="P47">
+        <v>3.322220666666666</v>
+      </c>
+      <c r="Q47">
+        <v>4.852220666666666</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2134079313342049</v>
+      </c>
+      <c r="T47">
+        <v>1.939993002725631</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.368779198873643</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1355064977014307</v>
+      </c>
+      <c r="C48">
+        <v>27.83640103076035</v>
+      </c>
+      <c r="D48">
+        <v>44.15640103076035</v>
+      </c>
+      <c r="E48">
+        <v>-8.909999999999997</v>
+      </c>
+      <c r="F48">
+        <v>19.09</v>
+      </c>
+      <c r="G48">
+        <v>2.77</v>
+      </c>
+      <c r="H48">
+        <v>13.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K48">
+        <v>1.53</v>
+      </c>
+      <c r="L48">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M48">
+        <v>0.971681</v>
+      </c>
+      <c r="N48">
+        <v>4.131652333333333</v>
+      </c>
+      <c r="O48">
+        <v>0.8263304666666667</v>
+      </c>
+      <c r="P48">
+        <v>3.305321866666667</v>
+      </c>
+      <c r="Q48">
+        <v>4.835321866666666</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2162505512989457</v>
+      </c>
+      <c r="T48">
+        <v>1.971576120393123</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.252066607593782</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1353146331690487</v>
+      </c>
+      <c r="C49">
+        <v>27.50918095549569</v>
+      </c>
+      <c r="D49">
+        <v>44.24418095549569</v>
+      </c>
+      <c r="E49">
+        <v>-8.494999999999994</v>
+      </c>
+      <c r="F49">
+        <v>19.505</v>
+      </c>
+      <c r="G49">
+        <v>2.77</v>
+      </c>
+      <c r="H49">
+        <v>13.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K49">
+        <v>1.53</v>
+      </c>
+      <c r="L49">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M49">
+        <v>0.9928045000000002</v>
+      </c>
+      <c r="N49">
+        <v>4.110528833333333</v>
+      </c>
+      <c r="O49">
+        <v>0.8221057666666667</v>
+      </c>
+      <c r="P49">
+        <v>3.288423066666667</v>
+      </c>
+      <c r="Q49">
+        <v>4.818423066666666</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2192004399416013</v>
+      </c>
+      <c r="T49">
+        <v>2.004351053821651</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.140320509559871</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1351227686366667</v>
+      </c>
+      <c r="C50">
+        <v>27.18231057645449</v>
+      </c>
+      <c r="D50">
+        <v>44.33231057645448</v>
+      </c>
+      <c r="E50">
+        <v>-8.079999999999998</v>
+      </c>
+      <c r="F50">
+        <v>19.92</v>
+      </c>
+      <c r="G50">
+        <v>2.77</v>
+      </c>
+      <c r="H50">
+        <v>13.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K50">
+        <v>1.53</v>
+      </c>
+      <c r="L50">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M50">
+        <v>1.013928</v>
+      </c>
+      <c r="N50">
+        <v>4.089405333333334</v>
+      </c>
+      <c r="O50">
+        <v>0.8178810666666667</v>
+      </c>
+      <c r="P50">
+        <v>3.271524266666667</v>
+      </c>
+      <c r="Q50">
+        <v>4.801524266666666</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2222637858397436</v>
+      </c>
+      <c r="T50">
+        <v>2.038386561612815</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.033230498944041</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1349309041042847</v>
+      </c>
+      <c r="C51">
+        <v>26.85579198747854</v>
+      </c>
+      <c r="D51">
+        <v>44.42079198747854</v>
+      </c>
+      <c r="E51">
+        <v>-7.664999999999996</v>
+      </c>
+      <c r="F51">
+        <v>20.335</v>
+      </c>
+      <c r="G51">
+        <v>2.77</v>
+      </c>
+      <c r="H51">
+        <v>13.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K51">
+        <v>1.53</v>
+      </c>
+      <c r="L51">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M51">
+        <v>1.0350515</v>
+      </c>
+      <c r="N51">
+        <v>4.068281833333334</v>
+      </c>
+      <c r="O51">
+        <v>0.8136563666666667</v>
+      </c>
+      <c r="P51">
+        <v>3.254625466666667</v>
+      </c>
+      <c r="Q51">
+        <v>4.784625466666666</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2254472629495778</v>
+      </c>
+      <c r="T51">
+        <v>2.073756795199711</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.930511509169673</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1347390395719027</v>
+      </c>
+      <c r="C52">
+        <v>26.52962729915922</v>
+      </c>
+      <c r="D52">
+        <v>44.50962729915922</v>
+      </c>
+      <c r="E52">
+        <v>-7.249999999999996</v>
+      </c>
+      <c r="F52">
+        <v>20.75</v>
+      </c>
+      <c r="G52">
+        <v>2.77</v>
+      </c>
+      <c r="H52">
+        <v>13.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K52">
+        <v>1.53</v>
+      </c>
+      <c r="L52">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M52">
+        <v>1.056175</v>
+      </c>
+      <c r="N52">
+        <v>4.047158333333334</v>
+      </c>
+      <c r="O52">
+        <v>0.8094316666666668</v>
+      </c>
+      <c r="P52">
+        <v>3.237726666666667</v>
+      </c>
+      <c r="Q52">
+        <v>4.767726666666666</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2287580791438054</v>
+      </c>
+      <c r="T52">
+        <v>2.110541838130083</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.83190127898628</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1345471750395207</v>
+      </c>
+      <c r="C53">
+        <v>26.2038186390053</v>
+      </c>
+      <c r="D53">
+        <v>44.59881863900529</v>
+      </c>
+      <c r="E53">
+        <v>-6.834999999999997</v>
+      </c>
+      <c r="F53">
+        <v>21.165</v>
+      </c>
+      <c r="G53">
+        <v>2.77</v>
+      </c>
+      <c r="H53">
+        <v>13.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K53">
+        <v>1.53</v>
+      </c>
+      <c r="L53">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M53">
+        <v>1.0772985</v>
+      </c>
+      <c r="N53">
+        <v>4.026034833333334</v>
+      </c>
+      <c r="O53">
+        <v>0.8052069666666668</v>
+      </c>
+      <c r="P53">
+        <v>3.220827866666667</v>
+      </c>
+      <c r="Q53">
+        <v>4.750827866666667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2322040306928993</v>
+      </c>
+      <c r="T53">
+        <v>2.148828311384143</v>
+      </c>
+      <c r="U53">
+        <v>0.0509</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.737158116653216</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1343553105071387</v>
+      </c>
+      <c r="C54">
+        <v>25.87836815161269</v>
+      </c>
+      <c r="D54">
+        <v>44.68836815161269</v>
+      </c>
+      <c r="E54">
+        <v>-6.419999999999995</v>
+      </c>
+      <c r="F54">
+        <v>21.58</v>
+      </c>
+      <c r="G54">
+        <v>2.77</v>
+      </c>
+      <c r="H54">
+        <v>13.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K54">
+        <v>1.53</v>
+      </c>
+      <c r="L54">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M54">
+        <v>1.098422</v>
+      </c>
+      <c r="N54">
+        <v>4.004911333333333</v>
+      </c>
+      <c r="O54">
+        <v>0.8009822666666667</v>
+      </c>
+      <c r="P54">
+        <v>3.203929066666666</v>
+      </c>
+      <c r="Q54">
+        <v>4.733929066666667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2357935635565389</v>
+      </c>
+      <c r="T54">
+        <v>2.188710054357123</v>
+      </c>
+      <c r="U54">
+        <v>0.0509</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.646058922102192</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1341634459747567</v>
+      </c>
+      <c r="C55">
+        <v>25.55327799883648</v>
+      </c>
+      <c r="D55">
+        <v>44.77827799883648</v>
+      </c>
+      <c r="E55">
+        <v>-6.004999999999995</v>
+      </c>
+      <c r="F55">
+        <v>21.995</v>
+      </c>
+      <c r="G55">
+        <v>2.77</v>
+      </c>
+      <c r="H55">
+        <v>13.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K55">
+        <v>1.53</v>
+      </c>
+      <c r="L55">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M55">
+        <v>1.1195455</v>
+      </c>
+      <c r="N55">
+        <v>3.983787833333333</v>
+      </c>
+      <c r="O55">
+        <v>0.7967575666666667</v>
+      </c>
+      <c r="P55">
+        <v>3.187030266666667</v>
+      </c>
+      <c r="Q55">
+        <v>4.717030266666667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2395358424994823</v>
+      </c>
+      <c r="T55">
+        <v>2.230288892775761</v>
+      </c>
+      <c r="U55">
+        <v>0.0509</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.558397433005924</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1350947814423747</v>
+      </c>
+      <c r="C56">
+        <v>24.70519535557682</v>
+      </c>
+      <c r="D56">
+        <v>44.34519535557681</v>
+      </c>
+      <c r="E56">
+        <v>-5.589999999999996</v>
+      </c>
+      <c r="F56">
+        <v>22.41</v>
+      </c>
+      <c r="G56">
+        <v>2.77</v>
+      </c>
+      <c r="H56">
+        <v>13.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K56">
+        <v>1.53</v>
+      </c>
+      <c r="L56">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M56">
+        <v>1.198935</v>
+      </c>
+      <c r="N56">
+        <v>3.904398333333333</v>
+      </c>
+      <c r="O56">
+        <v>0.7808796666666667</v>
+      </c>
+      <c r="P56">
+        <v>3.123518666666667</v>
+      </c>
+      <c r="Q56">
+        <v>4.653518666666667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2434408292225536</v>
+      </c>
+      <c r="T56">
+        <v>2.273675506777819</v>
+      </c>
+      <c r="U56">
+        <v>0.0535</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.0428</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.256555470758075</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1349237169099926</v>
+      </c>
+      <c r="C57">
+        <v>24.3691133411765</v>
+      </c>
+      <c r="D57">
+        <v>44.4241133411765</v>
+      </c>
+      <c r="E57">
+        <v>-5.174999999999994</v>
+      </c>
+      <c r="F57">
+        <v>22.825</v>
+      </c>
+      <c r="G57">
+        <v>2.77</v>
+      </c>
+      <c r="H57">
+        <v>13.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K57">
+        <v>1.53</v>
+      </c>
+      <c r="L57">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M57">
+        <v>1.2211375</v>
+      </c>
+      <c r="N57">
+        <v>3.882195833333333</v>
+      </c>
+      <c r="O57">
+        <v>0.7764391666666667</v>
+      </c>
+      <c r="P57">
+        <v>3.105756666666667</v>
+      </c>
+      <c r="Q57">
+        <v>4.635756666666667</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2475193709110948</v>
+      </c>
+      <c r="T57">
+        <v>2.318990414735523</v>
+      </c>
+      <c r="U57">
+        <v>0.0535</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.0428</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.179163553107928</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1347526523776106</v>
+      </c>
+      <c r="C58">
+        <v>24.03331271698205</v>
+      </c>
+      <c r="D58">
+        <v>44.50331271698204</v>
+      </c>
+      <c r="E58">
+        <v>-4.759999999999994</v>
+      </c>
+      <c r="F58">
+        <v>23.24</v>
+      </c>
+      <c r="G58">
+        <v>2.77</v>
+      </c>
+      <c r="H58">
+        <v>13.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K58">
+        <v>1.53</v>
+      </c>
+      <c r="L58">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M58">
+        <v>1.24334</v>
+      </c>
+      <c r="N58">
+        <v>3.859993333333334</v>
+      </c>
+      <c r="O58">
+        <v>0.7719986666666667</v>
+      </c>
+      <c r="P58">
+        <v>3.087994666666667</v>
+      </c>
+      <c r="Q58">
+        <v>4.617994666666666</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.251783300858206</v>
+      </c>
+      <c r="T58">
+        <v>2.36636509123676</v>
+      </c>
+      <c r="U58">
+        <v>0.0535</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.0428</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.104535632516716</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1345815878452286</v>
+      </c>
+      <c r="C59">
+        <v>23.69779499067</v>
+      </c>
+      <c r="D59">
+        <v>44.58279499067</v>
+      </c>
+      <c r="E59">
+        <v>-4.344999999999995</v>
+      </c>
+      <c r="F59">
+        <v>23.655</v>
+      </c>
+      <c r="G59">
+        <v>2.77</v>
+      </c>
+      <c r="H59">
+        <v>13.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K59">
+        <v>1.53</v>
+      </c>
+      <c r="L59">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M59">
+        <v>1.2655425</v>
+      </c>
+      <c r="N59">
+        <v>3.837790833333333</v>
+      </c>
+      <c r="O59">
+        <v>0.7675581666666668</v>
+      </c>
+      <c r="P59">
+        <v>3.070232666666667</v>
+      </c>
+      <c r="Q59">
+        <v>4.600232666666667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2562455531284387</v>
+      </c>
+      <c r="T59">
+        <v>2.415943241063635</v>
+      </c>
+      <c r="U59">
+        <v>0.0535</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.0428</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.032526235455019</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1356633233128466</v>
+      </c>
+      <c r="C60">
+        <v>22.78491004374135</v>
+      </c>
+      <c r="D60">
+        <v>44.08491004374135</v>
+      </c>
+      <c r="E60">
+        <v>-3.93</v>
+      </c>
+      <c r="F60">
+        <v>24.07</v>
+      </c>
+      <c r="G60">
+        <v>2.77</v>
+      </c>
+      <c r="H60">
+        <v>13.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K60">
+        <v>1.53</v>
+      </c>
+      <c r="L60">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M60">
+        <v>1.352734</v>
+      </c>
+      <c r="N60">
+        <v>3.750599333333334</v>
+      </c>
+      <c r="O60">
+        <v>0.7501198666666667</v>
+      </c>
+      <c r="P60">
+        <v>3.000479466666667</v>
+      </c>
+      <c r="Q60">
+        <v>4.530479466666667</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2609202936020157</v>
+      </c>
+      <c r="T60">
+        <v>2.46788225516798</v>
+      </c>
+      <c r="U60">
+        <v>0.0562</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.04496</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.772606686409401</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1355138587804646</v>
+      </c>
+      <c r="C61">
+        <v>22.43804020158922</v>
+      </c>
+      <c r="D61">
+        <v>44.15304020158922</v>
+      </c>
+      <c r="E61">
+        <v>-3.514999999999997</v>
+      </c>
+      <c r="F61">
+        <v>24.485</v>
+      </c>
+      <c r="G61">
+        <v>2.77</v>
+      </c>
+      <c r="H61">
+        <v>13.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K61">
+        <v>1.53</v>
+      </c>
+      <c r="L61">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M61">
+        <v>1.376057</v>
+      </c>
+      <c r="N61">
+        <v>3.727276333333334</v>
+      </c>
+      <c r="O61">
+        <v>0.7454552666666667</v>
+      </c>
+      <c r="P61">
+        <v>2.981821066666667</v>
+      </c>
+      <c r="Q61">
+        <v>4.511821066666666</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2658230701962552</v>
+      </c>
+      <c r="T61">
+        <v>2.52235487971644</v>
+      </c>
+      <c r="U61">
+        <v>0.0562</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.04496</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.708664200199072</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1353643942480826</v>
+      </c>
+      <c r="C62">
+        <v>22.09138126620586</v>
+      </c>
+      <c r="D62">
+        <v>44.22138126620585</v>
+      </c>
+      <c r="E62">
+        <v>-3.099999999999998</v>
+      </c>
+      <c r="F62">
+        <v>24.9</v>
+      </c>
+      <c r="G62">
+        <v>2.77</v>
+      </c>
+      <c r="H62">
+        <v>13.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K62">
+        <v>1.53</v>
+      </c>
+      <c r="L62">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M62">
+        <v>1.39938</v>
+      </c>
+      <c r="N62">
+        <v>3.703953333333334</v>
+      </c>
+      <c r="O62">
+        <v>0.7407906666666668</v>
+      </c>
+      <c r="P62">
+        <v>2.963162666666667</v>
+      </c>
+      <c r="Q62">
+        <v>4.493162666666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2709709856202066</v>
+      </c>
+      <c r="T62">
+        <v>2.579551135492324</v>
+      </c>
+      <c r="U62">
+        <v>0.0562</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.04496</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.646853130195754</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1352149297157006</v>
+      </c>
+      <c r="C63">
+        <v>21.74493421844811</v>
+      </c>
+      <c r="D63">
+        <v>44.2899342184481</v>
+      </c>
+      <c r="E63">
+        <v>-2.684999999999999</v>
+      </c>
+      <c r="F63">
+        <v>25.315</v>
+      </c>
+      <c r="G63">
+        <v>2.77</v>
+      </c>
+      <c r="H63">
+        <v>13.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K63">
+        <v>1.53</v>
+      </c>
+      <c r="L63">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M63">
+        <v>1.422703</v>
+      </c>
+      <c r="N63">
+        <v>3.680630333333334</v>
+      </c>
+      <c r="O63">
+        <v>0.7361260666666668</v>
+      </c>
+      <c r="P63">
+        <v>2.944504266666667</v>
+      </c>
+      <c r="Q63">
+        <v>4.474504266666667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2763828967069246</v>
+      </c>
+      <c r="T63">
+        <v>2.639680532590046</v>
+      </c>
+      <c r="U63">
+        <v>0.0562</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.04496</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.587068652651561</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1350654651833186</v>
+      </c>
+      <c r="C64">
+        <v>21.39870004526445</v>
+      </c>
+      <c r="D64">
+        <v>44.35870004526445</v>
+      </c>
+      <c r="E64">
+        <v>-2.269999999999996</v>
+      </c>
+      <c r="F64">
+        <v>25.73</v>
+      </c>
+      <c r="G64">
+        <v>2.77</v>
+      </c>
+      <c r="H64">
+        <v>13.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K64">
+        <v>1.53</v>
+      </c>
+      <c r="L64">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M64">
+        <v>1.446026</v>
+      </c>
+      <c r="N64">
+        <v>3.657307333333334</v>
+      </c>
+      <c r="O64">
+        <v>0.7314614666666668</v>
+      </c>
+      <c r="P64">
+        <v>2.925845866666667</v>
+      </c>
+      <c r="Q64">
+        <v>4.455845866666667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2820796452192594</v>
+      </c>
+      <c r="T64">
+        <v>2.702974634798176</v>
+      </c>
+      <c r="U64">
+        <v>0.0562</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.04496</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.529212706641052</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1372848006509366</v>
+      </c>
+      <c r="C65">
+        <v>19.98408552955035</v>
+      </c>
+      <c r="D65">
+        <v>43.35908552955035</v>
+      </c>
+      <c r="E65">
+        <v>-1.854999999999997</v>
+      </c>
+      <c r="F65">
+        <v>26.145</v>
+      </c>
+      <c r="G65">
+        <v>2.77</v>
+      </c>
+      <c r="H65">
+        <v>13.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K65">
+        <v>1.53</v>
+      </c>
+      <c r="L65">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M65">
+        <v>1.5922305</v>
+      </c>
+      <c r="N65">
+        <v>3.511102833333333</v>
+      </c>
+      <c r="O65">
+        <v>0.7022205666666667</v>
+      </c>
+      <c r="P65">
+        <v>2.808882266666667</v>
+      </c>
+      <c r="Q65">
+        <v>4.338882266666666</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2880843260836125</v>
+      </c>
+      <c r="T65">
+        <v>2.769690039828367</v>
+      </c>
+      <c r="U65">
+        <v>0.0609</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.205147328438522</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1371729361185546</v>
+      </c>
+      <c r="C66">
+        <v>19.61839120262114</v>
+      </c>
+      <c r="D66">
+        <v>43.40839120262114</v>
+      </c>
+      <c r="E66">
+        <v>-1.439999999999994</v>
+      </c>
+      <c r="F66">
+        <v>26.56</v>
+      </c>
+      <c r="G66">
+        <v>2.77</v>
+      </c>
+      <c r="H66">
+        <v>13.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K66">
+        <v>1.53</v>
+      </c>
+      <c r="L66">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M66">
+        <v>1.617504</v>
+      </c>
+      <c r="N66">
+        <v>3.485829333333333</v>
+      </c>
+      <c r="O66">
+        <v>0.6971658666666667</v>
+      </c>
+      <c r="P66">
+        <v>2.788663466666667</v>
+      </c>
+      <c r="Q66">
+        <v>4.318663466666667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2944226003293183</v>
+      </c>
+      <c r="T66">
+        <v>2.840111856249124</v>
+      </c>
+      <c r="U66">
+        <v>0.0609</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.15506690143167</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1370610715861726</v>
+      </c>
+      <c r="C67">
+        <v>19.25280913899158</v>
+      </c>
+      <c r="D67">
+        <v>43.45780913899158</v>
+      </c>
+      <c r="E67">
+        <v>-1.024999999999995</v>
+      </c>
+      <c r="F67">
+        <v>26.975</v>
+      </c>
+      <c r="G67">
+        <v>2.77</v>
+      </c>
+      <c r="H67">
+        <v>13.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K67">
+        <v>1.53</v>
+      </c>
+      <c r="L67">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M67">
+        <v>1.6427775</v>
+      </c>
+      <c r="N67">
+        <v>3.460555833333333</v>
+      </c>
+      <c r="O67">
+        <v>0.6921111666666667</v>
+      </c>
+      <c r="P67">
+        <v>2.768444666666666</v>
+      </c>
+      <c r="Q67">
+        <v>4.298444666666667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3011230616747788</v>
+      </c>
+      <c r="T67">
+        <v>2.914557776465352</v>
+      </c>
+      <c r="U67">
+        <v>0.0609</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.106527410640414</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1369492070537906</v>
+      </c>
+      <c r="C68">
+        <v>18.88733972251443</v>
+      </c>
+      <c r="D68">
+        <v>43.50733972251443</v>
+      </c>
+      <c r="E68">
+        <v>-0.6099999999999959</v>
+      </c>
+      <c r="F68">
+        <v>27.39</v>
+      </c>
+      <c r="G68">
+        <v>2.77</v>
+      </c>
+      <c r="H68">
+        <v>13.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K68">
+        <v>1.53</v>
+      </c>
+      <c r="L68">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M68">
+        <v>1.668051</v>
+      </c>
+      <c r="N68">
+        <v>3.435282333333333</v>
+      </c>
+      <c r="O68">
+        <v>0.6870564666666668</v>
+      </c>
+      <c r="P68">
+        <v>2.748225866666667</v>
+      </c>
+      <c r="Q68">
+        <v>4.278225866666666</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3082176678052664</v>
+      </c>
+      <c r="T68">
+        <v>2.993382868459006</v>
+      </c>
+      <c r="U68">
+        <v>0.0609</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>3.059458813509499</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1368373425214086</v>
+      </c>
+      <c r="C69">
+        <v>18.52198333879444</v>
+      </c>
+      <c r="D69">
+        <v>43.55698333879444</v>
+      </c>
+      <c r="E69">
+        <v>-0.1949999999999932</v>
+      </c>
+      <c r="F69">
+        <v>27.805</v>
+      </c>
+      <c r="G69">
+        <v>2.77</v>
+      </c>
+      <c r="H69">
+        <v>13.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K69">
+        <v>1.53</v>
+      </c>
+      <c r="L69">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M69">
+        <v>1.6933245</v>
+      </c>
+      <c r="N69">
+        <v>3.410008833333333</v>
+      </c>
+      <c r="O69">
+        <v>0.6820017666666667</v>
+      </c>
+      <c r="P69">
+        <v>2.728007066666667</v>
+      </c>
+      <c r="Q69">
+        <v>4.258007066666666</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3157422500648745</v>
+      </c>
+      <c r="T69">
+        <v>3.076985238755306</v>
+      </c>
+      <c r="U69">
+        <v>0.0609</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>3.01379524912876</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1417846779890266</v>
+      </c>
+      <c r="C70">
+        <v>16.01452635643222</v>
+      </c>
+      <c r="D70">
+        <v>41.46452635643222</v>
+      </c>
+      <c r="E70">
+        <v>0.220000000000006</v>
+      </c>
+      <c r="F70">
+        <v>28.22</v>
+      </c>
+      <c r="G70">
+        <v>2.77</v>
+      </c>
+      <c r="H70">
+        <v>13.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K70">
+        <v>1.53</v>
+      </c>
+      <c r="L70">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M70">
+        <v>1.981044</v>
+      </c>
+      <c r="N70">
+        <v>3.122289333333334</v>
+      </c>
+      <c r="O70">
+        <v>0.6244578666666668</v>
+      </c>
+      <c r="P70">
+        <v>2.497831466666667</v>
+      </c>
+      <c r="Q70">
+        <v>4.027831466666667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.323737118715708</v>
+      </c>
+      <c r="T70">
+        <v>3.165812757195124</v>
+      </c>
+      <c r="U70">
+        <v>0.0702</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.05616</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.576082779248383</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1417472134566446</v>
+      </c>
+      <c r="C71">
+        <v>15.61461611979953</v>
+      </c>
+      <c r="D71">
+        <v>41.47961611979953</v>
+      </c>
+      <c r="E71">
+        <v>0.6350000000000051</v>
+      </c>
+      <c r="F71">
+        <v>28.635</v>
+      </c>
+      <c r="G71">
+        <v>2.77</v>
+      </c>
+      <c r="H71">
+        <v>13.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K71">
+        <v>1.53</v>
+      </c>
+      <c r="L71">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M71">
+        <v>2.010177</v>
+      </c>
+      <c r="N71">
+        <v>3.093156333333333</v>
+      </c>
+      <c r="O71">
+        <v>0.6186312666666667</v>
+      </c>
+      <c r="P71">
+        <v>2.474525066666667</v>
+      </c>
+      <c r="Q71">
+        <v>4.004525066666666</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3322477853440148</v>
+      </c>
+      <c r="T71">
+        <v>3.260371083276222</v>
+      </c>
+      <c r="U71">
+        <v>0.0702</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.05616</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.538748246215798</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1417097489242626</v>
+      </c>
+      <c r="C72">
+        <v>15.21471687009343</v>
+      </c>
+      <c r="D72">
+        <v>41.49471687009343</v>
+      </c>
+      <c r="E72">
+        <v>1.050000000000008</v>
+      </c>
+      <c r="F72">
+        <v>29.05</v>
+      </c>
+      <c r="G72">
+        <v>2.77</v>
+      </c>
+      <c r="H72">
+        <v>13.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K72">
+        <v>1.53</v>
+      </c>
+      <c r="L72">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M72">
+        <v>2.03931</v>
+      </c>
+      <c r="N72">
+        <v>3.064023333333333</v>
+      </c>
+      <c r="O72">
+        <v>0.6128046666666667</v>
+      </c>
+      <c r="P72">
+        <v>2.451218666666667</v>
+      </c>
+      <c r="Q72">
+        <v>3.981218666666666</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3413258297475419</v>
+      </c>
+      <c r="T72">
+        <v>3.361233297762725</v>
+      </c>
+      <c r="U72">
+        <v>0.0702</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.05616</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.502480414127</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1443418843918806</v>
+      </c>
+      <c r="C73">
+        <v>13.7648697416586</v>
+      </c>
+      <c r="D73">
+        <v>40.45986974165859</v>
+      </c>
+      <c r="E73">
+        <v>1.465000000000003</v>
+      </c>
+      <c r="F73">
+        <v>29.465</v>
+      </c>
+      <c r="G73">
+        <v>2.77</v>
+      </c>
+      <c r="H73">
+        <v>13.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K73">
+        <v>1.53</v>
+      </c>
+      <c r="L73">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M73">
+        <v>2.2069285</v>
+      </c>
+      <c r="N73">
+        <v>2.896404833333334</v>
+      </c>
+      <c r="O73">
+        <v>0.5792809666666668</v>
+      </c>
+      <c r="P73">
+        <v>2.317123866666667</v>
+      </c>
+      <c r="Q73">
+        <v>3.847123866666667</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3510299461788984</v>
+      </c>
+      <c r="T73">
+        <v>3.4690515270414</v>
+      </c>
+      <c r="U73">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.05992</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.312414440854488</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1443420198594985</v>
+      </c>
+      <c r="C74">
+        <v>13.34981780971541</v>
+      </c>
+      <c r="D74">
+        <v>40.45981780971541</v>
+      </c>
+      <c r="E74">
+        <v>1.880000000000003</v>
+      </c>
+      <c r="F74">
+        <v>29.88</v>
+      </c>
+      <c r="G74">
+        <v>2.77</v>
+      </c>
+      <c r="H74">
+        <v>13.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K74">
+        <v>1.53</v>
+      </c>
+      <c r="L74">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M74">
+        <v>2.238012</v>
+      </c>
+      <c r="N74">
+        <v>2.865321333333334</v>
+      </c>
+      <c r="O74">
+        <v>0.5730642666666668</v>
+      </c>
+      <c r="P74">
+        <v>2.292257066666667</v>
+      </c>
+      <c r="Q74">
+        <v>3.822257066666667</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3614272137839233</v>
+      </c>
+      <c r="T74">
+        <v>3.58457105841141</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.05992</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.280297573620398</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1443421553271165</v>
+      </c>
+      <c r="C75">
+        <v>12.93476587790557</v>
+      </c>
+      <c r="D75">
+        <v>40.45976587790556</v>
+      </c>
+      <c r="E75">
+        <v>2.295000000000002</v>
+      </c>
+      <c r="F75">
+        <v>30.295</v>
+      </c>
+      <c r="G75">
+        <v>2.77</v>
+      </c>
+      <c r="H75">
+        <v>13.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K75">
+        <v>1.53</v>
+      </c>
+      <c r="L75">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M75">
+        <v>2.2690955</v>
+      </c>
+      <c r="N75">
+        <v>2.834237833333334</v>
+      </c>
+      <c r="O75">
+        <v>0.5668475666666668</v>
+      </c>
+      <c r="P75">
+        <v>2.267390266666667</v>
+      </c>
+      <c r="Q75">
+        <v>3.797390266666667</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3725946493596908</v>
+      </c>
+      <c r="T75">
+        <v>3.708647592105124</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.05992</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.249060620557105</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1443422907947345</v>
+      </c>
+      <c r="C76">
+        <v>12.519713946229</v>
+      </c>
+      <c r="D76">
+        <v>40.459713946229</v>
+      </c>
+      <c r="E76">
+        <v>2.710000000000004</v>
+      </c>
+      <c r="F76">
+        <v>30.71</v>
+      </c>
+      <c r="G76">
+        <v>2.77</v>
+      </c>
+      <c r="H76">
+        <v>13.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K76">
+        <v>1.53</v>
+      </c>
+      <c r="L76">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M76">
+        <v>2.300179</v>
+      </c>
+      <c r="N76">
+        <v>2.803154333333334</v>
+      </c>
+      <c r="O76">
+        <v>0.5606308666666667</v>
+      </c>
+      <c r="P76">
+        <v>2.242523466666667</v>
+      </c>
+      <c r="Q76">
+        <v>3.772523466666667</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3846211184412867</v>
+      </c>
+      <c r="T76">
+        <v>3.842268474544509</v>
+      </c>
+      <c r="U76">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.05992</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.218667909468495</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1443424262623525</v>
+      </c>
+      <c r="C77">
+        <v>12.10466201468576</v>
+      </c>
+      <c r="D77">
+        <v>40.45966201468576</v>
+      </c>
+      <c r="E77">
+        <v>3.125000000000004</v>
+      </c>
+      <c r="F77">
+        <v>31.125</v>
+      </c>
+      <c r="G77">
+        <v>2.77</v>
+      </c>
+      <c r="H77">
+        <v>13.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K77">
+        <v>1.53</v>
+      </c>
+      <c r="L77">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M77">
+        <v>2.3312625</v>
+      </c>
+      <c r="N77">
+        <v>2.772070833333334</v>
+      </c>
+      <c r="O77">
+        <v>0.5544141666666668</v>
+      </c>
+      <c r="P77">
+        <v>2.217656666666667</v>
+      </c>
+      <c r="Q77">
+        <v>3.747656666666667</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3976097050494101</v>
+      </c>
+      <c r="T77">
+        <v>3.986579027579045</v>
+      </c>
+      <c r="U77">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V77">
+        <v>0.2</v>
+      </c>
+      <c r="W77">
+        <v>0.05992</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.189085670675582</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1443425617299705</v>
+      </c>
+      <c r="C78">
+        <v>11.68961008327582</v>
+      </c>
+      <c r="D78">
+        <v>40.45961008327582</v>
+      </c>
+      <c r="E78">
+        <v>3.540000000000003</v>
+      </c>
+      <c r="F78">
+        <v>31.54</v>
+      </c>
+      <c r="G78">
+        <v>2.77</v>
+      </c>
+      <c r="H78">
+        <v>13.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K78">
+        <v>1.53</v>
+      </c>
+      <c r="L78">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M78">
+        <v>2.362346</v>
+      </c>
+      <c r="N78">
+        <v>2.740987333333334</v>
+      </c>
+      <c r="O78">
+        <v>0.5481974666666668</v>
+      </c>
+      <c r="P78">
+        <v>2.192789866666667</v>
+      </c>
+      <c r="Q78">
+        <v>3.722789866666667</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4116806738748772</v>
+      </c>
+      <c r="T78">
+        <v>4.142915460033126</v>
+      </c>
+      <c r="U78">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V78">
+        <v>0.2</v>
+      </c>
+      <c r="W78">
+        <v>0.05992</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.160281911850904</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1443426971975885</v>
+      </c>
+      <c r="C79">
+        <v>11.27455815199922</v>
+      </c>
+      <c r="D79">
+        <v>40.45955815199922</v>
+      </c>
+      <c r="E79">
+        <v>3.955000000000005</v>
+      </c>
+      <c r="F79">
+        <v>31.955</v>
+      </c>
+      <c r="G79">
+        <v>2.77</v>
+      </c>
+      <c r="H79">
+        <v>13.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K79">
+        <v>1.53</v>
+      </c>
+      <c r="L79">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M79">
+        <v>2.3934295</v>
+      </c>
+      <c r="N79">
+        <v>2.709903833333334</v>
+      </c>
+      <c r="O79">
+        <v>0.5419807666666667</v>
+      </c>
+      <c r="P79">
+        <v>2.167923066666667</v>
+      </c>
+      <c r="Q79">
+        <v>3.697923066666667</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4269752052069066</v>
+      </c>
+      <c r="T79">
+        <v>4.312846364874517</v>
+      </c>
+      <c r="U79">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V79">
+        <v>0.2</v>
+      </c>
+      <c r="W79">
+        <v>0.05992</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.132226302606086</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1443428326652065</v>
+      </c>
+      <c r="C80">
+        <v>10.85950622085591</v>
+      </c>
+      <c r="D80">
+        <v>40.45950622085591</v>
+      </c>
+      <c r="E80">
+        <v>4.370000000000008</v>
+      </c>
+      <c r="F80">
+        <v>32.37</v>
+      </c>
+      <c r="G80">
+        <v>2.77</v>
+      </c>
+      <c r="H80">
+        <v>13.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K80">
+        <v>1.53</v>
+      </c>
+      <c r="L80">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M80">
+        <v>2.424513</v>
+      </c>
+      <c r="N80">
+        <v>2.678820333333333</v>
+      </c>
+      <c r="O80">
+        <v>0.5357640666666666</v>
+      </c>
+      <c r="P80">
+        <v>2.143056266666667</v>
+      </c>
+      <c r="Q80">
+        <v>3.673056266666666</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4436601484782114</v>
+      </c>
+      <c r="T80">
+        <v>4.498225533792398</v>
+      </c>
+      <c r="U80">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V80">
+        <v>0.2</v>
+      </c>
+      <c r="W80">
+        <v>0.05992</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.10489006795729</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1443429681328245</v>
+      </c>
+      <c r="C81">
+        <v>10.44445428984591</v>
+      </c>
+      <c r="D81">
+        <v>40.45945428984591</v>
+      </c>
+      <c r="E81">
+        <v>4.785000000000007</v>
+      </c>
+      <c r="F81">
+        <v>32.785</v>
+      </c>
+      <c r="G81">
+        <v>2.77</v>
+      </c>
+      <c r="H81">
+        <v>13.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K81">
+        <v>1.53</v>
+      </c>
+      <c r="L81">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M81">
+        <v>2.4555965</v>
+      </c>
+      <c r="N81">
+        <v>2.647736833333334</v>
+      </c>
+      <c r="O81">
+        <v>0.5295473666666667</v>
+      </c>
+      <c r="P81">
+        <v>2.118189466666667</v>
+      </c>
+      <c r="Q81">
+        <v>3.648189466666667</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4619341339658311</v>
+      </c>
+      <c r="T81">
+        <v>4.701259861654841</v>
+      </c>
+      <c r="U81">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V81">
+        <v>0.2</v>
+      </c>
+      <c r="W81">
+        <v>0.05992</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.078245889881881</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1443431036004425</v>
+      </c>
+      <c r="C82">
+        <v>10.02940235896923</v>
+      </c>
+      <c r="D82">
+        <v>40.45940235896923</v>
+      </c>
+      <c r="E82">
+        <v>5.200000000000006</v>
+      </c>
+      <c r="F82">
+        <v>33.2</v>
+      </c>
+      <c r="G82">
+        <v>2.77</v>
+      </c>
+      <c r="H82">
+        <v>13.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K82">
+        <v>1.53</v>
+      </c>
+      <c r="L82">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M82">
+        <v>2.48668</v>
+      </c>
+      <c r="N82">
+        <v>2.616653333333333</v>
+      </c>
+      <c r="O82">
+        <v>0.5233306666666667</v>
+      </c>
+      <c r="P82">
+        <v>2.093322666666666</v>
+      </c>
+      <c r="Q82">
+        <v>3.623322666666666</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4820355180022126</v>
+      </c>
+      <c r="T82">
+        <v>4.924597622303527</v>
+      </c>
+      <c r="U82">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V82">
+        <v>0.2</v>
+      </c>
+      <c r="W82">
+        <v>0.05992</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.052267816258357</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1443432390680605</v>
+      </c>
+      <c r="C83">
+        <v>9.614350428225848</v>
+      </c>
+      <c r="D83">
+        <v>40.45935042822585</v>
+      </c>
+      <c r="E83">
+        <v>5.615000000000006</v>
+      </c>
+      <c r="F83">
+        <v>33.615</v>
+      </c>
+      <c r="G83">
+        <v>2.77</v>
+      </c>
+      <c r="H83">
+        <v>13.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K83">
+        <v>1.53</v>
+      </c>
+      <c r="L83">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M83">
+        <v>2.5177635</v>
+      </c>
+      <c r="N83">
+        <v>2.585569833333333</v>
+      </c>
+      <c r="O83">
+        <v>0.5171139666666668</v>
+      </c>
+      <c r="P83">
+        <v>2.068455866666667</v>
+      </c>
+      <c r="Q83">
+        <v>3.598455866666666</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5042528372003185</v>
+      </c>
+      <c r="T83">
+        <v>5.171444620915234</v>
+      </c>
+      <c r="U83">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V83">
+        <v>0.2</v>
+      </c>
+      <c r="W83">
+        <v>0.05992</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.026931176551464</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1443433745356785</v>
+      </c>
+      <c r="C84">
+        <v>9.199298497615793</v>
+      </c>
+      <c r="D84">
+        <v>40.45929849761579</v>
+      </c>
+      <c r="E84">
+        <v>6.030000000000005</v>
+      </c>
+      <c r="F84">
+        <v>34.03</v>
+      </c>
+      <c r="G84">
+        <v>2.77</v>
+      </c>
+      <c r="H84">
+        <v>13.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K84">
+        <v>1.53</v>
+      </c>
+      <c r="L84">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M84">
+        <v>2.548847</v>
+      </c>
+      <c r="N84">
+        <v>2.554486333333334</v>
+      </c>
+      <c r="O84">
+        <v>0.5108972666666668</v>
+      </c>
+      <c r="P84">
+        <v>2.043589066666667</v>
+      </c>
+      <c r="Q84">
+        <v>3.573589066666667</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5289387474204361</v>
+      </c>
+      <c r="T84">
+        <v>5.445719063817128</v>
+      </c>
+      <c r="U84">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V84">
+        <v>0.2</v>
+      </c>
+      <c r="W84">
+        <v>0.05992</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.002212503666691</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1551667100032965</v>
+      </c>
+      <c r="C85">
+        <v>5.021155581469209</v>
+      </c>
+      <c r="D85">
+        <v>36.69615558146921</v>
+      </c>
+      <c r="E85">
+        <v>6.445000000000004</v>
+      </c>
+      <c r="F85">
+        <v>34.445</v>
+      </c>
+      <c r="G85">
+        <v>2.77</v>
+      </c>
+      <c r="H85">
+        <v>13.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K85">
+        <v>1.53</v>
+      </c>
+      <c r="L85">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M85">
+        <v>3.141384</v>
+      </c>
+      <c r="N85">
+        <v>1.961949333333334</v>
+      </c>
+      <c r="O85">
+        <v>0.3923898666666668</v>
+      </c>
+      <c r="P85">
+        <v>1.569559466666667</v>
+      </c>
+      <c r="Q85">
+        <v>3.099559466666666</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5565288823723324</v>
+      </c>
+      <c r="T85">
+        <v>5.752261088236894</v>
+      </c>
+      <c r="U85">
+        <v>0.0912</v>
+      </c>
+      <c r="V85">
+        <v>0.2</v>
+      </c>
+      <c r="W85">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.624549349373822</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1552972454709145</v>
+      </c>
+      <c r="C86">
+        <v>4.56503744336004</v>
+      </c>
+      <c r="D86">
+        <v>36.65503744336004</v>
+      </c>
+      <c r="E86">
+        <v>6.860000000000003</v>
+      </c>
+      <c r="F86">
+        <v>34.86</v>
+      </c>
+      <c r="G86">
+        <v>2.77</v>
+      </c>
+      <c r="H86">
+        <v>13.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K86">
+        <v>1.53</v>
+      </c>
+      <c r="L86">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M86">
+        <v>3.179232</v>
+      </c>
+      <c r="N86">
+        <v>1.924101333333333</v>
+      </c>
+      <c r="O86">
+        <v>0.3848202666666667</v>
+      </c>
+      <c r="P86">
+        <v>1.539281066666667</v>
+      </c>
+      <c r="Q86">
+        <v>3.069281066666666</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5875677841932154</v>
+      </c>
+      <c r="T86">
+        <v>6.097120865709127</v>
+      </c>
+      <c r="U86">
+        <v>0.0912</v>
+      </c>
+      <c r="V86">
+        <v>0.2</v>
+      </c>
+      <c r="W86">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.60520947616699</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1554277809385325</v>
+      </c>
+      <c r="C87">
+        <v>4.109011348078816</v>
+      </c>
+      <c r="D87">
+        <v>36.61401134807881</v>
+      </c>
+      <c r="E87">
+        <v>7.275000000000002</v>
+      </c>
+      <c r="F87">
+        <v>35.275</v>
+      </c>
+      <c r="G87">
+        <v>2.77</v>
+      </c>
+      <c r="H87">
+        <v>13.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K87">
+        <v>1.53</v>
+      </c>
+      <c r="L87">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M87">
+        <v>3.21708</v>
+      </c>
+      <c r="N87">
+        <v>1.886253333333333</v>
+      </c>
+      <c r="O87">
+        <v>0.3772506666666667</v>
+      </c>
+      <c r="P87">
+        <v>1.509002666666667</v>
+      </c>
+      <c r="Q87">
+        <v>3.039002666666667</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.622745206256883</v>
+      </c>
+      <c r="T87">
+        <v>6.487961946844328</v>
+      </c>
+      <c r="U87">
+        <v>0.0912</v>
+      </c>
+      <c r="V87">
+        <v>0.2</v>
+      </c>
+      <c r="W87">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.58632465880032</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1555583164061505</v>
+      </c>
+      <c r="C88">
+        <v>3.65307698691462</v>
+      </c>
+      <c r="D88">
+        <v>36.57307698691461</v>
+      </c>
+      <c r="E88">
+        <v>7.690000000000001</v>
+      </c>
+      <c r="F88">
+        <v>35.69</v>
+      </c>
+      <c r="G88">
+        <v>2.77</v>
+      </c>
+      <c r="H88">
+        <v>13.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K88">
+        <v>1.53</v>
+      </c>
+      <c r="L88">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M88">
+        <v>3.254928</v>
+      </c>
+      <c r="N88">
+        <v>1.848405333333333</v>
+      </c>
+      <c r="O88">
+        <v>0.3696810666666667</v>
+      </c>
+      <c r="P88">
+        <v>1.478724266666667</v>
+      </c>
+      <c r="Q88">
+        <v>3.008724266666666</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.662947974329646</v>
+      </c>
+      <c r="T88">
+        <v>6.9346374681417</v>
+      </c>
+      <c r="U88">
+        <v>0.0912</v>
+      </c>
+      <c r="V88">
+        <v>0.2</v>
+      </c>
+      <c r="W88">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.567879023232874</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1556888518737685</v>
+      </c>
+      <c r="C89">
+        <v>3.197234052535634</v>
+      </c>
+      <c r="D89">
+        <v>36.53223405253563</v>
+      </c>
+      <c r="E89">
+        <v>8.105</v>
+      </c>
+      <c r="F89">
+        <v>36.105</v>
+      </c>
+      <c r="G89">
+        <v>2.77</v>
+      </c>
+      <c r="H89">
+        <v>13.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K89">
+        <v>1.53</v>
+      </c>
+      <c r="L89">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M89">
+        <v>3.292776</v>
+      </c>
+      <c r="N89">
+        <v>1.810557333333334</v>
+      </c>
+      <c r="O89">
+        <v>0.3621114666666667</v>
+      </c>
+      <c r="P89">
+        <v>1.448445866666667</v>
+      </c>
+      <c r="Q89">
+        <v>2.978445866666667</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7093357836443726</v>
+      </c>
+      <c r="T89">
+        <v>7.450032300407898</v>
+      </c>
+      <c r="U89">
+        <v>0.0912</v>
+      </c>
+      <c r="V89">
+        <v>0.2</v>
+      </c>
+      <c r="W89">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.549857425264681</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1558193873413865</v>
+      </c>
+      <c r="C90">
+        <v>2.741482238981298</v>
+      </c>
+      <c r="D90">
+        <v>36.4914822389813</v>
+      </c>
+      <c r="E90">
+        <v>8.520000000000007</v>
+      </c>
+      <c r="F90">
+        <v>36.52</v>
+      </c>
+      <c r="G90">
+        <v>2.77</v>
+      </c>
+      <c r="H90">
+        <v>13.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K90">
+        <v>1.53</v>
+      </c>
+      <c r="L90">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M90">
+        <v>3.330624</v>
+      </c>
+      <c r="N90">
+        <v>1.772709333333333</v>
+      </c>
+      <c r="O90">
+        <v>0.3545418666666666</v>
+      </c>
+      <c r="P90">
+        <v>1.418167466666667</v>
+      </c>
+      <c r="Q90">
+        <v>2.948167466666666</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7634548945115538</v>
+      </c>
+      <c r="T90">
+        <v>8.051326271385131</v>
+      </c>
+      <c r="U90">
+        <v>0.0912</v>
+      </c>
+      <c r="V90">
+        <v>0.2</v>
+      </c>
+      <c r="W90">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.532245409068491</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1559499228090045</v>
+      </c>
+      <c r="C91">
+        <v>2.285821241654773</v>
+      </c>
+      <c r="D91">
+        <v>36.45082124165477</v>
+      </c>
+      <c r="E91">
+        <v>8.935000000000006</v>
+      </c>
+      <c r="F91">
+        <v>36.935</v>
+      </c>
+      <c r="G91">
+        <v>2.77</v>
+      </c>
+      <c r="H91">
+        <v>13.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K91">
+        <v>1.53</v>
+      </c>
+      <c r="L91">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M91">
+        <v>3.368472</v>
+      </c>
+      <c r="N91">
+        <v>1.734861333333333</v>
+      </c>
+      <c r="O91">
+        <v>0.3469722666666667</v>
+      </c>
+      <c r="P91">
+        <v>1.387889066666667</v>
+      </c>
+      <c r="Q91">
+        <v>2.917889066666667</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8274138437182224</v>
+      </c>
+      <c r="T91">
+        <v>8.761946418903678</v>
+      </c>
+      <c r="U91">
+        <v>0.0912</v>
+      </c>
+      <c r="V91">
+        <v>0.2</v>
+      </c>
+      <c r="W91">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>1.51502916851716</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2091838120897011</v>
+      </c>
+      <c r="C92">
+        <v>-9.517696002854073</v>
+      </c>
+      <c r="D92">
+        <v>25.06230399714593</v>
+      </c>
+      <c r="E92">
+        <v>9.350000000000005</v>
+      </c>
+      <c r="F92">
+        <v>37.35</v>
+      </c>
+      <c r="G92">
+        <v>2.77</v>
+      </c>
+      <c r="H92">
+        <v>13.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K92">
+        <v>1.53</v>
+      </c>
+      <c r="L92">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M92">
+        <v>5.849010000000001</v>
+      </c>
+      <c r="N92">
+        <v>-0.7456766666666672</v>
+      </c>
+      <c r="O92">
+        <v>-0.1491353333333335</v>
+      </c>
+      <c r="P92">
+        <v>-0.5965413333333338</v>
+      </c>
+      <c r="Q92">
+        <v>0.933458666666666</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9283818959974131</v>
+      </c>
+      <c r="T92">
+        <v>9.883758660900583</v>
+      </c>
+      <c r="U92">
+        <v>0.1566</v>
+      </c>
+      <c r="V92">
+        <v>0.1745024656594307</v>
+      </c>
+      <c r="W92">
+        <v>0.1292729138777332</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8725123282971533</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2103618120897011</v>
+      </c>
+      <c r="C93">
+        <v>-10.10478205014531</v>
+      </c>
+      <c r="D93">
+        <v>24.89021794985469</v>
+      </c>
+      <c r="E93">
+        <v>9.765000000000004</v>
+      </c>
+      <c r="F93">
+        <v>37.765</v>
+      </c>
+      <c r="G93">
+        <v>2.77</v>
+      </c>
+      <c r="H93">
+        <v>13.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K93">
+        <v>1.53</v>
+      </c>
+      <c r="L93">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M93">
+        <v>5.913999</v>
+      </c>
+      <c r="N93">
+        <v>-0.810665666666667</v>
+      </c>
+      <c r="O93">
+        <v>-0.1621331333333334</v>
+      </c>
+      <c r="P93">
+        <v>-0.6485325333333336</v>
+      </c>
+      <c r="Q93">
+        <v>0.8814674666666662</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.027224328886015</v>
+      </c>
+      <c r="T93">
+        <v>10.98195406766732</v>
+      </c>
+      <c r="U93">
+        <v>0.1566</v>
+      </c>
+      <c r="V93">
+        <v>0.1725848561466897</v>
+      </c>
+      <c r="W93">
+        <v>0.1295732115274284</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.8629242807334484</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2115398120897012</v>
+      </c>
+      <c r="C94">
+        <v>-10.68952101414108</v>
+      </c>
+      <c r="D94">
+        <v>24.72047898585892</v>
+      </c>
+      <c r="E94">
+        <v>10.18</v>
+      </c>
+      <c r="F94">
+        <v>38.18</v>
+      </c>
+      <c r="G94">
+        <v>2.77</v>
+      </c>
+      <c r="H94">
+        <v>13.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K94">
+        <v>1.53</v>
+      </c>
+      <c r="L94">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M94">
+        <v>5.978988</v>
+      </c>
+      <c r="N94">
+        <v>-0.8756546666666667</v>
+      </c>
+      <c r="O94">
+        <v>-0.1751309333333333</v>
+      </c>
+      <c r="P94">
+        <v>-0.7005237333333334</v>
+      </c>
+      <c r="Q94">
+        <v>0.8294762666666664</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.150777369996767</v>
+      </c>
+      <c r="T94">
+        <v>12.35469832612574</v>
+      </c>
+      <c r="U94">
+        <v>0.1566</v>
+      </c>
+      <c r="V94">
+        <v>0.1707089337972691</v>
+      </c>
+      <c r="W94">
+        <v>0.1298669809673477</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.8535446689863457</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2127178120897012</v>
+      </c>
+      <c r="C95">
+        <v>-11.27196058743977</v>
+      </c>
+      <c r="D95">
+        <v>24.55303941256023</v>
+      </c>
+      <c r="E95">
+        <v>10.595</v>
+      </c>
+      <c r="F95">
+        <v>38.595</v>
+      </c>
+      <c r="G95">
+        <v>2.77</v>
+      </c>
+      <c r="H95">
+        <v>13.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K95">
+        <v>1.53</v>
+      </c>
+      <c r="L95">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M95">
+        <v>6.043977000000001</v>
+      </c>
+      <c r="N95">
+        <v>-0.9406436666666673</v>
+      </c>
+      <c r="O95">
+        <v>-0.1881287333333335</v>
+      </c>
+      <c r="P95">
+        <v>-0.7525149333333339</v>
+      </c>
+      <c r="Q95">
+        <v>0.7774850666666659</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.309631279996305</v>
+      </c>
+      <c r="T95">
+        <v>14.11965522985798</v>
+      </c>
+      <c r="U95">
+        <v>0.1566</v>
+      </c>
+      <c r="V95">
+        <v>0.1688733538639652</v>
+      </c>
+      <c r="W95">
+        <v>0.1301544327849031</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8443667693198258</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2138958120897012</v>
+      </c>
+      <c r="C96">
+        <v>-11.8521471791852</v>
+      </c>
+      <c r="D96">
+        <v>24.3878528208148</v>
+      </c>
+      <c r="E96">
+        <v>11.01000000000001</v>
+      </c>
+      <c r="F96">
+        <v>39.01000000000001</v>
+      </c>
+      <c r="G96">
+        <v>2.77</v>
+      </c>
+      <c r="H96">
+        <v>13.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K96">
+        <v>1.53</v>
+      </c>
+      <c r="L96">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M96">
+        <v>6.108966000000001</v>
+      </c>
+      <c r="N96">
+        <v>-1.005632666666668</v>
+      </c>
+      <c r="O96">
+        <v>-0.2011265333333336</v>
+      </c>
+      <c r="P96">
+        <v>-0.8045061333333343</v>
+      </c>
+      <c r="Q96">
+        <v>0.7254938666666655</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.521436493329023</v>
+      </c>
+      <c r="T96">
+        <v>16.47293110150099</v>
+      </c>
+      <c r="U96">
+        <v>0.1566</v>
+      </c>
+      <c r="V96">
+        <v>0.1670768288228591</v>
+      </c>
+      <c r="W96">
+        <v>0.1304357686063403</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8353841441142956</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2150738120897012</v>
+      </c>
+      <c r="C97">
+        <v>-12.43012595795184</v>
+      </c>
+      <c r="D97">
+        <v>24.22487404204816</v>
+      </c>
+      <c r="E97">
+        <v>11.42500000000001</v>
+      </c>
+      <c r="F97">
+        <v>39.425</v>
+      </c>
+      <c r="G97">
+        <v>2.77</v>
+      </c>
+      <c r="H97">
+        <v>13.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K97">
+        <v>1.53</v>
+      </c>
+      <c r="L97">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M97">
+        <v>6.173955000000001</v>
+      </c>
+      <c r="N97">
+        <v>-1.070621666666668</v>
+      </c>
+      <c r="O97">
+        <v>-0.2141243333333336</v>
+      </c>
+      <c r="P97">
+        <v>-0.8564973333333341</v>
+      </c>
+      <c r="Q97">
+        <v>0.6735026666666657</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.817963791994829</v>
+      </c>
+      <c r="T97">
+        <v>19.76751732180119</v>
+      </c>
+      <c r="U97">
+        <v>0.1566</v>
+      </c>
+      <c r="V97">
+        <v>0.1653181253615659</v>
+      </c>
+      <c r="W97">
+        <v>0.1307111815683788</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8265906268078295</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2162518120897012</v>
+      </c>
+      <c r="C98">
+        <v>-13.00594089292194</v>
+      </c>
+      <c r="D98">
+        <v>24.06405910707806</v>
+      </c>
+      <c r="E98">
+        <v>11.84</v>
+      </c>
+      <c r="F98">
+        <v>39.84</v>
+      </c>
+      <c r="G98">
+        <v>2.77</v>
+      </c>
+      <c r="H98">
+        <v>13.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K98">
+        <v>1.53</v>
+      </c>
+      <c r="L98">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M98">
+        <v>6.238944</v>
+      </c>
+      <c r="N98">
+        <v>-1.135610666666667</v>
+      </c>
+      <c r="O98">
+        <v>-0.2271221333333333</v>
+      </c>
+      <c r="P98">
+        <v>-0.9084885333333332</v>
+      </c>
+      <c r="Q98">
+        <v>0.6215114666666666</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.262754739993531</v>
+      </c>
+      <c r="T98">
+        <v>24.70939665225144</v>
+      </c>
+      <c r="U98">
+        <v>0.1566</v>
+      </c>
+      <c r="V98">
+        <v>0.1635960615557163</v>
+      </c>
+      <c r="W98">
+        <v>0.1309808567603749</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.8179803077785813</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2174298120897012</v>
+      </c>
+      <c r="C99">
+        <v>-13.57963479343337</v>
+      </c>
+      <c r="D99">
+        <v>23.90536520656663</v>
+      </c>
+      <c r="E99">
+        <v>12.255</v>
+      </c>
+      <c r="F99">
+        <v>40.255</v>
+      </c>
+      <c r="G99">
+        <v>2.77</v>
+      </c>
+      <c r="H99">
+        <v>13.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K99">
+        <v>1.53</v>
+      </c>
+      <c r="L99">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M99">
+        <v>6.303933</v>
+      </c>
+      <c r="N99">
+        <v>-1.200599666666666</v>
+      </c>
+      <c r="O99">
+        <v>-0.2401199333333333</v>
+      </c>
+      <c r="P99">
+        <v>-0.960479733333333</v>
+      </c>
+      <c r="Q99">
+        <v>0.5695202666666668</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.004072986658042</v>
+      </c>
+      <c r="T99">
+        <v>32.94586220300192</v>
+      </c>
+      <c r="U99">
+        <v>0.1566</v>
+      </c>
+      <c r="V99">
+        <v>0.1619095042200903</v>
+      </c>
+      <c r="W99">
+        <v>0.1312449716391339</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8095475211004517</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2186078120897011</v>
+      </c>
+      <c r="C100">
+        <v>-14.15124934697283</v>
+      </c>
+      <c r="D100">
+        <v>23.74875065302717</v>
+      </c>
+      <c r="E100">
+        <v>12.67000000000001</v>
+      </c>
+      <c r="F100">
+        <v>40.67</v>
+      </c>
+      <c r="G100">
+        <v>2.77</v>
+      </c>
+      <c r="H100">
+        <v>13.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K100">
+        <v>1.53</v>
+      </c>
+      <c r="L100">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M100">
+        <v>6.368922000000001</v>
+      </c>
+      <c r="N100">
+        <v>-1.265588666666668</v>
+      </c>
+      <c r="O100">
+        <v>-0.2531177333333336</v>
+      </c>
+      <c r="P100">
+        <v>-1.012470933333334</v>
+      </c>
+      <c r="Q100">
+        <v>0.5175290666666656</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.486709479987062</v>
+      </c>
+      <c r="T100">
+        <v>49.41879330450287</v>
+      </c>
+      <c r="U100">
+        <v>0.1566</v>
+      </c>
+      <c r="V100">
+        <v>0.1602573664219261</v>
+      </c>
+      <c r="W100">
+        <v>0.1315036964183264</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8012868321096306</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2756073312375166</v>
+      </c>
+      <c r="C101">
+        <v>-20.28257307947668</v>
+      </c>
+      <c r="D101">
+        <v>18.03242692052332</v>
+      </c>
+      <c r="E101">
+        <v>13.085</v>
+      </c>
+      <c r="F101">
+        <v>41.085</v>
+      </c>
+      <c r="G101">
+        <v>2.77</v>
+      </c>
+      <c r="H101">
+        <v>13.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="K101">
+        <v>1.53</v>
+      </c>
+      <c r="L101">
+        <v>5.103333333333333</v>
+      </c>
+      <c r="M101">
+        <v>8.578548000000001</v>
+      </c>
+      <c r="N101">
+        <v>-3.475214666666668</v>
+      </c>
+      <c r="O101">
+        <v>-0.6950429333333337</v>
+      </c>
+      <c r="P101">
+        <v>-2.780171733333334</v>
+      </c>
+      <c r="Q101">
+        <v>-1.250171733333334</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.348970874755667</v>
+      </c>
+      <c r="T101">
+        <v>103.4412710418943</v>
+      </c>
+      <c r="U101">
+        <v>0.2088</v>
+      </c>
+      <c r="V101">
+        <v>0.1189789538587027</v>
+      </c>
+      <c r="W101">
+        <v>0.1839571944343029</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5948947692935136</v>
+      </c>
+      <c r="Z101">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/vietnam/vietnam_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_telecom_equipment.xlsx
@@ -1483,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1620,22 +1620,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1436754977896528</v>
+        <v>0.1434241467940735</v>
       </c>
       <c r="C2">
-        <v>40.74923745846493</v>
+        <v>40.44949355722428</v>
       </c>
       <c r="D2">
-        <v>38.93923745846492</v>
+        <v>39.03949355722428</v>
       </c>
       <c r="E2">
-        <v>-28.4</v>
+        <v>-28</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G2">
         <v>1.81</v>
@@ -1656,28 +1656,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02012</v>
       </c>
       <c r="N2">
-        <v>3.993333333333333</v>
+        <v>3.973213333333333</v>
       </c>
       <c r="O2">
-        <v>0.7986666666666666</v>
+        <v>0.7946426666666667</v>
       </c>
       <c r="P2">
-        <v>3.194666666666667</v>
+        <v>3.178570666666666</v>
       </c>
       <c r="Q2">
-        <v>4.284666666666666</v>
+        <v>4.268570666666666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1436754977896528</v>
+        <v>0.1444664109031045</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181998178705849</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>198.4758117958913</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1702,22 +1702,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1434241467940735</v>
+        <v>0.1431727957984942</v>
       </c>
       <c r="C3">
-        <v>40.44949355722428</v>
+        <v>40.15026724346851</v>
       </c>
       <c r="D3">
-        <v>39.03949355722428</v>
+        <v>39.14026724346851</v>
       </c>
       <c r="E3">
-        <v>-28</v>
+        <v>-27.6</v>
       </c>
       <c r="F3">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G3">
         <v>1.81</v>
@@ -1738,28 +1738,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M3">
-        <v>0.02012</v>
+        <v>0.04024</v>
       </c>
       <c r="N3">
-        <v>3.973213333333333</v>
+        <v>3.953093333333333</v>
       </c>
       <c r="O3">
-        <v>0.7946426666666667</v>
+        <v>0.7906186666666667</v>
       </c>
       <c r="P3">
-        <v>3.178570666666666</v>
+        <v>3.162474666666667</v>
       </c>
       <c r="Q3">
-        <v>4.268570666666666</v>
+        <v>4.252474666666666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1444664109031045</v>
+        <v>0.1452734651005042</v>
       </c>
       <c r="T3">
-        <v>1.181998178705849</v>
+        <v>1.191666480032632</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>198.4758117958913</v>
+        <v>99.23790589794567</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1784,22 +1784,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1431727957984942</v>
+        <v>0.1429214448029148</v>
       </c>
       <c r="C4">
-        <v>40.15026724346851</v>
+        <v>39.85156253575798</v>
       </c>
       <c r="D4">
-        <v>39.14026724346851</v>
+        <v>39.24156253575798</v>
       </c>
       <c r="E4">
-        <v>-27.6</v>
+        <v>-27.2</v>
       </c>
       <c r="F4">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G4">
         <v>1.81</v>
@@ -1820,28 +1820,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M4">
-        <v>0.04024</v>
+        <v>0.06036</v>
       </c>
       <c r="N4">
-        <v>3.953093333333333</v>
+        <v>3.932973333333333</v>
       </c>
       <c r="O4">
-        <v>0.7906186666666667</v>
+        <v>0.7865946666666667</v>
       </c>
       <c r="P4">
-        <v>3.162474666666667</v>
+        <v>3.146378666666666</v>
       </c>
       <c r="Q4">
-        <v>4.252474666666666</v>
+        <v>4.236378666666666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1452734651005042</v>
+        <v>0.1460971595906339</v>
       </c>
       <c r="T4">
-        <v>1.191666480032632</v>
+        <v>1.201534127778523</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.23790589794567</v>
+        <v>66.15860393196377</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1866,22 +1866,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1429214448029148</v>
+        <v>0.1426700938073355</v>
       </c>
       <c r="C5">
-        <v>39.85156253575798</v>
+        <v>39.55338349436123</v>
       </c>
       <c r="D5">
-        <v>39.24156253575798</v>
+        <v>39.34338349436123</v>
       </c>
       <c r="E5">
-        <v>-27.2</v>
+        <v>-26.8</v>
       </c>
       <c r="F5">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
         <v>1.81</v>
@@ -1902,28 +1902,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M5">
-        <v>0.06036</v>
+        <v>0.08048</v>
       </c>
       <c r="N5">
-        <v>3.932973333333333</v>
+        <v>3.912853333333333</v>
       </c>
       <c r="O5">
-        <v>0.7865946666666667</v>
+        <v>0.7825706666666666</v>
       </c>
       <c r="P5">
-        <v>3.146378666666666</v>
+        <v>3.130282666666667</v>
       </c>
       <c r="Q5">
-        <v>4.236378666666666</v>
+        <v>4.220282666666666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1460971595906339</v>
+        <v>0.1469380143826412</v>
       </c>
       <c r="T5">
-        <v>1.201534127778523</v>
+        <v>1.211607351519122</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.15860393196377</v>
+        <v>49.61895294897283</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1948,22 +1948,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1426700938073355</v>
+        <v>0.1424187428117562</v>
       </c>
       <c r="C6">
-        <v>39.55338349436123</v>
+        <v>39.25573422179756</v>
       </c>
       <c r="D6">
-        <v>39.34338349436123</v>
+        <v>39.44573422179756</v>
       </c>
       <c r="E6">
-        <v>-26.8</v>
+        <v>-26.4</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1.81</v>
@@ -1984,28 +1984,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M6">
-        <v>0.08048</v>
+        <v>0.1006</v>
       </c>
       <c r="N6">
-        <v>3.912853333333333</v>
+        <v>3.892733333333333</v>
       </c>
       <c r="O6">
-        <v>0.7825706666666666</v>
+        <v>0.7785466666666667</v>
       </c>
       <c r="P6">
-        <v>3.130282666666667</v>
+        <v>3.114186666666666</v>
       </c>
       <c r="Q6">
-        <v>4.220282666666666</v>
+        <v>4.204186666666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1469380143826412</v>
+        <v>0.147796571380796</v>
       </c>
       <c r="T6">
-        <v>1.211607351519122</v>
+        <v>1.221892643127942</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.61895294897283</v>
+        <v>39.69516235917826</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2030,22 +2030,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1424187428117562</v>
+        <v>0.1421673918161769</v>
       </c>
       <c r="C7">
-        <v>39.25573422179756</v>
+        <v>38.9586188633879</v>
       </c>
       <c r="D7">
-        <v>39.44573422179756</v>
+        <v>39.5486188633879</v>
       </c>
       <c r="E7">
-        <v>-26.4</v>
+        <v>-26</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G7">
         <v>1.81</v>
@@ -2066,28 +2066,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M7">
-        <v>0.1006</v>
+        <v>0.12072</v>
       </c>
       <c r="N7">
-        <v>3.892733333333333</v>
+        <v>3.872613333333333</v>
       </c>
       <c r="O7">
-        <v>0.7785466666666667</v>
+        <v>0.7745226666666667</v>
       </c>
       <c r="P7">
-        <v>3.114186666666666</v>
+        <v>3.098090666666667</v>
       </c>
       <c r="Q7">
-        <v>4.204186666666667</v>
+        <v>4.188090666666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.147796571380796</v>
+        <v>0.1486733955491244</v>
       </c>
       <c r="T7">
-        <v>1.221892643127942</v>
+        <v>1.232396770728441</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.69516235917826</v>
+        <v>33.07930196598188</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2112,22 +2112,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1421673918161769</v>
+        <v>0.1419160408205977</v>
       </c>
       <c r="C8">
-        <v>38.9586188633879</v>
+        <v>38.66204160781464</v>
       </c>
       <c r="D8">
-        <v>39.5486188633879</v>
+        <v>39.65204160781463</v>
       </c>
       <c r="E8">
-        <v>-26</v>
+        <v>-25.6</v>
       </c>
       <c r="F8">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
         <v>1.81</v>
@@ -2148,28 +2148,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M8">
-        <v>0.12072</v>
+        <v>0.14084</v>
       </c>
       <c r="N8">
-        <v>3.872613333333333</v>
+        <v>3.852493333333333</v>
       </c>
       <c r="O8">
-        <v>0.7745226666666667</v>
+        <v>0.7704986666666667</v>
       </c>
       <c r="P8">
-        <v>3.098090666666667</v>
+        <v>3.081994666666667</v>
       </c>
       <c r="Q8">
-        <v>4.188090666666667</v>
+        <v>4.171994666666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1486733955491244</v>
+        <v>0.1495690761511803</v>
       </c>
       <c r="T8">
-        <v>1.232396770728441</v>
+        <v>1.243126793546154</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.07930196598188</v>
+        <v>28.35368739941305</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2194,22 +2194,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1419160408205976</v>
+        <v>0.1416646898250183</v>
       </c>
       <c r="C9">
-        <v>38.66204160781465</v>
+        <v>38.36600668768991</v>
       </c>
       <c r="D9">
-        <v>39.65204160781465</v>
+        <v>39.75600668768991</v>
       </c>
       <c r="E9">
-        <v>-25.6</v>
+        <v>-25.2</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
         <v>1.81</v>
@@ -2230,28 +2230,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M9">
-        <v>0.14084</v>
+        <v>0.16096</v>
       </c>
       <c r="N9">
-        <v>3.852493333333333</v>
+        <v>3.832373333333333</v>
       </c>
       <c r="O9">
-        <v>0.7704986666666667</v>
+        <v>0.7664746666666666</v>
       </c>
       <c r="P9">
-        <v>3.081994666666667</v>
+        <v>3.065898666666667</v>
       </c>
       <c r="Q9">
-        <v>4.171994666666667</v>
+        <v>4.155898666666666</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1495690761511803</v>
+        <v>0.1504842280706721</v>
       </c>
       <c r="T9">
-        <v>1.243126793546154</v>
+        <v>1.254090077729469</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.35368739941305</v>
+        <v>24.80947647448641</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2276,22 +2276,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1416646898250183</v>
+        <v>0.141413338829439</v>
       </c>
       <c r="C10">
-        <v>38.36600668768991</v>
+        <v>38.07051838013312</v>
       </c>
       <c r="D10">
-        <v>39.75600668768991</v>
+        <v>39.86051838013312</v>
       </c>
       <c r="E10">
-        <v>-25.2</v>
+        <v>-24.8</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G10">
         <v>1.81</v>
@@ -2312,28 +2312,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M10">
-        <v>0.16096</v>
+        <v>0.18108</v>
       </c>
       <c r="N10">
-        <v>3.832373333333333</v>
+        <v>3.812253333333333</v>
       </c>
       <c r="O10">
-        <v>0.7664746666666666</v>
+        <v>0.7624506666666666</v>
       </c>
       <c r="P10">
-        <v>3.065898666666667</v>
+        <v>3.049802666666666</v>
       </c>
       <c r="Q10">
-        <v>4.155898666666666</v>
+        <v>4.139802666666666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1504842280706721</v>
+        <v>0.1514194932191637</v>
       </c>
       <c r="T10">
-        <v>1.254090077729469</v>
+        <v>1.265294313213517</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.80947647448641</v>
+        <v>22.05286797732126</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2358,22 +2358,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.141413338829439</v>
+        <v>0.1411619878338597</v>
       </c>
       <c r="C11">
-        <v>38.07051838013312</v>
+        <v>37.77558100735738</v>
       </c>
       <c r="D11">
-        <v>39.86051838013312</v>
+        <v>39.96558100735738</v>
       </c>
       <c r="E11">
-        <v>-24.8</v>
+        <v>-24.4</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G11">
         <v>1.81</v>
@@ -2394,28 +2394,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M11">
-        <v>0.18108</v>
+        <v>0.2012</v>
       </c>
       <c r="N11">
-        <v>3.812253333333333</v>
+        <v>3.792133333333333</v>
       </c>
       <c r="O11">
-        <v>0.7624506666666666</v>
+        <v>0.7584266666666667</v>
       </c>
       <c r="P11">
-        <v>3.049802666666666</v>
+        <v>3.033706666666666</v>
       </c>
       <c r="Q11">
-        <v>4.139802666666666</v>
+        <v>4.123706666666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1514194932191637</v>
+        <v>0.1523755420376219</v>
       </c>
       <c r="T11">
-        <v>1.265294313213517</v>
+        <v>1.276747531708321</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.05286797732126</v>
+        <v>19.84758117958913</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2440,22 +2440,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1411619878338597</v>
+        <v>0.1409106368382804</v>
       </c>
       <c r="C12">
-        <v>37.77558100735737</v>
+        <v>37.48119893726552</v>
       </c>
       <c r="D12">
-        <v>39.96558100735736</v>
+        <v>40.07119893726552</v>
       </c>
       <c r="E12">
-        <v>-24.4</v>
+        <v>-24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G12">
         <v>1.81</v>
@@ -2476,28 +2476,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M12">
-        <v>0.2012</v>
+        <v>0.22132</v>
       </c>
       <c r="N12">
-        <v>3.792133333333333</v>
+        <v>3.772013333333333</v>
       </c>
       <c r="O12">
-        <v>0.7584266666666667</v>
+        <v>0.7544026666666667</v>
       </c>
       <c r="P12">
-        <v>3.033706666666666</v>
+        <v>3.017610666666667</v>
       </c>
       <c r="Q12">
-        <v>4.123706666666666</v>
+        <v>4.107610666666666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1523755420376219</v>
+        <v>0.1533530750991915</v>
       </c>
       <c r="T12">
-        <v>1.276747531708322</v>
+        <v>1.288458125899638</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.84758117958913</v>
+        <v>18.0432556178083</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2522,22 +2522,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1409106368382804</v>
+        <v>0.1406592858427011</v>
       </c>
       <c r="C13">
-        <v>37.48119893726552</v>
+        <v>37.18737658405531</v>
       </c>
       <c r="D13">
-        <v>40.07119893726552</v>
+        <v>40.17737658405531</v>
       </c>
       <c r="E13">
-        <v>-24</v>
+        <v>-23.6</v>
       </c>
       <c r="F13">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="G13">
         <v>1.81</v>
@@ -2558,28 +2558,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M13">
-        <v>0.22132</v>
+        <v>0.24144</v>
       </c>
       <c r="N13">
-        <v>3.772013333333333</v>
+        <v>3.751893333333333</v>
       </c>
       <c r="O13">
-        <v>0.7544026666666667</v>
+        <v>0.7503786666666667</v>
       </c>
       <c r="P13">
-        <v>3.017610666666667</v>
+        <v>3.001514666666667</v>
       </c>
       <c r="Q13">
-        <v>4.107610666666666</v>
+        <v>4.091514666666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1533530750991915</v>
+        <v>0.1543528248212513</v>
       </c>
       <c r="T13">
-        <v>1.288458125899638</v>
+        <v>1.30043486995894</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.0432556178083</v>
+        <v>16.53965098299094</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2604,22 +2604,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1406592858427011</v>
+        <v>0.1404079348471218</v>
       </c>
       <c r="C14">
-        <v>37.18737658405531</v>
+        <v>36.89411840883445</v>
       </c>
       <c r="D14">
-        <v>40.17737658405531</v>
+        <v>40.28411840883445</v>
       </c>
       <c r="E14">
-        <v>-23.6</v>
+        <v>-23.2</v>
       </c>
       <c r="F14">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="G14">
         <v>1.81</v>
@@ -2640,28 +2640,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M14">
-        <v>0.24144</v>
+        <v>0.26156</v>
       </c>
       <c r="N14">
-        <v>3.751893333333333</v>
+        <v>3.731773333333333</v>
       </c>
       <c r="O14">
-        <v>0.7503786666666667</v>
+        <v>0.7463546666666666</v>
       </c>
       <c r="P14">
-        <v>3.001514666666667</v>
+        <v>2.985418666666666</v>
       </c>
       <c r="Q14">
-        <v>4.091514666666667</v>
+        <v>4.075418666666666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1543528248212513</v>
+        <v>0.1553755572955423</v>
       </c>
       <c r="T14">
-        <v>1.30043486995894</v>
+        <v>1.31268694146788</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.53965098299094</v>
+        <v>15.26737013814548</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2686,22 +2686,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1404079348471218</v>
+        <v>0.1401565838515425</v>
       </c>
       <c r="C15">
-        <v>36.89411840883445</v>
+        <v>36.60142892024535</v>
       </c>
       <c r="D15">
-        <v>40.28411840883445</v>
+        <v>40.39142892024535</v>
       </c>
       <c r="E15">
-        <v>-23.2</v>
+        <v>-22.8</v>
       </c>
       <c r="F15">
-        <v>5.2</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="G15">
         <v>1.81</v>
@@ -2722,28 +2722,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M15">
-        <v>0.26156</v>
+        <v>0.28168</v>
       </c>
       <c r="N15">
-        <v>3.731773333333333</v>
+        <v>3.711653333333333</v>
       </c>
       <c r="O15">
-        <v>0.7463546666666666</v>
+        <v>0.7423306666666667</v>
       </c>
       <c r="P15">
-        <v>2.985418666666666</v>
+        <v>2.969322666666666</v>
       </c>
       <c r="Q15">
-        <v>4.075418666666666</v>
+        <v>4.059322666666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1553755572955423</v>
+        <v>0.1564220742459796</v>
       </c>
       <c r="T15">
-        <v>1.31268694146788</v>
+        <v>1.325223944872377</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.26737013814548</v>
+        <v>14.17684369970652</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2768,22 +2768,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1401565838515425</v>
+        <v>0.1399052328559632</v>
       </c>
       <c r="C16">
-        <v>36.60142892024535</v>
+        <v>36.30931267510001</v>
       </c>
       <c r="D16">
-        <v>40.39142892024535</v>
+        <v>40.49931267510001</v>
       </c>
       <c r="E16">
-        <v>-22.8</v>
+        <v>-22.4</v>
       </c>
       <c r="F16">
-        <v>5.600000000000001</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="G16">
         <v>1.81</v>
@@ -2804,28 +2804,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M16">
-        <v>0.28168</v>
+        <v>0.3018</v>
       </c>
       <c r="N16">
-        <v>3.711653333333333</v>
+        <v>3.691533333333333</v>
       </c>
       <c r="O16">
-        <v>0.7423306666666667</v>
+        <v>0.7383066666666667</v>
       </c>
       <c r="P16">
-        <v>2.969322666666666</v>
+        <v>2.953226666666667</v>
       </c>
       <c r="Q16">
-        <v>4.059322666666667</v>
+        <v>4.043226666666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1564220742459796</v>
+        <v>0.1574932151246626</v>
       </c>
       <c r="T16">
-        <v>1.325223944872377</v>
+        <v>1.338055936592275</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.17684369970652</v>
+        <v>13.23172078639275</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2850,22 +2850,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1399052328559632</v>
+        <v>0.1398458818603839</v>
       </c>
       <c r="C17">
-        <v>36.30931267510002</v>
+        <v>35.93487120546835</v>
       </c>
       <c r="D17">
-        <v>40.49931267510002</v>
+        <v>40.52487120546835</v>
       </c>
       <c r="E17">
-        <v>-22.4</v>
+        <v>-22</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G17">
         <v>1.81</v>
@@ -2886,45 +2886,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M17">
-        <v>0.3018</v>
+        <v>0.33152</v>
       </c>
       <c r="N17">
-        <v>3.691533333333333</v>
+        <v>3.661813333333333</v>
       </c>
       <c r="O17">
-        <v>0.7383066666666667</v>
+        <v>0.7323626666666666</v>
       </c>
       <c r="P17">
-        <v>2.953226666666667</v>
+        <v>2.929450666666666</v>
       </c>
       <c r="Q17">
-        <v>4.043226666666667</v>
+        <v>4.019450666666666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1574932151246626</v>
+        <v>0.1585898593575998</v>
       </c>
       <c r="T17">
-        <v>1.338055936592275</v>
+        <v>1.35119345192455</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.23172078639276</v>
+        <v>12.04552767052767</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2932,22 +2932,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1398458818603839</v>
+        <v>0.1396065308648045</v>
       </c>
       <c r="C18">
-        <v>35.93487120546835</v>
+        <v>35.63827198342412</v>
       </c>
       <c r="D18">
-        <v>40.52487120546835</v>
+        <v>40.62827198342412</v>
       </c>
       <c r="E18">
-        <v>-22</v>
+        <v>-21.6</v>
       </c>
       <c r="F18">
-        <v>6.4</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="G18">
         <v>1.81</v>
@@ -2968,28 +2968,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M18">
-        <v>0.33152</v>
+        <v>0.3522400000000001</v>
       </c>
       <c r="N18">
-        <v>3.661813333333333</v>
+        <v>3.641093333333333</v>
       </c>
       <c r="O18">
-        <v>0.7323626666666666</v>
+        <v>0.7282186666666667</v>
       </c>
       <c r="P18">
-        <v>2.929450666666666</v>
+        <v>2.912874666666666</v>
       </c>
       <c r="Q18">
-        <v>4.019450666666666</v>
+        <v>4.002874666666666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1585898593575998</v>
+        <v>0.1597129287527766</v>
       </c>
       <c r="T18">
-        <v>1.35119345192455</v>
+        <v>1.364647533891338</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.04552767052767</v>
+        <v>11.33696721932016</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3014,22 +3014,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1396065308648045</v>
+        <v>0.1393671798692253</v>
       </c>
       <c r="C19">
-        <v>35.63827198342412</v>
+        <v>35.34220177335141</v>
       </c>
       <c r="D19">
-        <v>40.62827198342412</v>
+        <v>40.73220177335141</v>
       </c>
       <c r="E19">
-        <v>-21.6</v>
+        <v>-21.2</v>
       </c>
       <c r="F19">
-        <v>6.800000000000001</v>
+        <v>7.200000000000001</v>
       </c>
       <c r="G19">
         <v>1.81</v>
@@ -3050,28 +3050,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M19">
-        <v>0.3522400000000001</v>
+        <v>0.3729600000000001</v>
       </c>
       <c r="N19">
-        <v>3.641093333333333</v>
+        <v>3.620373333333333</v>
       </c>
       <c r="O19">
-        <v>0.7282186666666667</v>
+        <v>0.7240746666666666</v>
       </c>
       <c r="P19">
-        <v>2.912874666666666</v>
+        <v>2.896298666666667</v>
       </c>
       <c r="Q19">
-        <v>4.002874666666666</v>
+        <v>3.986298666666666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1597129287527766</v>
+        <v>0.1608633900844211</v>
       </c>
       <c r="T19">
-        <v>1.364647533891338</v>
+        <v>1.37842976419878</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.33696721932016</v>
+        <v>10.70713570713571</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3096,22 +3096,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1393671798692253</v>
+        <v>0.139127828873646</v>
       </c>
       <c r="C20">
-        <v>35.34220177335141</v>
+        <v>35.04666464540416</v>
       </c>
       <c r="D20">
-        <v>40.73220177335141</v>
+        <v>40.83666464540416</v>
       </c>
       <c r="E20">
-        <v>-21.2</v>
+        <v>-20.8</v>
       </c>
       <c r="F20">
-        <v>7.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G20">
         <v>1.81</v>
@@ -3132,28 +3132,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M20">
-        <v>0.37296</v>
+        <v>0.39368</v>
       </c>
       <c r="N20">
-        <v>3.620373333333333</v>
+        <v>3.599653333333333</v>
       </c>
       <c r="O20">
-        <v>0.7240746666666666</v>
+        <v>0.7199306666666667</v>
       </c>
       <c r="P20">
-        <v>2.896298666666667</v>
+        <v>2.879722666666667</v>
       </c>
       <c r="Q20">
-        <v>3.986298666666666</v>
+        <v>3.969722666666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.160863390084421</v>
+        <v>0.1620422578686987</v>
       </c>
       <c r="T20">
-        <v>1.37842976419878</v>
+        <v>1.392552296489122</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.70713570713571</v>
+        <v>10.14360224886541</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3178,22 +3178,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.139127828873646</v>
+        <v>0.1391604778780667</v>
       </c>
       <c r="C21">
-        <v>35.04666464540416</v>
+        <v>34.63238369403333</v>
       </c>
       <c r="D21">
-        <v>40.83666464540416</v>
+        <v>40.82238369403333</v>
       </c>
       <c r="E21">
-        <v>-20.8</v>
+        <v>-20.4</v>
       </c>
       <c r="F21">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>1.81</v>
@@ -3214,45 +3214,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M21">
-        <v>0.39368</v>
+        <v>0.428</v>
       </c>
       <c r="N21">
-        <v>3.599653333333333</v>
+        <v>3.565333333333333</v>
       </c>
       <c r="O21">
-        <v>0.7199306666666667</v>
+        <v>0.7130666666666667</v>
       </c>
       <c r="P21">
-        <v>2.879722666666667</v>
+        <v>2.852266666666667</v>
       </c>
       <c r="Q21">
-        <v>3.969722666666667</v>
+        <v>3.942266666666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1620422578686987</v>
+        <v>0.1632505973475833</v>
       </c>
       <c r="T21">
-        <v>1.392552296489122</v>
+        <v>1.407027892086722</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.14360224886541</v>
+        <v>9.330218068535826</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3260,22 +3260,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1391604778780667</v>
+        <v>0.1389347268824873</v>
       </c>
       <c r="C22">
-        <v>34.63238369403333</v>
+        <v>34.33133382863218</v>
       </c>
       <c r="D22">
-        <v>40.82238369403333</v>
+        <v>40.92133382863218</v>
       </c>
       <c r="E22">
-        <v>-20.4</v>
+        <v>-20</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="G22">
         <v>1.81</v>
@@ -3296,28 +3296,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M22">
-        <v>0.428</v>
+        <v>0.4494</v>
       </c>
       <c r="N22">
-        <v>3.565333333333333</v>
+        <v>3.543933333333333</v>
       </c>
       <c r="O22">
-        <v>0.7130666666666667</v>
+        <v>0.7087866666666667</v>
       </c>
       <c r="P22">
-        <v>2.852266666666667</v>
+        <v>2.835146666666667</v>
       </c>
       <c r="Q22">
-        <v>3.942266666666666</v>
+        <v>3.925146666666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1632505973475833</v>
+        <v>0.1644895276993511</v>
       </c>
       <c r="T22">
-        <v>1.407027892086722</v>
+        <v>1.421869958458944</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.330218068535826</v>
+        <v>8.885921970034119</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3342,22 +3342,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1389347268824873</v>
+        <v>0.1387089758869081</v>
       </c>
       <c r="C23">
-        <v>34.33133382863218</v>
+        <v>34.03076482293666</v>
       </c>
       <c r="D23">
-        <v>40.92133382863218</v>
+        <v>41.02076482293666</v>
       </c>
       <c r="E23">
-        <v>-20</v>
+        <v>-19.6</v>
       </c>
       <c r="F23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G23">
         <v>1.81</v>
@@ -3378,28 +3378,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M23">
-        <v>0.4494</v>
+        <v>0.4708000000000001</v>
       </c>
       <c r="N23">
-        <v>3.543933333333333</v>
+        <v>3.522533333333333</v>
       </c>
       <c r="O23">
-        <v>0.7087866666666667</v>
+        <v>0.7045066666666666</v>
       </c>
       <c r="P23">
-        <v>2.835146666666667</v>
+        <v>2.818026666666666</v>
       </c>
       <c r="Q23">
-        <v>3.925146666666667</v>
+        <v>3.908026666666666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1644895276993511</v>
+        <v>0.1657602254960359</v>
       </c>
       <c r="T23">
-        <v>1.421869958458944</v>
+        <v>1.437092590635583</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.885921970034119</v>
+        <v>8.482016425941659</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3424,22 +3424,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1387089758869081</v>
+        <v>0.1384832248913287</v>
       </c>
       <c r="C24">
-        <v>34.03076482293666</v>
+        <v>33.73068019067511</v>
       </c>
       <c r="D24">
-        <v>41.02076482293666</v>
+        <v>41.12068019067511</v>
       </c>
       <c r="E24">
-        <v>-19.6</v>
+        <v>-19.2</v>
       </c>
       <c r="F24">
-        <v>8.800000000000001</v>
+        <v>9.200000000000001</v>
       </c>
       <c r="G24">
         <v>1.81</v>
@@ -3460,28 +3460,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M24">
-        <v>0.4708000000000001</v>
+        <v>0.4922</v>
       </c>
       <c r="N24">
-        <v>3.522533333333333</v>
+        <v>3.501133333333333</v>
       </c>
       <c r="O24">
-        <v>0.7045066666666666</v>
+        <v>0.7002266666666667</v>
       </c>
       <c r="P24">
-        <v>2.818026666666666</v>
+        <v>2.800906666666667</v>
       </c>
       <c r="Q24">
-        <v>3.908026666666666</v>
+        <v>3.890906666666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1657602254960359</v>
+        <v>0.1670639284302971</v>
       </c>
       <c r="T24">
-        <v>1.437092590635583</v>
+        <v>1.452710615855771</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.482016425941659</v>
+        <v>8.113233103074631</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3506,22 +3506,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1384832248913287</v>
+        <v>0.1382574738957494</v>
       </c>
       <c r="C25">
-        <v>33.73068019067511</v>
+        <v>33.43108347989336</v>
       </c>
       <c r="D25">
-        <v>41.12068019067511</v>
+        <v>41.22108347989336</v>
       </c>
       <c r="E25">
-        <v>-19.2</v>
+        <v>-18.8</v>
       </c>
       <c r="F25">
-        <v>9.200000000000001</v>
+        <v>9.600000000000001</v>
       </c>
       <c r="G25">
         <v>1.81</v>
@@ -3542,28 +3542,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M25">
-        <v>0.4922</v>
+        <v>0.5136000000000001</v>
       </c>
       <c r="N25">
-        <v>3.501133333333333</v>
+        <v>3.479733333333333</v>
       </c>
       <c r="O25">
-        <v>0.7002266666666667</v>
+        <v>0.6959466666666666</v>
       </c>
       <c r="P25">
-        <v>2.800906666666667</v>
+        <v>2.783786666666666</v>
       </c>
       <c r="Q25">
-        <v>3.890906666666667</v>
+        <v>3.873786666666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1670639284302971</v>
+        <v>0.1684019393365124</v>
       </c>
       <c r="T25">
-        <v>1.452710615855771</v>
+        <v>1.468739641739648</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.113233103074631</v>
+        <v>7.775181723779853</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3588,22 +3588,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1382574738957494</v>
+        <v>0.1381917229001701</v>
       </c>
       <c r="C26">
-        <v>33.43108347989336</v>
+        <v>33.06041865400402</v>
       </c>
       <c r="D26">
-        <v>41.22108347989336</v>
+        <v>41.25041865400402</v>
       </c>
       <c r="E26">
-        <v>-18.8</v>
+        <v>-18.4</v>
       </c>
       <c r="F26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1.81</v>
@@ -3624,45 +3624,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M26">
-        <v>0.5135999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="N26">
-        <v>3.479733333333333</v>
+        <v>3.450333333333333</v>
       </c>
       <c r="O26">
-        <v>0.6959466666666667</v>
+        <v>0.6900666666666666</v>
       </c>
       <c r="P26">
-        <v>2.783786666666667</v>
+        <v>2.760266666666666</v>
       </c>
       <c r="Q26">
-        <v>3.873786666666667</v>
+        <v>3.850266666666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1684019393365124</v>
+        <v>0.1697756305335602</v>
       </c>
       <c r="T26">
-        <v>1.468739641739648</v>
+        <v>1.485196108313762</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.775181723779856</v>
+        <v>7.354205033763044</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3670,22 +3670,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1381917229001701</v>
+        <v>0.1379723719045908</v>
       </c>
       <c r="C27">
-        <v>33.06041865400402</v>
+        <v>32.75858603553984</v>
       </c>
       <c r="D27">
-        <v>41.25041865400402</v>
+        <v>41.34858603553983</v>
       </c>
       <c r="E27">
-        <v>-18.4</v>
+        <v>-18</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="G27">
         <v>1.81</v>
@@ -3706,28 +3706,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M27">
-        <v>0.543</v>
+        <v>0.56472</v>
       </c>
       <c r="N27">
-        <v>3.450333333333333</v>
+        <v>3.428613333333333</v>
       </c>
       <c r="O27">
-        <v>0.6900666666666666</v>
+        <v>0.6857226666666667</v>
       </c>
       <c r="P27">
-        <v>2.760266666666666</v>
+        <v>2.742890666666667</v>
       </c>
       <c r="Q27">
-        <v>3.850266666666666</v>
+        <v>3.832890666666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1697756305335602</v>
+        <v>0.1711864485197173</v>
       </c>
       <c r="T27">
-        <v>1.485196108313762</v>
+        <v>1.502097344254743</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.354205033763044</v>
+        <v>7.071350994002928</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3752,22 +3752,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1379723719045908</v>
+        <v>0.1377530209090115</v>
       </c>
       <c r="C28">
-        <v>32.75858603553984</v>
+        <v>32.45722176738454</v>
       </c>
       <c r="D28">
-        <v>41.34858603553983</v>
+        <v>41.44722176738454</v>
       </c>
       <c r="E28">
-        <v>-18</v>
+        <v>-17.6</v>
       </c>
       <c r="F28">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="G28">
         <v>1.81</v>
@@ -3788,28 +3788,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M28">
-        <v>0.56472</v>
+        <v>0.5864400000000001</v>
       </c>
       <c r="N28">
-        <v>3.428613333333333</v>
+        <v>3.406893333333333</v>
       </c>
       <c r="O28">
-        <v>0.6857226666666667</v>
+        <v>0.6813786666666667</v>
       </c>
       <c r="P28">
-        <v>2.742890666666667</v>
+        <v>2.725514666666666</v>
       </c>
       <c r="Q28">
-        <v>3.832890666666667</v>
+        <v>3.815514666666666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1711864485197173</v>
+        <v>0.1726359190534404</v>
       </c>
       <c r="T28">
-        <v>1.502097344254743</v>
+        <v>1.519461627755752</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.071350994002928</v>
+        <v>6.809449105336151</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3834,22 +3834,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1377530209090115</v>
+        <v>0.1375336699134322</v>
       </c>
       <c r="C29">
-        <v>32.45722176738454</v>
+        <v>32.15632920925677</v>
       </c>
       <c r="D29">
-        <v>41.44722176738454</v>
+        <v>41.54632920925678</v>
       </c>
       <c r="E29">
-        <v>-17.6</v>
+        <v>-17.2</v>
       </c>
       <c r="F29">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="G29">
         <v>1.81</v>
@@ -3870,28 +3870,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M29">
-        <v>0.5864400000000001</v>
+        <v>0.60816</v>
       </c>
       <c r="N29">
-        <v>3.406893333333333</v>
+        <v>3.385173333333333</v>
       </c>
       <c r="O29">
-        <v>0.6813786666666667</v>
+        <v>0.6770346666666667</v>
       </c>
       <c r="P29">
-        <v>2.725514666666666</v>
+        <v>2.708138666666667</v>
       </c>
       <c r="Q29">
-        <v>3.815514666666666</v>
+        <v>3.798138666666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1726359190534404</v>
+        <v>0.1741256526575447</v>
       </c>
       <c r="T29">
-        <v>1.519461627755752</v>
+        <v>1.537308252465122</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.809449105336151</v>
+        <v>6.56625449443129</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3916,22 +3916,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1375336699134322</v>
+        <v>0.1373143189178529</v>
       </c>
       <c r="C30">
-        <v>32.15632920925677</v>
+        <v>31.85591175308685</v>
       </c>
       <c r="D30">
-        <v>41.54632920925678</v>
+        <v>41.64591175308685</v>
       </c>
       <c r="E30">
-        <v>-17.2</v>
+        <v>-16.8</v>
       </c>
       <c r="F30">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="G30">
         <v>1.81</v>
@@ -3952,28 +3952,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M30">
-        <v>0.60816</v>
+        <v>0.6298800000000001</v>
       </c>
       <c r="N30">
-        <v>3.385173333333333</v>
+        <v>3.363453333333333</v>
       </c>
       <c r="O30">
-        <v>0.6770346666666667</v>
+        <v>0.6726906666666667</v>
       </c>
       <c r="P30">
-        <v>2.708138666666667</v>
+        <v>2.690762666666667</v>
       </c>
       <c r="Q30">
-        <v>3.798138666666667</v>
+        <v>3.780762666666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1741256526575447</v>
+        <v>0.1756573505885252</v>
       </c>
       <c r="T30">
-        <v>1.537308252465122</v>
+        <v>1.555657598997291</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.56625449443129</v>
+        <v>6.339831925657796</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3998,22 +3998,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1373143189178529</v>
+        <v>0.1370949679222736</v>
       </c>
       <c r="C31">
-        <v>31.85591175308685</v>
+        <v>31.55597282340372</v>
       </c>
       <c r="D31">
-        <v>41.64591175308685</v>
+        <v>41.74597282340372</v>
       </c>
       <c r="E31">
-        <v>-16.8</v>
+        <v>-16.4</v>
       </c>
       <c r="F31">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1.81</v>
@@ -4034,28 +4034,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M31">
-        <v>0.62988</v>
+        <v>0.6516</v>
       </c>
       <c r="N31">
-        <v>3.363453333333333</v>
+        <v>3.341733333333333</v>
       </c>
       <c r="O31">
-        <v>0.6726906666666667</v>
+        <v>0.6683466666666666</v>
       </c>
       <c r="P31">
-        <v>2.690762666666667</v>
+        <v>2.673386666666667</v>
       </c>
       <c r="Q31">
-        <v>3.780762666666666</v>
+        <v>3.763386666666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1756573505885252</v>
+        <v>0.1772328113175337</v>
       </c>
       <c r="T31">
-        <v>1.555657598997291</v>
+        <v>1.574531212573236</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.339831925657797</v>
+        <v>6.128504194802537</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4080,22 +4080,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1370949679222736</v>
+        <v>0.1371236169266943</v>
       </c>
       <c r="C32">
-        <v>31.55597282340372</v>
+        <v>31.14287675252731</v>
       </c>
       <c r="D32">
-        <v>41.74597282340372</v>
+        <v>41.7328767525273</v>
       </c>
       <c r="E32">
-        <v>-16.4</v>
+        <v>-16</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G32">
         <v>1.81</v>
@@ -4116,45 +4116,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M32">
-        <v>0.6516</v>
+        <v>0.68572</v>
       </c>
       <c r="N32">
-        <v>3.341733333333333</v>
+        <v>3.307613333333333</v>
       </c>
       <c r="O32">
-        <v>0.6683466666666666</v>
+        <v>0.6615226666666667</v>
       </c>
       <c r="P32">
-        <v>2.673386666666667</v>
+        <v>2.646090666666667</v>
       </c>
       <c r="Q32">
-        <v>3.763386666666666</v>
+        <v>3.736090666666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1772328113175337</v>
+        <v>0.1788539375749193</v>
       </c>
       <c r="T32">
-        <v>1.574531212573236</v>
+        <v>1.593951887412252</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.128504194802537</v>
+        <v>5.823562581422933</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4162,22 +4162,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1371236169266943</v>
+        <v>0.136912265931115</v>
       </c>
       <c r="C33">
-        <v>31.14287675252731</v>
+        <v>30.83968353216225</v>
       </c>
       <c r="D33">
-        <v>41.7328767525273</v>
+        <v>41.82968353216225</v>
       </c>
       <c r="E33">
-        <v>-16</v>
+        <v>-15.6</v>
       </c>
       <c r="F33">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="G33">
         <v>1.81</v>
@@ -4198,28 +4198,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M33">
-        <v>0.68572</v>
+        <v>0.70784</v>
       </c>
       <c r="N33">
-        <v>3.307613333333333</v>
+        <v>3.285493333333333</v>
       </c>
       <c r="O33">
-        <v>0.6615226666666667</v>
+        <v>0.6570986666666667</v>
       </c>
       <c r="P33">
-        <v>2.646090666666667</v>
+        <v>2.628394666666666</v>
       </c>
       <c r="Q33">
-        <v>3.736090666666667</v>
+        <v>3.718394666666666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1788539375749193</v>
+        <v>0.1805227440163456</v>
       </c>
       <c r="T33">
-        <v>1.593951887412252</v>
+        <v>1.613943758570063</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.823562581422933</v>
+        <v>5.641576250753466</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4244,22 +4244,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.136912265931115</v>
+        <v>0.1367009149355357</v>
       </c>
       <c r="C34">
-        <v>30.83968353216225</v>
+        <v>30.53694047688673</v>
       </c>
       <c r="D34">
-        <v>41.82968353216225</v>
+        <v>41.92694047688673</v>
       </c>
       <c r="E34">
-        <v>-15.6</v>
+        <v>-15.2</v>
       </c>
       <c r="F34">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="G34">
         <v>1.81</v>
@@ -4280,28 +4280,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M34">
-        <v>0.70784</v>
+        <v>0.7299600000000001</v>
       </c>
       <c r="N34">
-        <v>3.285493333333333</v>
+        <v>3.263373333333333</v>
       </c>
       <c r="O34">
-        <v>0.6570986666666667</v>
+        <v>0.6526746666666666</v>
       </c>
       <c r="P34">
-        <v>2.628394666666666</v>
+        <v>2.610698666666667</v>
       </c>
       <c r="Q34">
-        <v>3.718394666666666</v>
+        <v>3.700698666666666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1805227440163456</v>
+        <v>0.1822413655754264</v>
       </c>
       <c r="T34">
-        <v>1.613943758570063</v>
+        <v>1.634532402001242</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.641576250753466</v>
+        <v>5.470619394670027</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4326,22 +4326,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1367009149355357</v>
+        <v>0.1364895639399564</v>
       </c>
       <c r="C35">
-        <v>30.53694047688673</v>
+        <v>30.23465073401456</v>
       </c>
       <c r="D35">
-        <v>41.92694047688673</v>
+        <v>42.02465073401456</v>
       </c>
       <c r="E35">
-        <v>-15.2</v>
+        <v>-14.8</v>
       </c>
       <c r="F35">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="G35">
         <v>1.81</v>
@@ -4362,28 +4362,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M35">
-        <v>0.7299600000000001</v>
+        <v>0.7520800000000001</v>
       </c>
       <c r="N35">
-        <v>3.263373333333333</v>
+        <v>3.241253333333333</v>
       </c>
       <c r="O35">
-        <v>0.6526746666666666</v>
+        <v>0.6482506666666666</v>
       </c>
       <c r="P35">
-        <v>2.610698666666667</v>
+        <v>2.593002666666666</v>
       </c>
       <c r="Q35">
-        <v>3.700698666666666</v>
+        <v>3.683002666666666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1822413655754264</v>
+        <v>0.1840120665756915</v>
       </c>
       <c r="T35">
-        <v>1.634532402001242</v>
+        <v>1.655744943718213</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.470619394670027</v>
+        <v>5.309718824238555</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4408,22 +4408,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1364895639399564</v>
+        <v>0.1362782129443771</v>
       </c>
       <c r="C36">
-        <v>30.23465073401456</v>
+        <v>29.93281748026725</v>
       </c>
       <c r="D36">
-        <v>42.02465073401456</v>
+        <v>42.12281748026725</v>
       </c>
       <c r="E36">
-        <v>-14.8</v>
+        <v>-14.4</v>
       </c>
       <c r="F36">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>1.81</v>
@@ -4444,28 +4444,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M36">
-        <v>0.7520800000000001</v>
+        <v>0.7742000000000001</v>
       </c>
       <c r="N36">
-        <v>3.241253333333333</v>
+        <v>3.219133333333333</v>
       </c>
       <c r="O36">
-        <v>0.6482506666666666</v>
+        <v>0.6438266666666667</v>
       </c>
       <c r="P36">
-        <v>2.593002666666666</v>
+        <v>2.575306666666667</v>
       </c>
       <c r="Q36">
-        <v>3.683002666666666</v>
+        <v>3.665306666666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1840120665756915</v>
+        <v>0.185837250683657</v>
       </c>
       <c r="T36">
-        <v>1.655744943718213</v>
+        <v>1.677610179026476</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.309718824238555</v>
+        <v>5.158012572117454</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4490,22 +4490,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1362782129443771</v>
+        <v>0.1360668619487977</v>
       </c>
       <c r="C37">
-        <v>29.93281748026725</v>
+        <v>29.63144392211819</v>
       </c>
       <c r="D37">
-        <v>42.12281748026725</v>
+        <v>42.22144392211819</v>
       </c>
       <c r="E37">
-        <v>-14.4</v>
+        <v>-14</v>
       </c>
       <c r="F37">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G37">
         <v>1.81</v>
@@ -4526,28 +4526,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M37">
-        <v>0.7742000000000001</v>
+        <v>0.7963200000000001</v>
       </c>
       <c r="N37">
-        <v>3.219133333333333</v>
+        <v>3.197013333333333</v>
       </c>
       <c r="O37">
-        <v>0.6438266666666667</v>
+        <v>0.6394026666666667</v>
       </c>
       <c r="P37">
-        <v>2.575306666666667</v>
+        <v>2.557610666666666</v>
       </c>
       <c r="Q37">
-        <v>3.665306666666666</v>
+        <v>3.647610666666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.185837250683657</v>
+        <v>0.1877194717949965</v>
       </c>
       <c r="T37">
-        <v>1.677610179026476</v>
+        <v>1.700158702938122</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.158012572117454</v>
+        <v>5.014734445114191</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4572,22 +4572,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1360668619487978</v>
+        <v>0.1358555109532185</v>
       </c>
       <c r="C38">
-        <v>29.63144392211819</v>
+        <v>29.33053329614183</v>
       </c>
       <c r="D38">
-        <v>42.22144392211818</v>
+        <v>42.32053329614183</v>
       </c>
       <c r="E38">
-        <v>-14</v>
+        <v>-13.6</v>
       </c>
       <c r="F38">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="G38">
         <v>1.81</v>
@@ -4608,28 +4608,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M38">
-        <v>0.7963199999999999</v>
+        <v>0.8184400000000001</v>
       </c>
       <c r="N38">
-        <v>3.197013333333333</v>
+        <v>3.174893333333333</v>
       </c>
       <c r="O38">
-        <v>0.6394026666666668</v>
+        <v>0.6349786666666667</v>
       </c>
       <c r="P38">
-        <v>2.557610666666667</v>
+        <v>2.539914666666667</v>
       </c>
       <c r="Q38">
-        <v>3.647610666666667</v>
+        <v>3.629914666666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1877194717949965</v>
+        <v>0.1896614459574897</v>
       </c>
       <c r="T38">
-        <v>1.700158702938122</v>
+        <v>1.723423053005694</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.014734445114192</v>
+        <v>4.879201081732727</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1358555109532185</v>
+        <v>0.1356441599576392</v>
       </c>
       <c r="C39">
-        <v>29.33053329614183</v>
+        <v>29.03008886936778</v>
       </c>
       <c r="D39">
-        <v>42.32053329614183</v>
+        <v>42.42008886936778</v>
       </c>
       <c r="E39">
-        <v>-13.6</v>
+        <v>-13.2</v>
       </c>
       <c r="F39">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G39">
         <v>1.81</v>
@@ -4690,28 +4690,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M39">
-        <v>0.8184400000000001</v>
+        <v>0.84056</v>
       </c>
       <c r="N39">
-        <v>3.174893333333333</v>
+        <v>3.152773333333333</v>
       </c>
       <c r="O39">
-        <v>0.6349786666666667</v>
+        <v>0.6305546666666667</v>
       </c>
       <c r="P39">
-        <v>2.539914666666667</v>
+        <v>2.522218666666666</v>
       </c>
       <c r="Q39">
-        <v>3.629914666666667</v>
+        <v>3.612218666666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1896614459574897</v>
+        <v>0.1916660644478051</v>
       </c>
       <c r="T39">
-        <v>1.723423053005694</v>
+        <v>1.74743786597867</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.879201081732727</v>
+        <v>4.750801053266077</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4736,22 +4736,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1356441599576392</v>
+        <v>0.1354328089620599</v>
       </c>
       <c r="C40">
-        <v>29.03008886936778</v>
+        <v>28.73011393963976</v>
       </c>
       <c r="D40">
-        <v>42.42008886936778</v>
+        <v>42.52011393963976</v>
       </c>
       <c r="E40">
-        <v>-13.2</v>
+        <v>-12.8</v>
       </c>
       <c r="F40">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="G40">
         <v>1.81</v>
@@ -4772,28 +4772,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M40">
-        <v>0.84056</v>
+        <v>0.8626800000000001</v>
       </c>
       <c r="N40">
-        <v>3.152773333333333</v>
+        <v>3.130653333333333</v>
       </c>
       <c r="O40">
-        <v>0.6305546666666667</v>
+        <v>0.6261306666666666</v>
       </c>
       <c r="P40">
-        <v>2.522218666666666</v>
+        <v>2.504522666666666</v>
       </c>
       <c r="Q40">
-        <v>3.612218666666666</v>
+        <v>3.594522666666666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1916660644478051</v>
+        <v>0.1937364081345244</v>
       </c>
       <c r="T40">
-        <v>1.74743786597867</v>
+        <v>1.772240049868794</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.750801053266077</v>
+        <v>4.628985641643869</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4818,22 +4818,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1354328089620599</v>
+        <v>0.1352214579664806</v>
       </c>
       <c r="C41">
-        <v>28.73011393963976</v>
+        <v>28.43061183597978</v>
       </c>
       <c r="D41">
-        <v>42.52011393963976</v>
+        <v>42.62061183597977</v>
       </c>
       <c r="E41">
-        <v>-12.8</v>
+        <v>-12.4</v>
       </c>
       <c r="F41">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="G41">
         <v>1.81</v>
@@ -4854,28 +4854,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M41">
-        <v>0.8626800000000001</v>
+        <v>0.8848</v>
       </c>
       <c r="N41">
-        <v>3.130653333333333</v>
+        <v>3.108533333333333</v>
       </c>
       <c r="O41">
-        <v>0.6261306666666666</v>
+        <v>0.6217066666666666</v>
       </c>
       <c r="P41">
-        <v>2.504522666666666</v>
+        <v>2.486826666666667</v>
       </c>
       <c r="Q41">
-        <v>3.594522666666666</v>
+        <v>3.576826666666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1937364081345244</v>
+        <v>0.1958757632774676</v>
       </c>
       <c r="T41">
-        <v>1.772240049868794</v>
+        <v>1.797868973221922</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.628985641643869</v>
+        <v>4.513261000602772</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4900,22 +4900,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1352214579664806</v>
+        <v>0.1358301069709013</v>
       </c>
       <c r="C42">
-        <v>28.43061183597978</v>
+        <v>27.74247496894089</v>
       </c>
       <c r="D42">
-        <v>42.62061183597977</v>
+        <v>42.33247496894089</v>
       </c>
       <c r="E42">
-        <v>-12.4</v>
+        <v>-12</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G42">
         <v>1.81</v>
@@ -4936,45 +4936,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M42">
-        <v>0.8848</v>
+        <v>0.9479200000000002</v>
       </c>
       <c r="N42">
-        <v>3.108533333333333</v>
+        <v>3.045413333333333</v>
       </c>
       <c r="O42">
-        <v>0.6217066666666666</v>
+        <v>0.6090826666666667</v>
       </c>
       <c r="P42">
-        <v>2.486826666666667</v>
+        <v>2.436330666666666</v>
       </c>
       <c r="Q42">
-        <v>3.576826666666666</v>
+        <v>3.526330666666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1958757632774676</v>
+        <v>0.1980876389337309</v>
       </c>
       <c r="T42">
-        <v>1.797868973221922</v>
+        <v>1.824366673637868</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.513261000602772</v>
+        <v>4.212732438743071</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4982,22 +4982,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1358301069709013</v>
+        <v>0.1356387559753219</v>
       </c>
       <c r="C43">
-        <v>27.74247496894089</v>
+        <v>27.43264052324653</v>
       </c>
       <c r="D43">
-        <v>42.33247496894089</v>
+        <v>42.42264052324653</v>
       </c>
       <c r="E43">
-        <v>-12</v>
+        <v>-11.6</v>
       </c>
       <c r="F43">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="G43">
         <v>1.81</v>
@@ -5018,28 +5018,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M43">
-        <v>0.9479200000000002</v>
+        <v>0.9710400000000001</v>
       </c>
       <c r="N43">
-        <v>3.045413333333333</v>
+        <v>3.022293333333333</v>
       </c>
       <c r="O43">
-        <v>0.6090826666666667</v>
+        <v>0.6044586666666666</v>
       </c>
       <c r="P43">
-        <v>2.436330666666666</v>
+        <v>2.417834666666666</v>
       </c>
       <c r="Q43">
-        <v>3.526330666666666</v>
+        <v>3.507834666666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1980876389337309</v>
+        <v>0.2003757861643482</v>
       </c>
       <c r="T43">
-        <v>1.824366673637868</v>
+        <v>1.85177808786126</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.212732438743071</v>
+        <v>4.112429285439665</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5064,22 +5064,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1356387559753219</v>
+        <v>0.1354474049797426</v>
       </c>
       <c r="C44">
-        <v>27.43264052324653</v>
+        <v>27.12319099150671</v>
       </c>
       <c r="D44">
-        <v>42.42264052324653</v>
+        <v>42.51319099150671</v>
       </c>
       <c r="E44">
-        <v>-11.6</v>
+        <v>-11.2</v>
       </c>
       <c r="F44">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="G44">
         <v>1.81</v>
@@ -5100,28 +5100,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M44">
-        <v>0.9710400000000001</v>
+        <v>0.99416</v>
       </c>
       <c r="N44">
-        <v>3.022293333333333</v>
+        <v>2.999173333333333</v>
       </c>
       <c r="O44">
-        <v>0.6044586666666666</v>
+        <v>0.5998346666666666</v>
       </c>
       <c r="P44">
-        <v>2.417834666666666</v>
+        <v>2.399338666666667</v>
       </c>
       <c r="Q44">
-        <v>3.507834666666666</v>
+        <v>3.489338666666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2003757861643481</v>
+        <v>0.2027442192627064</v>
       </c>
       <c r="T44">
-        <v>1.85177808786126</v>
+        <v>1.880151306092491</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.112429285439665</v>
+        <v>4.016791395080604</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5146,22 +5146,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1354474049797426</v>
+        <v>0.1364880539841633</v>
       </c>
       <c r="C45">
-        <v>27.12319099150671</v>
+        <v>26.23535044430758</v>
       </c>
       <c r="D45">
-        <v>42.51319099150671</v>
+        <v>42.02535044430758</v>
       </c>
       <c r="E45">
-        <v>-11.2</v>
+        <v>-10.8</v>
       </c>
       <c r="F45">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="G45">
         <v>1.81</v>
@@ -5182,45 +5182,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M45">
-        <v>0.99416</v>
+        <v>1.07888</v>
       </c>
       <c r="N45">
-        <v>2.999173333333333</v>
+        <v>2.914453333333333</v>
       </c>
       <c r="O45">
-        <v>0.5998346666666666</v>
+        <v>0.5828906666666667</v>
       </c>
       <c r="P45">
-        <v>2.399338666666667</v>
+        <v>2.331562666666667</v>
       </c>
       <c r="Q45">
-        <v>3.489338666666666</v>
+        <v>3.421562666666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2027442192627064</v>
+        <v>0.2051972392574345</v>
       </c>
       <c r="T45">
-        <v>1.880151306092491</v>
+        <v>1.909537853546265</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.016791395080604</v>
+        <v>3.701369321271442</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5228,22 +5228,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1364880539841633</v>
+        <v>0.136324702988584</v>
       </c>
       <c r="C46">
-        <v>26.23535044430758</v>
+        <v>25.9111848034163</v>
       </c>
       <c r="D46">
-        <v>42.02535044430758</v>
+        <v>42.1011848034163</v>
       </c>
       <c r="E46">
-        <v>-10.8</v>
+        <v>-10.4</v>
       </c>
       <c r="F46">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="G46">
         <v>1.81</v>
@@ -5264,28 +5264,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M46">
-        <v>1.07888</v>
+        <v>1.1034</v>
       </c>
       <c r="N46">
-        <v>2.914453333333333</v>
+        <v>2.889933333333333</v>
       </c>
       <c r="O46">
-        <v>0.5828906666666667</v>
+        <v>0.5779866666666668</v>
       </c>
       <c r="P46">
-        <v>2.331562666666667</v>
+        <v>2.311946666666667</v>
       </c>
       <c r="Q46">
-        <v>3.421562666666667</v>
+        <v>3.401946666666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2051972392574345</v>
+        <v>0.2077394599792437</v>
       </c>
       <c r="T46">
-        <v>1.909537853546265</v>
+        <v>1.939993002725631</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.701369321271442</v>
+        <v>3.619116669687632</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5310,22 +5310,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.136324702988584</v>
+        <v>0.1361613519930047</v>
       </c>
       <c r="C47">
-        <v>25.9111848034163</v>
+        <v>25.58729334208931</v>
       </c>
       <c r="D47">
-        <v>42.1011848034163</v>
+        <v>42.17729334208931</v>
       </c>
       <c r="E47">
-        <v>-10.4</v>
+        <v>-9.999999999999996</v>
       </c>
       <c r="F47">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="G47">
         <v>1.81</v>
@@ -5346,28 +5346,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M47">
-        <v>1.1034</v>
+        <v>1.12792</v>
       </c>
       <c r="N47">
-        <v>2.889933333333333</v>
+        <v>2.865413333333333</v>
       </c>
       <c r="O47">
-        <v>0.5779866666666668</v>
+        <v>0.5730826666666666</v>
       </c>
       <c r="P47">
-        <v>2.311946666666667</v>
+        <v>2.292330666666667</v>
       </c>
       <c r="Q47">
-        <v>3.401946666666666</v>
+        <v>3.382330666666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2077394599792437</v>
+        <v>0.2103758370240828</v>
       </c>
       <c r="T47">
-        <v>1.939993002725631</v>
+        <v>1.971576120393123</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.619116669687632</v>
+        <v>3.540440220346596</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5392,22 +5392,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1361613519930047</v>
+        <v>0.1370508009974254</v>
       </c>
       <c r="C48">
-        <v>25.58729334208931</v>
+        <v>24.77617857748207</v>
       </c>
       <c r="D48">
-        <v>42.17729334208931</v>
+        <v>41.76617857748207</v>
       </c>
       <c r="E48">
-        <v>-9.999999999999996</v>
+        <v>-9.599999999999998</v>
       </c>
       <c r="F48">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="G48">
         <v>1.81</v>
@@ -5428,45 +5428,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M48">
-        <v>1.12792</v>
+        <v>1.20508</v>
       </c>
       <c r="N48">
-        <v>2.865413333333333</v>
+        <v>2.788253333333333</v>
       </c>
       <c r="O48">
-        <v>0.5730826666666666</v>
+        <v>0.5576506666666666</v>
       </c>
       <c r="P48">
-        <v>2.292330666666667</v>
+        <v>2.230602666666667</v>
       </c>
       <c r="Q48">
-        <v>3.382330666666666</v>
+        <v>3.320602666666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2103758370240828</v>
+        <v>0.2131116999951423</v>
       </c>
       <c r="T48">
-        <v>1.971576120393123</v>
+        <v>2.004351053821651</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.540440220346596</v>
+        <v>3.313749571259446</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5474,22 +5474,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1370508009974254</v>
+        <v>0.1369098500018461</v>
       </c>
       <c r="C49">
-        <v>24.77617857748207</v>
+        <v>24.44079271582078</v>
       </c>
       <c r="D49">
-        <v>41.76617857748207</v>
+        <v>41.83079271582078</v>
       </c>
       <c r="E49">
-        <v>-9.599999999999998</v>
+        <v>-9.199999999999996</v>
       </c>
       <c r="F49">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="G49">
         <v>1.81</v>
@@ -5510,28 +5510,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M49">
-        <v>1.20508</v>
+        <v>1.23072</v>
       </c>
       <c r="N49">
-        <v>2.788253333333333</v>
+        <v>2.762613333333333</v>
       </c>
       <c r="O49">
-        <v>0.5576506666666666</v>
+        <v>0.5525226666666666</v>
       </c>
       <c r="P49">
-        <v>2.230602666666667</v>
+        <v>2.210090666666666</v>
       </c>
       <c r="Q49">
-        <v>3.320602666666666</v>
+        <v>3.300090666666666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2131116999951423</v>
+        <v>0.2159527884650887</v>
       </c>
       <c r="T49">
-        <v>2.004351053821651</v>
+        <v>2.038386561612815</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.313749571259446</v>
+        <v>3.244713121858207</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5556,22 +5556,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1369098500018461</v>
+        <v>0.1367688990062668</v>
       </c>
       <c r="C50">
-        <v>24.44079271582079</v>
+        <v>24.10560708582607</v>
       </c>
       <c r="D50">
-        <v>41.83079271582078</v>
+        <v>41.89560708582607</v>
       </c>
       <c r="E50">
-        <v>-9.199999999999999</v>
+        <v>-8.799999999999997</v>
       </c>
       <c r="F50">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="G50">
         <v>1.81</v>
@@ -5592,28 +5592,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M50">
-        <v>1.23072</v>
+        <v>1.25636</v>
       </c>
       <c r="N50">
-        <v>2.762613333333333</v>
+        <v>2.736973333333333</v>
       </c>
       <c r="O50">
-        <v>0.5525226666666667</v>
+        <v>0.5473946666666667</v>
       </c>
       <c r="P50">
-        <v>2.210090666666667</v>
+        <v>2.189578666666667</v>
       </c>
       <c r="Q50">
-        <v>3.300090666666667</v>
+        <v>3.279578666666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2159527884650887</v>
+        <v>0.2189052921691506</v>
       </c>
       <c r="T50">
-        <v>2.038386561612815</v>
+        <v>2.073756795199711</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.244713121858207</v>
+        <v>3.178494486718244</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5638,22 +5638,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1367688990062668</v>
+        <v>0.1366279480106875</v>
       </c>
       <c r="C51">
-        <v>24.10560708582607</v>
+        <v>23.77062261968413</v>
       </c>
       <c r="D51">
-        <v>41.89560708582607</v>
+        <v>41.96062261968413</v>
       </c>
       <c r="E51">
-        <v>-8.799999999999997</v>
+        <v>-8.399999999999999</v>
       </c>
       <c r="F51">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="G51">
         <v>1.81</v>
@@ -5674,28 +5674,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M51">
-        <v>1.25636</v>
+        <v>1.282</v>
       </c>
       <c r="N51">
-        <v>2.736973333333333</v>
+        <v>2.711333333333333</v>
       </c>
       <c r="O51">
-        <v>0.5473946666666667</v>
+        <v>0.5422666666666667</v>
       </c>
       <c r="P51">
-        <v>2.189578666666667</v>
+        <v>2.169066666666667</v>
       </c>
       <c r="Q51">
-        <v>3.279578666666667</v>
+        <v>3.259066666666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2189052921691506</v>
+        <v>0.221975896021375</v>
       </c>
       <c r="T51">
-        <v>2.073756795199711</v>
+        <v>2.110541838130083</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.178494486718244</v>
+        <v>3.114924596983879</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5720,22 +5720,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1366279480106875</v>
+        <v>0.1364869970151082</v>
       </c>
       <c r="C52">
-        <v>23.77062261968413</v>
+        <v>23.43584025537658</v>
       </c>
       <c r="D52">
-        <v>41.96062261968413</v>
+        <v>42.02584025537657</v>
       </c>
       <c r="E52">
-        <v>-8.399999999999999</v>
+        <v>-8</v>
       </c>
       <c r="F52">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="G52">
         <v>1.81</v>
@@ -5756,28 +5756,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M52">
-        <v>1.282</v>
+        <v>1.30764</v>
       </c>
       <c r="N52">
-        <v>2.711333333333333</v>
+        <v>2.685693333333333</v>
       </c>
       <c r="O52">
-        <v>0.5422666666666667</v>
+        <v>0.5371386666666667</v>
       </c>
       <c r="P52">
-        <v>2.169066666666667</v>
+        <v>2.148554666666667</v>
       </c>
       <c r="Q52">
-        <v>3.259066666666667</v>
+        <v>3.238554666666666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.221975896021375</v>
+        <v>0.2251718306430779</v>
       </c>
       <c r="T52">
-        <v>2.110541838130083</v>
+        <v>2.148828311384143</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.114924596983879</v>
+        <v>3.053847644101842</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5802,22 +5802,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1364869970151082</v>
+        <v>0.1395908460195289</v>
       </c>
       <c r="C53">
-        <v>23.43584025537658</v>
+        <v>21.64506633689167</v>
       </c>
       <c r="D53">
-        <v>42.02584025537657</v>
+        <v>40.63506633689167</v>
       </c>
       <c r="E53">
-        <v>-8</v>
+        <v>-7.599999999999998</v>
       </c>
       <c r="F53">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="G53">
         <v>1.81</v>
@@ -5838,45 +5838,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M53">
-        <v>1.30764</v>
+        <v>1.49552</v>
       </c>
       <c r="N53">
-        <v>2.685693333333333</v>
+        <v>2.497813333333333</v>
       </c>
       <c r="O53">
-        <v>0.5371386666666667</v>
+        <v>0.4995626666666667</v>
       </c>
       <c r="P53">
-        <v>2.148554666666667</v>
+        <v>1.998250666666667</v>
       </c>
       <c r="Q53">
-        <v>3.238554666666666</v>
+        <v>3.088250666666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2251718306430779</v>
+        <v>0.2285009292073518</v>
       </c>
       <c r="T53">
-        <v>2.148828311384143</v>
+        <v>2.188710054357123</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.053847644101842</v>
+        <v>2.670197211226419</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5884,22 +5884,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1395908460195289</v>
+        <v>0.1395122950239496</v>
       </c>
       <c r="C54">
-        <v>21.64506633689167</v>
+        <v>21.27912723482805</v>
       </c>
       <c r="D54">
-        <v>40.63506633689167</v>
+        <v>40.66912723482805</v>
       </c>
       <c r="E54">
-        <v>-7.599999999999998</v>
+        <v>-7.199999999999996</v>
       </c>
       <c r="F54">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="G54">
         <v>1.81</v>
@@ -5920,28 +5920,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M54">
-        <v>1.49552</v>
+        <v>1.52428</v>
       </c>
       <c r="N54">
-        <v>2.497813333333333</v>
+        <v>2.469053333333333</v>
       </c>
       <c r="O54">
-        <v>0.4995626666666667</v>
+        <v>0.4938106666666666</v>
       </c>
       <c r="P54">
-        <v>1.998250666666667</v>
+        <v>1.975242666666666</v>
       </c>
       <c r="Q54">
-        <v>3.088250666666666</v>
+        <v>3.065242666666666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2285009292073518</v>
+        <v>0.2319716915403182</v>
       </c>
       <c r="T54">
-        <v>2.188710054357123</v>
+        <v>2.230288892775761</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.670197211226419</v>
+        <v>2.619816131769316</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5966,22 +5966,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1395122950239496</v>
+        <v>0.1394337440283703</v>
       </c>
       <c r="C55">
-        <v>21.27912723482805</v>
+        <v>20.91324528133774</v>
       </c>
       <c r="D55">
-        <v>40.66912723482805</v>
+        <v>40.70324528133774</v>
       </c>
       <c r="E55">
-        <v>-7.199999999999996</v>
+        <v>-6.799999999999997</v>
       </c>
       <c r="F55">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="G55">
         <v>1.81</v>
@@ -6002,28 +6002,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M55">
-        <v>1.52428</v>
+        <v>1.55304</v>
       </c>
       <c r="N55">
-        <v>2.469053333333333</v>
+        <v>2.440293333333333</v>
       </c>
       <c r="O55">
-        <v>0.4938106666666666</v>
+        <v>0.4880586666666666</v>
       </c>
       <c r="P55">
-        <v>1.975242666666666</v>
+        <v>1.952234666666666</v>
       </c>
       <c r="Q55">
-        <v>3.065242666666666</v>
+        <v>3.042234666666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2319716915403182</v>
+        <v>0.2355933565834137</v>
       </c>
       <c r="T55">
-        <v>2.230288892775761</v>
+        <v>2.273675506777819</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.619816131769316</v>
+        <v>2.571301018218032</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6048,22 +6048,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1394337440283703</v>
+        <v>0.139355193032791</v>
       </c>
       <c r="C56">
-        <v>20.91324528133774</v>
+        <v>20.54742062037037</v>
       </c>
       <c r="D56">
-        <v>40.70324528133774</v>
+        <v>40.73742062037037</v>
       </c>
       <c r="E56">
-        <v>-6.799999999999997</v>
+        <v>-6.399999999999999</v>
       </c>
       <c r="F56">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="G56">
         <v>1.81</v>
@@ -6084,28 +6084,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M56">
-        <v>1.55304</v>
+        <v>1.5818</v>
       </c>
       <c r="N56">
-        <v>2.440293333333333</v>
+        <v>2.411533333333333</v>
       </c>
       <c r="O56">
-        <v>0.4880586666666666</v>
+        <v>0.4823066666666666</v>
       </c>
       <c r="P56">
-        <v>1.952234666666666</v>
+        <v>1.929226666666666</v>
       </c>
       <c r="Q56">
-        <v>3.042234666666666</v>
+        <v>3.019226666666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2355933565834137</v>
+        <v>0.2393759845173133</v>
       </c>
       <c r="T56">
-        <v>2.273675506777819</v>
+        <v>2.318990414735523</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.571301018218032</v>
+        <v>2.524550090614068</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6130,22 +6130,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.139355193032791</v>
+        <v>0.1410238420372117</v>
       </c>
       <c r="C57">
-        <v>20.54742062037037</v>
+        <v>19.43356099334246</v>
       </c>
       <c r="D57">
-        <v>40.73742062037037</v>
+        <v>40.02356099334246</v>
       </c>
       <c r="E57">
-        <v>-6.399999999999999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="F57">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="G57">
         <v>1.81</v>
@@ -6166,45 +6166,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M57">
-        <v>1.5818</v>
+        <v>1.69792</v>
       </c>
       <c r="N57">
-        <v>2.411533333333333</v>
+        <v>2.295413333333333</v>
       </c>
       <c r="O57">
-        <v>0.4823066666666666</v>
+        <v>0.4590826666666666</v>
       </c>
       <c r="P57">
-        <v>1.929226666666666</v>
+        <v>1.836330666666666</v>
       </c>
       <c r="Q57">
-        <v>3.019226666666666</v>
+        <v>2.926330666666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2393759845173133</v>
+        <v>0.243330550084572</v>
       </c>
       <c r="T57">
-        <v>2.318990414735523</v>
+        <v>2.36636509123676</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.524550090614068</v>
+        <v>2.351897223269254</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6212,22 +6212,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1410238420372117</v>
+        <v>0.1409764910416323</v>
       </c>
       <c r="C58">
-        <v>19.43356099334246</v>
+        <v>19.05347300563586</v>
       </c>
       <c r="D58">
-        <v>40.02356099334246</v>
+        <v>40.04347300563586</v>
       </c>
       <c r="E58">
-        <v>-5.999999999999996</v>
+        <v>-5.599999999999994</v>
       </c>
       <c r="F58">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="G58">
         <v>1.81</v>
@@ -6248,28 +6248,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M58">
-        <v>1.69792</v>
+        <v>1.72824</v>
       </c>
       <c r="N58">
-        <v>2.295413333333333</v>
+        <v>2.265093333333333</v>
       </c>
       <c r="O58">
-        <v>0.4590826666666666</v>
+        <v>0.4530186666666666</v>
       </c>
       <c r="P58">
-        <v>1.836330666666666</v>
+        <v>1.812074666666666</v>
       </c>
       <c r="Q58">
-        <v>2.926330666666666</v>
+        <v>2.902074666666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.243330550084572</v>
+        <v>0.2474690489340288</v>
       </c>
       <c r="T58">
-        <v>2.36636509123676</v>
+        <v>2.415943241063635</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.351897223269254</v>
+        <v>2.310635868475057</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6294,22 +6294,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1409764910416323</v>
+        <v>0.1409291400460531</v>
       </c>
       <c r="C59">
-        <v>19.05347300563586</v>
+        <v>18.67340484053263</v>
       </c>
       <c r="D59">
-        <v>40.04347300563586</v>
+        <v>40.06340484053263</v>
       </c>
       <c r="E59">
-        <v>-5.599999999999994</v>
+        <v>-5.199999999999996</v>
       </c>
       <c r="F59">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="G59">
         <v>1.81</v>
@@ -6330,28 +6330,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M59">
-        <v>1.72824</v>
+        <v>1.75856</v>
       </c>
       <c r="N59">
-        <v>2.265093333333333</v>
+        <v>2.234773333333333</v>
       </c>
       <c r="O59">
-        <v>0.4530186666666666</v>
+        <v>0.4469546666666666</v>
       </c>
       <c r="P59">
-        <v>1.812074666666666</v>
+        <v>1.787818666666666</v>
       </c>
       <c r="Q59">
-        <v>2.902074666666666</v>
+        <v>2.877818666666666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2474690489340288</v>
+        <v>0.2518046191572692</v>
       </c>
       <c r="T59">
-        <v>2.415943241063635</v>
+        <v>2.467882255167981</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.310635868475057</v>
+        <v>2.270797319018591</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6376,22 +6376,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.140929140046053</v>
+        <v>0.1408817890504737</v>
       </c>
       <c r="C60">
-        <v>18.67340484053264</v>
+        <v>18.29335652764792</v>
       </c>
       <c r="D60">
-        <v>40.06340484053264</v>
+        <v>40.08335652764791</v>
       </c>
       <c r="E60">
-        <v>-5.199999999999999</v>
+        <v>-4.800000000000001</v>
       </c>
       <c r="F60">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="G60">
         <v>1.81</v>
@@ -6412,28 +6412,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M60">
-        <v>1.75856</v>
+        <v>1.78888</v>
       </c>
       <c r="N60">
-        <v>2.234773333333333</v>
+        <v>2.204453333333333</v>
       </c>
       <c r="O60">
-        <v>0.4469546666666666</v>
+        <v>0.4408906666666667</v>
       </c>
       <c r="P60">
-        <v>1.787818666666666</v>
+        <v>1.763562666666667</v>
       </c>
       <c r="Q60">
-        <v>2.877818666666666</v>
+        <v>2.853562666666666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2518046191572691</v>
+        <v>0.2563516806109116</v>
       </c>
       <c r="T60">
-        <v>2.46788225516798</v>
+        <v>2.52235487971644</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.270797319018591</v>
+        <v>2.232309228865733</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6458,22 +6458,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1408817890504737</v>
+        <v>0.1408344380548945</v>
       </c>
       <c r="C61">
-        <v>18.29335652764792</v>
+        <v>17.91332809665585</v>
       </c>
       <c r="D61">
-        <v>40.08335652764791</v>
+        <v>40.10332809665584</v>
       </c>
       <c r="E61">
-        <v>-4.800000000000001</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="F61">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="G61">
         <v>1.81</v>
@@ -6494,28 +6494,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M61">
-        <v>1.78888</v>
+        <v>1.8192</v>
       </c>
       <c r="N61">
-        <v>2.204453333333333</v>
+        <v>2.174133333333333</v>
       </c>
       <c r="O61">
-        <v>0.4408906666666667</v>
+        <v>0.4348266666666666</v>
       </c>
       <c r="P61">
-        <v>1.763562666666667</v>
+        <v>1.739306666666666</v>
       </c>
       <c r="Q61">
-        <v>2.853562666666666</v>
+        <v>2.829306666666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2563516806109116</v>
+        <v>0.2611260951372361</v>
       </c>
       <c r="T61">
-        <v>2.52235487971644</v>
+        <v>2.579551135492324</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.232309228865733</v>
+        <v>2.195104075051304</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6540,22 +6540,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1408344380548945</v>
+        <v>0.1407870870593151</v>
       </c>
       <c r="C62">
-        <v>17.91332809665585</v>
+        <v>17.5333195772898</v>
       </c>
       <c r="D62">
-        <v>40.10332809665584</v>
+        <v>40.12331957728979</v>
       </c>
       <c r="E62">
-        <v>-4.399999999999999</v>
+        <v>-4</v>
       </c>
       <c r="F62">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="G62">
         <v>1.81</v>
@@ -6576,28 +6576,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M62">
-        <v>1.8192</v>
+        <v>1.84952</v>
       </c>
       <c r="N62">
-        <v>2.174133333333333</v>
+        <v>2.143813333333333</v>
       </c>
       <c r="O62">
-        <v>0.4348266666666666</v>
+        <v>0.4287626666666666</v>
       </c>
       <c r="P62">
-        <v>1.739306666666666</v>
+        <v>1.715050666666667</v>
       </c>
       <c r="Q62">
-        <v>2.829306666666666</v>
+        <v>2.805050666666666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2611260951372361</v>
+        <v>0.2661453514341413</v>
       </c>
       <c r="T62">
-        <v>2.579551135492324</v>
+        <v>2.639680532590046</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.195104075051304</v>
+        <v>2.159118762345545</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6622,22 +6622,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1407870870593151</v>
+        <v>0.1407397360637358</v>
       </c>
       <c r="C63">
-        <v>17.5333195772898</v>
+        <v>17.15333099934237</v>
       </c>
       <c r="D63">
-        <v>40.12331957728979</v>
+        <v>40.14333099934237</v>
       </c>
       <c r="E63">
-        <v>-4</v>
+        <v>-3.599999999999998</v>
       </c>
       <c r="F63">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="G63">
         <v>1.81</v>
@@ -6658,28 +6658,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M63">
-        <v>1.84952</v>
+        <v>1.87984</v>
       </c>
       <c r="N63">
-        <v>2.143813333333333</v>
+        <v>2.113493333333333</v>
       </c>
       <c r="O63">
-        <v>0.4287626666666666</v>
+        <v>0.4226986666666666</v>
       </c>
       <c r="P63">
-        <v>1.715050666666667</v>
+        <v>1.690794666666666</v>
       </c>
       <c r="Q63">
-        <v>2.805050666666666</v>
+        <v>2.780794666666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2661453514341413</v>
+        <v>0.2714287791150943</v>
       </c>
       <c r="T63">
-        <v>2.639680532590046</v>
+        <v>2.702974634798176</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.159118762345545</v>
+        <v>2.124294266178682</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6704,22 +6704,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1407397360637358</v>
+        <v>0.1406923850681565</v>
       </c>
       <c r="C64">
-        <v>17.15333099934237</v>
+        <v>16.77336239266569</v>
       </c>
       <c r="D64">
-        <v>40.14333099934237</v>
+        <v>40.16336239266569</v>
       </c>
       <c r="E64">
-        <v>-3.599999999999998</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="F64">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="G64">
         <v>1.81</v>
@@ -6740,28 +6740,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M64">
-        <v>1.87984</v>
+        <v>1.91016</v>
       </c>
       <c r="N64">
-        <v>2.113493333333333</v>
+        <v>2.083173333333333</v>
       </c>
       <c r="O64">
-        <v>0.4226986666666666</v>
+        <v>0.4166346666666666</v>
       </c>
       <c r="P64">
-        <v>1.690794666666666</v>
+        <v>1.666538666666666</v>
       </c>
       <c r="Q64">
-        <v>2.780794666666666</v>
+        <v>2.756538666666666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2714287791150943</v>
+        <v>0.2769977974815041</v>
       </c>
       <c r="T64">
-        <v>2.702974634798176</v>
+        <v>2.769690039828367</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.124294266178682</v>
+        <v>2.090575309572671</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6786,22 +6786,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1406923850681565</v>
+        <v>0.1406450340725772</v>
       </c>
       <c r="C65">
-        <v>16.77336239266569</v>
+        <v>16.39341378717148</v>
       </c>
       <c r="D65">
-        <v>40.16336239266569</v>
+        <v>40.18341378717147</v>
       </c>
       <c r="E65">
-        <v>-3.199999999999999</v>
+        <v>-2.799999999999997</v>
       </c>
       <c r="F65">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="G65">
         <v>1.81</v>
@@ -6822,28 +6822,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M65">
-        <v>1.91016</v>
+        <v>1.94048</v>
       </c>
       <c r="N65">
-        <v>2.083173333333333</v>
+        <v>2.052853333333333</v>
       </c>
       <c r="O65">
-        <v>0.4166346666666666</v>
+        <v>0.4105706666666666</v>
       </c>
       <c r="P65">
-        <v>1.666538666666666</v>
+        <v>1.642282666666667</v>
       </c>
       <c r="Q65">
-        <v>2.756538666666666</v>
+        <v>2.732282666666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2769977974815041</v>
+        <v>0.2828762057571589</v>
       </c>
       <c r="T65">
-        <v>2.769690039828367</v>
+        <v>2.840111856249124</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.090575309572671</v>
+        <v>2.057910070360598</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6868,22 +6868,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1406450340725772</v>
+        <v>0.1405976830769979</v>
       </c>
       <c r="C66">
-        <v>16.39341378717148</v>
+        <v>16.01348521283126</v>
       </c>
       <c r="D66">
-        <v>40.18341378717147</v>
+        <v>40.20348521283125</v>
       </c>
       <c r="E66">
-        <v>-2.799999999999997</v>
+        <v>-2.399999999999999</v>
       </c>
       <c r="F66">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="G66">
         <v>1.81</v>
@@ -6904,28 +6904,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M66">
-        <v>1.94048</v>
+        <v>1.9708</v>
       </c>
       <c r="N66">
-        <v>2.052853333333333</v>
+        <v>2.022533333333333</v>
       </c>
       <c r="O66">
-        <v>0.4105706666666666</v>
+        <v>0.4045066666666666</v>
       </c>
       <c r="P66">
-        <v>1.642282666666667</v>
+        <v>1.618026666666667</v>
       </c>
       <c r="Q66">
-        <v>2.732282666666666</v>
+        <v>2.708026666666666</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2828762057571589</v>
+        <v>0.2890905230771369</v>
       </c>
       <c r="T66">
-        <v>2.840111856249124</v>
+        <v>2.914557776465352</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.057910070360598</v>
+        <v>2.026249915431973</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6950,22 +6950,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1405976830769979</v>
+        <v>0.1480479320814186</v>
       </c>
       <c r="C67">
-        <v>16.01348521283126</v>
+        <v>12.68407657263861</v>
       </c>
       <c r="D67">
-        <v>40.20348521283125</v>
+        <v>37.27407657263861</v>
       </c>
       <c r="E67">
-        <v>-2.399999999999999</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="F67">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="G67">
         <v>1.81</v>
@@ -6986,45 +6986,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M67">
-        <v>1.9708</v>
+        <v>2.376</v>
       </c>
       <c r="N67">
-        <v>2.022533333333333</v>
+        <v>1.617333333333333</v>
       </c>
       <c r="O67">
-        <v>0.4045066666666666</v>
+        <v>0.3234666666666667</v>
       </c>
       <c r="P67">
-        <v>1.618026666666667</v>
+        <v>1.293866666666667</v>
       </c>
       <c r="Q67">
-        <v>2.708026666666666</v>
+        <v>2.383866666666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2890905230771369</v>
+        <v>0.2956703884747606</v>
       </c>
       <c r="T67">
-        <v>2.914557776465352</v>
+        <v>2.993382868459006</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.026249915431973</v>
+        <v>1.680695847362514</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7032,22 +7032,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1480479320814186</v>
+        <v>0.1481141810858393</v>
       </c>
       <c r="C68">
-        <v>12.68407657263861</v>
+        <v>12.25994139961145</v>
       </c>
       <c r="D68">
-        <v>37.27407657263861</v>
+        <v>37.24994139961145</v>
       </c>
       <c r="E68">
-        <v>-1.999999999999996</v>
+        <v>-1.599999999999998</v>
       </c>
       <c r="F68">
-        <v>26.4</v>
+        <v>26.8</v>
       </c>
       <c r="G68">
         <v>1.81</v>
@@ -7068,28 +7068,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M68">
-        <v>2.376</v>
+        <v>2.412</v>
       </c>
       <c r="N68">
-        <v>1.617333333333333</v>
+        <v>1.581333333333333</v>
       </c>
       <c r="O68">
-        <v>0.3234666666666667</v>
+        <v>0.3162666666666667</v>
       </c>
       <c r="P68">
-        <v>1.293866666666667</v>
+        <v>1.265066666666667</v>
       </c>
       <c r="Q68">
-        <v>2.383866666666667</v>
+        <v>2.355066666666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2956703884747606</v>
+        <v>0.3026490335934525</v>
       </c>
       <c r="T68">
-        <v>2.993382868459006</v>
+        <v>3.076985238755306</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.680695847362514</v>
+        <v>1.655610834715312</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7114,22 +7114,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1481141810858393</v>
+        <v>0.14818043009026</v>
       </c>
       <c r="C69">
-        <v>12.25994139961145</v>
+        <v>11.83583746167842</v>
       </c>
       <c r="D69">
-        <v>37.24994139961145</v>
+        <v>37.22583746167842</v>
       </c>
       <c r="E69">
-        <v>-1.599999999999998</v>
+        <v>-1.199999999999996</v>
       </c>
       <c r="F69">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
       <c r="G69">
         <v>1.81</v>
@@ -7150,28 +7150,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M69">
-        <v>2.412</v>
+        <v>2.448</v>
       </c>
       <c r="N69">
-        <v>1.581333333333333</v>
+        <v>1.545333333333333</v>
       </c>
       <c r="O69">
-        <v>0.3162666666666667</v>
+        <v>0.3090666666666667</v>
       </c>
       <c r="P69">
-        <v>1.265066666666667</v>
+        <v>1.236266666666667</v>
       </c>
       <c r="Q69">
-        <v>2.355066666666667</v>
+        <v>2.326266666666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3026490335934525</v>
+        <v>0.3100638440320625</v>
       </c>
       <c r="T69">
-        <v>3.076985238755306</v>
+        <v>3.165812757195124</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.655610834715312</v>
+        <v>1.631263616557734</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7196,22 +7196,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.14818043009026</v>
+        <v>0.1482466790946807</v>
       </c>
       <c r="C70">
-        <v>11.83583746167842</v>
+        <v>11.41176469824326</v>
       </c>
       <c r="D70">
-        <v>37.22583746167842</v>
+        <v>37.20176469824326</v>
       </c>
       <c r="E70">
-        <v>-1.199999999999996</v>
+        <v>-0.7999999999999972</v>
       </c>
       <c r="F70">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="G70">
         <v>1.81</v>
@@ -7232,28 +7232,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M70">
-        <v>2.448</v>
+        <v>2.484</v>
       </c>
       <c r="N70">
-        <v>1.545333333333333</v>
+        <v>1.509333333333333</v>
       </c>
       <c r="O70">
-        <v>0.3090666666666667</v>
+        <v>0.3018666666666667</v>
       </c>
       <c r="P70">
-        <v>1.236266666666667</v>
+        <v>1.207466666666666</v>
       </c>
       <c r="Q70">
-        <v>2.326266666666666</v>
+        <v>2.297466666666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3100638440320625</v>
+        <v>0.3179570293376797</v>
       </c>
       <c r="T70">
-        <v>3.165812757195124</v>
+        <v>3.260371083276222</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.631263616557734</v>
+        <v>1.607622114868492</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7278,22 +7278,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1482466790946807</v>
+        <v>0.1483129280991014</v>
       </c>
       <c r="C71">
-        <v>11.41176469824326</v>
+        <v>10.98772304886642</v>
       </c>
       <c r="D71">
-        <v>37.20176469824326</v>
+        <v>37.17772304886643</v>
       </c>
       <c r="E71">
-        <v>-0.7999999999999972</v>
+        <v>-0.399999999999995</v>
       </c>
       <c r="F71">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="G71">
         <v>1.81</v>
@@ -7314,28 +7314,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M71">
-        <v>2.484</v>
+        <v>2.52</v>
       </c>
       <c r="N71">
-        <v>1.509333333333333</v>
+        <v>1.473333333333333</v>
       </c>
       <c r="O71">
-        <v>0.3018666666666667</v>
+        <v>0.2946666666666666</v>
       </c>
       <c r="P71">
-        <v>1.207466666666666</v>
+        <v>1.178666666666667</v>
       </c>
       <c r="Q71">
-        <v>2.297466666666666</v>
+        <v>2.268666666666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3179570293376797</v>
+        <v>0.3263764269970046</v>
       </c>
       <c r="T71">
-        <v>3.260371083276222</v>
+        <v>3.361233297762725</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.607622114868492</v>
+        <v>1.584656084656085</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7360,22 +7360,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1483129280991014</v>
+        <v>0.1483791771035221</v>
       </c>
       <c r="C72">
-        <v>10.98772304886642</v>
+        <v>10.56371245326445</v>
       </c>
       <c r="D72">
-        <v>37.17772304886643</v>
+        <v>37.15371245326445</v>
       </c>
       <c r="E72">
-        <v>-0.399999999999995</v>
+        <v>3.552713678800501E-15</v>
       </c>
       <c r="F72">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="G72">
         <v>1.81</v>
@@ -7396,28 +7396,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M72">
-        <v>2.52</v>
+        <v>2.556</v>
       </c>
       <c r="N72">
-        <v>1.473333333333333</v>
+        <v>1.437333333333333</v>
       </c>
       <c r="O72">
-        <v>0.2946666666666666</v>
+        <v>0.2874666666666666</v>
       </c>
       <c r="P72">
-        <v>1.178666666666667</v>
+        <v>1.149866666666667</v>
       </c>
       <c r="Q72">
-        <v>2.268666666666666</v>
+        <v>2.239866666666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3263764269970046</v>
+        <v>0.3353764727707659</v>
       </c>
       <c r="T72">
-        <v>3.361233297762725</v>
+        <v>3.469051527041402</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.584656084656085</v>
+        <v>1.562336984872196</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7442,22 +7442,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1483791771035221</v>
+        <v>0.1484454261079428</v>
       </c>
       <c r="C73">
-        <v>10.56371245326446</v>
+        <v>10.13973285130955</v>
       </c>
       <c r="D73">
-        <v>37.15371245326445</v>
+        <v>37.12973285130954</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="F73">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="G73">
         <v>1.81</v>
@@ -7478,28 +7478,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M73">
-        <v>2.556</v>
+        <v>2.592</v>
       </c>
       <c r="N73">
-        <v>1.437333333333334</v>
+        <v>1.401333333333334</v>
       </c>
       <c r="O73">
-        <v>0.2874666666666667</v>
+        <v>0.2802666666666667</v>
       </c>
       <c r="P73">
-        <v>1.149866666666667</v>
+        <v>1.121066666666667</v>
       </c>
       <c r="Q73">
-        <v>2.239866666666667</v>
+        <v>2.211066666666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3353764727707658</v>
+        <v>0.3450193789569385</v>
       </c>
       <c r="T73">
-        <v>3.4690515270414</v>
+        <v>3.58457105841141</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.562336984872196</v>
+        <v>1.540637860082305</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7524,22 +7524,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1484454261079428</v>
+        <v>0.1485116751123635</v>
       </c>
       <c r="C74">
-        <v>10.13973285130955</v>
+        <v>9.715784183028997</v>
       </c>
       <c r="D74">
-        <v>37.12973285130954</v>
+        <v>37.10578418302899</v>
       </c>
       <c r="E74">
-        <v>0.3999999999999986</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="F74">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="G74">
         <v>1.81</v>
@@ -7560,28 +7560,28 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M74">
-        <v>2.592</v>
+        <v>2.628</v>
       </c>
       <c r="N74">
-        <v>1.401333333333334</v>
+        <v>1.365333333333334</v>
       </c>
       <c r="O74">
-        <v>0.2802666666666667</v>
+        <v>0.2730666666666667</v>
       </c>
       <c r="P74">
-        <v>1.121066666666667</v>
+        <v>1.092266666666667</v>
       </c>
       <c r="Q74">
-        <v>2.211066666666667</v>
+        <v>2.182266666666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3450193789569385</v>
+        <v>0.355376574490235</v>
       </c>
       <c r="T74">
-        <v>3.58457105841141</v>
+        <v>3.708647592105124</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.540637860082305</v>
+        <v>1.519533231861999</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7606,22 +7606,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1485116751123635</v>
+        <v>0.1851365188668549</v>
       </c>
       <c r="C75">
-        <v>9.715784183028997</v>
+        <v>-0.4375350411287684</v>
       </c>
       <c r="D75">
-        <v>37.10578418302899</v>
+        <v>27.35246495887123</v>
       </c>
       <c r="E75">
-        <v>0.8000000000000007</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="F75">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="G75">
         <v>1.81</v>
@@ -7642,45 +7642,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M75">
-        <v>2.628</v>
+        <v>4.345280000000001</v>
       </c>
       <c r="N75">
-        <v>1.365333333333334</v>
+        <v>-0.3519466666666675</v>
       </c>
       <c r="O75">
-        <v>0.2730666666666667</v>
+        <v>-0.07038933333333351</v>
       </c>
       <c r="P75">
-        <v>1.092266666666667</v>
+        <v>-0.281557333333334</v>
       </c>
       <c r="Q75">
-        <v>2.182266666666667</v>
+        <v>0.8084426666666659</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.355376574490235</v>
+        <v>0.3710430212827751</v>
       </c>
       <c r="T75">
-        <v>3.708647592105124</v>
+        <v>3.896327587820787</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2</v>
+        <v>0.1838009671797138</v>
       </c>
       <c r="W75">
-        <v>0.07199999999999999</v>
+        <v>0.119818018018018</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.519533231861999</v>
+        <v>0.9190048358985687</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7688,22 +7688,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1851365188668549</v>
+        <v>0.1861465188668549</v>
       </c>
       <c r="C76">
-        <v>-0.4375350411287684</v>
+        <v>-1.034376329616077</v>
       </c>
       <c r="D76">
-        <v>27.35246495887123</v>
+        <v>27.15562367038392</v>
       </c>
       <c r="E76">
-        <v>1.200000000000003</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="F76">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="G76">
         <v>1.81</v>
@@ -7724,37 +7724,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M76">
-        <v>4.345280000000001</v>
+        <v>4.404000000000001</v>
       </c>
       <c r="N76">
-        <v>-0.3519466666666675</v>
+        <v>-0.4106666666666676</v>
       </c>
       <c r="O76">
-        <v>-0.07038933333333351</v>
+        <v>-0.08213333333333353</v>
       </c>
       <c r="P76">
-        <v>-0.281557333333334</v>
+        <v>-0.3285333333333341</v>
       </c>
       <c r="Q76">
-        <v>0.8084426666666659</v>
+        <v>0.7614666666666657</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3710430212827751</v>
+        <v>0.3840527421340861</v>
       </c>
       <c r="T76">
-        <v>3.896327587820787</v>
+        <v>4.052180691333619</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1838009671797138</v>
+        <v>0.1813502876173176</v>
       </c>
       <c r="W76">
-        <v>0.119818018018018</v>
+        <v>0.1201777777777778</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9190048358985687</v>
+        <v>0.9067514380865878</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7770,22 +7770,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1861465188668549</v>
+        <v>0.1871565188668549</v>
       </c>
       <c r="C77">
-        <v>-1.034376329616077</v>
+        <v>-1.628404734722182</v>
       </c>
       <c r="D77">
-        <v>27.15562367038392</v>
+        <v>26.96159526527782</v>
       </c>
       <c r="E77">
-        <v>1.600000000000001</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="G77">
         <v>1.81</v>
@@ -7806,37 +7806,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M77">
-        <v>4.404000000000001</v>
+        <v>4.46272</v>
       </c>
       <c r="N77">
-        <v>-0.4106666666666676</v>
+        <v>-0.4693866666666668</v>
       </c>
       <c r="O77">
-        <v>-0.08213333333333353</v>
+        <v>-0.09387733333333337</v>
       </c>
       <c r="P77">
-        <v>-0.3285333333333341</v>
+        <v>-0.3755093333333335</v>
       </c>
       <c r="Q77">
-        <v>0.7614666666666657</v>
+        <v>0.7144906666666664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3840527421340861</v>
+        <v>0.398146606389673</v>
       </c>
       <c r="T77">
-        <v>4.052180691333619</v>
+        <v>4.221021553472519</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1813502876173176</v>
+        <v>0.1789640996223529</v>
       </c>
       <c r="W77">
-        <v>0.1201777777777778</v>
+        <v>0.1205280701754386</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9067514380865878</v>
+        <v>0.8948204981117643</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7852,22 +7852,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1871565188668549</v>
+        <v>0.1881665188668549</v>
       </c>
       <c r="C78">
-        <v>-1.628404734722182</v>
+        <v>-2.219680123308446</v>
       </c>
       <c r="D78">
-        <v>26.96159526527782</v>
+        <v>26.77031987669156</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>2.400000000000002</v>
       </c>
       <c r="F78">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="G78">
         <v>1.81</v>
@@ -7888,37 +7888,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M78">
-        <v>4.46272</v>
+        <v>4.52144</v>
       </c>
       <c r="N78">
-        <v>-0.4693866666666668</v>
+        <v>-0.5281066666666669</v>
       </c>
       <c r="O78">
-        <v>-0.09387733333333337</v>
+        <v>-0.1056213333333334</v>
       </c>
       <c r="P78">
-        <v>-0.3755093333333335</v>
+        <v>-0.4224853333333335</v>
       </c>
       <c r="Q78">
-        <v>0.7144906666666664</v>
+        <v>0.6675146666666663</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.398146606389673</v>
+        <v>0.4134660240587892</v>
       </c>
       <c r="T78">
-        <v>4.221021553472519</v>
+        <v>4.404544229710455</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1789640996223529</v>
+        <v>0.1766398905363483</v>
       </c>
       <c r="W78">
-        <v>0.1205280701754386</v>
+        <v>0.1208692640692641</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8948204981117643</v>
+        <v>0.8831994526817415</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7934,22 +7934,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1881665188668549</v>
+        <v>0.1891765188668549</v>
       </c>
       <c r="C79">
-        <v>-2.219680123308446</v>
+        <v>-2.808260675334317</v>
       </c>
       <c r="D79">
-        <v>26.77031987669156</v>
+        <v>26.58173932466569</v>
       </c>
       <c r="E79">
-        <v>2.400000000000002</v>
+        <v>2.800000000000004</v>
       </c>
       <c r="F79">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="G79">
         <v>1.81</v>
@@ -7970,37 +7970,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M79">
-        <v>4.52144</v>
+        <v>4.580160000000001</v>
       </c>
       <c r="N79">
-        <v>-0.5281066666666669</v>
+        <v>-0.5868266666666679</v>
       </c>
       <c r="O79">
-        <v>-0.1056213333333334</v>
+        <v>-0.1173653333333336</v>
       </c>
       <c r="P79">
-        <v>-0.4224853333333335</v>
+        <v>-0.4694613333333343</v>
       </c>
       <c r="Q79">
-        <v>0.6675146666666663</v>
+        <v>0.6205386666666655</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4134660240587892</v>
+        <v>0.4301781160614616</v>
       </c>
       <c r="T79">
-        <v>4.404544229710455</v>
+        <v>4.604750785606385</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1766398905363483</v>
+        <v>0.174375276555113</v>
       </c>
       <c r="W79">
-        <v>0.1208692640692641</v>
+        <v>0.1212017094017094</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8831994526817415</v>
+        <v>0.8718763827755651</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8016,22 +8016,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1891765188668549</v>
+        <v>0.1901865188668549</v>
       </c>
       <c r="C80">
-        <v>-2.808260675334317</v>
+        <v>-3.39420294285771</v>
       </c>
       <c r="D80">
-        <v>26.58173932466569</v>
+        <v>26.39579705714229</v>
       </c>
       <c r="E80">
-        <v>2.800000000000004</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="F80">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="G80">
         <v>1.81</v>
@@ -8052,37 +8052,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M80">
-        <v>4.580160000000001</v>
+        <v>4.63888</v>
       </c>
       <c r="N80">
-        <v>-0.5868266666666679</v>
+        <v>-0.6455466666666672</v>
       </c>
       <c r="O80">
-        <v>-0.1173653333333336</v>
+        <v>-0.1291093333333334</v>
       </c>
       <c r="P80">
-        <v>-0.4694613333333343</v>
+        <v>-0.5164373333333337</v>
       </c>
       <c r="Q80">
-        <v>0.6205386666666655</v>
+        <v>0.5735626666666661</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4301781160614616</v>
+        <v>0.4484818358739122</v>
       </c>
       <c r="T80">
-        <v>4.604750785606385</v>
+        <v>4.824024632540024</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.174375276555113</v>
+        <v>0.1721679945734028</v>
       </c>
       <c r="W80">
-        <v>0.1212017094017094</v>
+        <v>0.1215257383966245</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8718763827755651</v>
+        <v>0.8608399728670137</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8098,22 +8098,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1901865188668549</v>
+        <v>0.1911965188668548</v>
       </c>
       <c r="C81">
-        <v>-3.39420294285771</v>
+        <v>-3.97756190657627</v>
       </c>
       <c r="D81">
-        <v>26.39579705714229</v>
+        <v>26.21243809342373</v>
       </c>
       <c r="E81">
-        <v>3.200000000000003</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="F81">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="G81">
         <v>1.81</v>
@@ -8134,37 +8134,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M81">
-        <v>4.63888</v>
+        <v>4.6976</v>
       </c>
       <c r="N81">
-        <v>-0.6455466666666672</v>
+        <v>-0.7042666666666673</v>
       </c>
       <c r="O81">
-        <v>-0.1291093333333334</v>
+        <v>-0.1408533333333335</v>
       </c>
       <c r="P81">
-        <v>-0.5164373333333337</v>
+        <v>-0.5634133333333338</v>
       </c>
       <c r="Q81">
-        <v>0.5735626666666661</v>
+        <v>0.5265866666666661</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4484818358739122</v>
+        <v>0.4686159276676076</v>
       </c>
       <c r="T81">
-        <v>4.824024632540024</v>
+        <v>5.065225864167023</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1721679945734028</v>
+        <v>0.1700158946412352</v>
       </c>
       <c r="W81">
-        <v>0.1215257383966245</v>
+        <v>0.1218416666666667</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8608399728670137</v>
+        <v>0.8500794732061761</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8180,22 +8180,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1911965188668548</v>
+        <v>0.1922065188668549</v>
       </c>
       <c r="C82">
-        <v>-3.97756190657627</v>
+        <v>-4.558391030028314</v>
       </c>
       <c r="D82">
-        <v>26.21243809342373</v>
+        <v>26.03160896997169</v>
       </c>
       <c r="E82">
-        <v>3.600000000000001</v>
+        <v>4.000000000000007</v>
       </c>
       <c r="F82">
-        <v>32</v>
+        <v>32.40000000000001</v>
       </c>
       <c r="G82">
         <v>1.81</v>
@@ -8216,37 +8216,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M82">
-        <v>4.6976</v>
+        <v>4.756320000000001</v>
       </c>
       <c r="N82">
-        <v>-0.7042666666666673</v>
+        <v>-0.7629866666666683</v>
       </c>
       <c r="O82">
-        <v>-0.1408533333333335</v>
+        <v>-0.1525973333333337</v>
       </c>
       <c r="P82">
-        <v>-0.5634133333333338</v>
+        <v>-0.6103893333333346</v>
       </c>
       <c r="Q82">
-        <v>0.5265866666666661</v>
+        <v>0.4796106666666653</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4686159276676076</v>
+        <v>0.4908693975448503</v>
       </c>
       <c r="T82">
-        <v>5.065225864167023</v>
+        <v>5.331816699123183</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1700158946412352</v>
+        <v>0.1679169329789977</v>
       </c>
       <c r="W82">
-        <v>0.1218416666666667</v>
+        <v>0.1221497942386831</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8500794732061761</v>
+        <v>0.8395846648949885</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8262,22 +8262,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1922065188668549</v>
+        <v>0.1932165188668548</v>
       </c>
       <c r="C83">
-        <v>-4.558391030028314</v>
+        <v>-5.136742311565616</v>
       </c>
       <c r="D83">
-        <v>26.03160896997169</v>
+        <v>25.85325768843439</v>
       </c>
       <c r="E83">
-        <v>4.000000000000007</v>
+        <v>4.400000000000006</v>
       </c>
       <c r="F83">
-        <v>32.40000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="G83">
         <v>1.81</v>
@@ -8298,37 +8298,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M83">
-        <v>4.756320000000001</v>
+        <v>4.815040000000001</v>
       </c>
       <c r="N83">
-        <v>-0.7629866666666683</v>
+        <v>-0.8217066666666675</v>
       </c>
       <c r="O83">
-        <v>-0.1525973333333337</v>
+        <v>-0.1643413333333335</v>
       </c>
       <c r="P83">
-        <v>-0.6103893333333346</v>
+        <v>-0.657365333333334</v>
       </c>
       <c r="Q83">
-        <v>0.4796106666666653</v>
+        <v>0.4326346666666658</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4908693975448503</v>
+        <v>0.5155954751862307</v>
       </c>
       <c r="T83">
-        <v>5.331816699123183</v>
+        <v>5.628028737963359</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1679169329789977</v>
+        <v>0.1658691655036441</v>
       </c>
       <c r="W83">
-        <v>0.1221497942386831</v>
+        <v>0.1224504065040651</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8395846648949885</v>
+        <v>0.8293458275182205</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8344,22 +8344,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1932165188668548</v>
+        <v>0.1942265188668549</v>
       </c>
       <c r="C84">
-        <v>-5.136742311565616</v>
+        <v>-5.712666334204339</v>
       </c>
       <c r="D84">
-        <v>25.85325768843439</v>
+        <v>25.67733366579566</v>
       </c>
       <c r="E84">
-        <v>4.400000000000006</v>
+        <v>4.800000000000004</v>
       </c>
       <c r="F84">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="G84">
         <v>1.81</v>
@@ -8380,37 +8380,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M84">
-        <v>4.815040000000001</v>
+        <v>4.873760000000001</v>
       </c>
       <c r="N84">
-        <v>-0.8217066666666675</v>
+        <v>-0.8804266666666676</v>
       </c>
       <c r="O84">
-        <v>-0.1643413333333335</v>
+        <v>-0.1760853333333335</v>
       </c>
       <c r="P84">
-        <v>-0.657365333333334</v>
+        <v>-0.704341333333334</v>
       </c>
       <c r="Q84">
-        <v>0.4326346666666658</v>
+        <v>0.3856586666666658</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5155954751862307</v>
+        <v>0.5432305031383621</v>
       </c>
       <c r="T84">
-        <v>5.628028737963359</v>
+        <v>5.959089251961205</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1658691655036441</v>
+        <v>0.1638707418228773</v>
       </c>
       <c r="W84">
-        <v>0.1224504065040651</v>
+        <v>0.1227437751004016</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8293458275182205</v>
+        <v>0.8193537091143865</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8426,22 +8426,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1942265188668549</v>
+        <v>0.1952365188668549</v>
       </c>
       <c r="C85">
-        <v>-5.712666334204339</v>
+        <v>-6.286212313454293</v>
       </c>
       <c r="D85">
-        <v>25.67733366579566</v>
+        <v>25.50378768654571</v>
       </c>
       <c r="E85">
-        <v>4.800000000000004</v>
+        <v>5.200000000000003</v>
       </c>
       <c r="F85">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="G85">
         <v>1.81</v>
@@ -8462,37 +8462,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M85">
-        <v>4.873760000000001</v>
+        <v>4.932480000000001</v>
       </c>
       <c r="N85">
-        <v>-0.8804266666666676</v>
+        <v>-0.9391466666666677</v>
       </c>
       <c r="O85">
-        <v>-0.1760853333333335</v>
+        <v>-0.1878293333333335</v>
       </c>
       <c r="P85">
-        <v>-0.704341333333334</v>
+        <v>-0.7513173333333342</v>
       </c>
       <c r="Q85">
-        <v>0.3856586666666658</v>
+        <v>0.3386826666666657</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5432305031383621</v>
+        <v>0.5743199095845097</v>
       </c>
       <c r="T85">
-        <v>5.959089251961205</v>
+        <v>6.331532330208782</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1638707418228773</v>
+        <v>0.1619198996583192</v>
       </c>
       <c r="W85">
-        <v>0.1227437751004016</v>
+        <v>0.1230301587301588</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8193537091143865</v>
+        <v>0.8095994982915962</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8508,22 +8508,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1952365188668549</v>
+        <v>0.1962465188668548</v>
       </c>
       <c r="C86">
-        <v>-6.286212313454293</v>
+        <v>-6.857428143221732</v>
       </c>
       <c r="D86">
-        <v>25.50378768654571</v>
+        <v>25.33257185677827</v>
       </c>
       <c r="E86">
-        <v>5.200000000000003</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="F86">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="G86">
         <v>1.81</v>
@@ -8544,37 +8544,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M86">
-        <v>4.932480000000001</v>
+        <v>4.9912</v>
       </c>
       <c r="N86">
-        <v>-0.9391466666666677</v>
+        <v>-0.9978666666666669</v>
       </c>
       <c r="O86">
-        <v>-0.1878293333333335</v>
+        <v>-0.1995733333333334</v>
       </c>
       <c r="P86">
-        <v>-0.7513173333333342</v>
+        <v>-0.7982933333333335</v>
       </c>
       <c r="Q86">
-        <v>0.3386826666666657</v>
+        <v>0.2917066666666663</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5743199095845094</v>
+        <v>0.6095545702234767</v>
       </c>
       <c r="T86">
-        <v>6.331532330208778</v>
+        <v>6.75363448555603</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1619198996583192</v>
+        <v>0.1600149596623391</v>
       </c>
       <c r="W86">
-        <v>0.1230301587301588</v>
+        <v>0.1233098039215686</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8095994982915962</v>
+        <v>0.8000747983116951</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8590,22 +8590,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1962465188668548</v>
+        <v>0.2472765231588423</v>
       </c>
       <c r="C87">
-        <v>-6.857428143221732</v>
+        <v>-13.67366577880623</v>
       </c>
       <c r="D87">
-        <v>25.33257185677827</v>
+        <v>18.91633422119377</v>
       </c>
       <c r="E87">
-        <v>5.600000000000001</v>
+        <v>6</v>
       </c>
       <c r="F87">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="G87">
         <v>1.81</v>
@@ -8626,45 +8626,45 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M87">
-        <v>4.9912</v>
+        <v>6.90752</v>
       </c>
       <c r="N87">
-        <v>-0.9978666666666669</v>
+        <v>-2.914186666666667</v>
       </c>
       <c r="O87">
-        <v>-0.1995733333333334</v>
+        <v>-0.5828373333333333</v>
       </c>
       <c r="P87">
-        <v>-0.7982933333333335</v>
+        <v>-2.331349333333333</v>
       </c>
       <c r="Q87">
-        <v>0.2917066666666663</v>
+        <v>-1.241349333333333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6095545702234767</v>
+        <v>0.67539421303935</v>
       </c>
       <c r="T87">
-        <v>6.75363448555603</v>
+        <v>7.542376441229591</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1600149596623391</v>
+        <v>0.1156227801970413</v>
       </c>
       <c r="W87">
-        <v>0.1233098039215686</v>
+        <v>0.1775829457364341</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8000747983116951</v>
+        <v>0.5781139009852064</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8672,22 +8672,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2472765231588423</v>
+        <v>0.2488265231588423</v>
       </c>
       <c r="C88">
-        <v>-13.67366577880623</v>
+        <v>-14.21808197422081</v>
       </c>
       <c r="D88">
-        <v>18.91633422119377</v>
+        <v>18.77191802577919</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>6.399999999999999</v>
       </c>
       <c r="F88">
-        <v>34.4</v>
+        <v>34.8</v>
       </c>
       <c r="G88">
         <v>1.81</v>
@@ -8708,37 +8708,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M88">
-        <v>6.90752</v>
+        <v>6.987839999999999</v>
       </c>
       <c r="N88">
-        <v>-2.914186666666667</v>
+        <v>-2.994506666666666</v>
       </c>
       <c r="O88">
-        <v>-0.5828373333333333</v>
+        <v>-0.5989013333333333</v>
       </c>
       <c r="P88">
-        <v>-2.331349333333333</v>
+        <v>-2.395605333333333</v>
       </c>
       <c r="Q88">
-        <v>-1.241349333333333</v>
+        <v>-1.305605333333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.67539421303935</v>
+        <v>0.7238245371192999</v>
       </c>
       <c r="T88">
-        <v>7.542376441229591</v>
+        <v>8.122559244401097</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1156227801970413</v>
+        <v>0.1142937827235121</v>
       </c>
       <c r="W88">
-        <v>0.1775829457364341</v>
+        <v>0.1778498084291188</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5781139009852064</v>
+        <v>0.5714689136175604</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8754,22 +8754,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2488265231588423</v>
+        <v>0.2503765231588423</v>
       </c>
       <c r="C89">
-        <v>-14.21808197422081</v>
+        <v>-14.76030979435718</v>
       </c>
       <c r="D89">
-        <v>18.77191802577919</v>
+        <v>18.62969020564283</v>
       </c>
       <c r="E89">
-        <v>6.399999999999999</v>
+        <v>6.800000000000004</v>
       </c>
       <c r="F89">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="G89">
         <v>1.81</v>
@@ -8790,37 +8790,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M89">
-        <v>6.987839999999999</v>
+        <v>7.068160000000001</v>
       </c>
       <c r="N89">
-        <v>-2.994506666666666</v>
+        <v>-3.074826666666667</v>
       </c>
       <c r="O89">
-        <v>-0.5989013333333333</v>
+        <v>-0.6149653333333336</v>
       </c>
       <c r="P89">
-        <v>-2.395605333333333</v>
+        <v>-2.459861333333334</v>
       </c>
       <c r="Q89">
-        <v>-1.305605333333333</v>
+        <v>-1.369861333333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7238245371192999</v>
+        <v>0.7803265818792418</v>
       </c>
       <c r="T89">
-        <v>8.122559244401097</v>
+        <v>8.799439181434524</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1142937827235121</v>
+        <v>0.1129949897380176</v>
       </c>
       <c r="W89">
-        <v>0.1778498084291188</v>
+        <v>0.1781106060606061</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5714689136175604</v>
+        <v>0.5649749486900881</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8836,22 +8836,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2503765231588423</v>
+        <v>0.2519265231588423</v>
       </c>
       <c r="C90">
-        <v>-14.76030979435718</v>
+        <v>-15.30039860668577</v>
       </c>
       <c r="D90">
-        <v>18.62969020564283</v>
+        <v>18.48960139331423</v>
       </c>
       <c r="E90">
-        <v>6.800000000000004</v>
+        <v>7.200000000000003</v>
       </c>
       <c r="F90">
-        <v>35.2</v>
+        <v>35.6</v>
       </c>
       <c r="G90">
         <v>1.81</v>
@@ -8872,37 +8872,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M90">
-        <v>7.068160000000001</v>
+        <v>7.14848</v>
       </c>
       <c r="N90">
-        <v>-3.074826666666667</v>
+        <v>-3.155146666666667</v>
       </c>
       <c r="O90">
-        <v>-0.6149653333333336</v>
+        <v>-0.6310293333333334</v>
       </c>
       <c r="P90">
-        <v>-2.459861333333334</v>
+        <v>-2.524117333333334</v>
       </c>
       <c r="Q90">
-        <v>-1.369861333333334</v>
+        <v>-1.434117333333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7803265818792418</v>
+        <v>0.8471017256864456</v>
       </c>
       <c r="T90">
-        <v>8.799439181434524</v>
+        <v>9.599388197928572</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1129949897380176</v>
+        <v>0.1117253831117478</v>
       </c>
       <c r="W90">
-        <v>0.1781106060606061</v>
+        <v>0.1783655430711611</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5649749486900881</v>
+        <v>0.5586269155587388</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8918,22 +8918,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2519265231588423</v>
+        <v>0.2534765231588423</v>
       </c>
       <c r="C91">
-        <v>-15.30039860668577</v>
+        <v>-15.83839630485466</v>
       </c>
       <c r="D91">
-        <v>18.48960139331423</v>
+        <v>18.35160369514534</v>
       </c>
       <c r="E91">
-        <v>7.200000000000003</v>
+        <v>7.600000000000001</v>
       </c>
       <c r="F91">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="G91">
         <v>1.81</v>
@@ -8954,37 +8954,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M91">
-        <v>7.14848</v>
+        <v>7.228800000000001</v>
       </c>
       <c r="N91">
-        <v>-3.155146666666667</v>
+        <v>-3.235466666666667</v>
       </c>
       <c r="O91">
-        <v>-0.6310293333333334</v>
+        <v>-0.6470933333333335</v>
       </c>
       <c r="P91">
-        <v>-2.524117333333334</v>
+        <v>-2.588373333333334</v>
       </c>
       <c r="Q91">
-        <v>-1.434117333333334</v>
+        <v>-1.498373333333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8471017256864456</v>
+        <v>0.9272318982550901</v>
       </c>
       <c r="T91">
-        <v>9.599388197928572</v>
+        <v>10.55932701772143</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1117253831117478</v>
+        <v>0.1104839899660617</v>
       </c>
       <c r="W91">
-        <v>0.1783655430711611</v>
+        <v>0.1786148148148148</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5586269155587388</v>
+        <v>0.5524199498303084</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9000,22 +9000,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2534765231588423</v>
+        <v>0.2550265231588423</v>
       </c>
       <c r="C92">
-        <v>-15.83839630485466</v>
+        <v>-16.37434936328157</v>
       </c>
       <c r="D92">
-        <v>18.35160369514534</v>
+        <v>18.21565063671843</v>
       </c>
       <c r="E92">
-        <v>7.600000000000001</v>
+        <v>8</v>
       </c>
       <c r="F92">
-        <v>36</v>
+        <v>36.4</v>
       </c>
       <c r="G92">
         <v>1.81</v>
@@ -9036,37 +9036,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M92">
-        <v>7.228800000000001</v>
+        <v>7.30912</v>
       </c>
       <c r="N92">
-        <v>-3.235466666666667</v>
+        <v>-3.315786666666667</v>
       </c>
       <c r="O92">
-        <v>-0.6470933333333335</v>
+        <v>-0.6631573333333334</v>
       </c>
       <c r="P92">
-        <v>-2.588373333333334</v>
+        <v>-2.652629333333334</v>
       </c>
       <c r="Q92">
-        <v>-1.498373333333334</v>
+        <v>-1.562629333333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9272318982550901</v>
+        <v>1.025168775838989</v>
       </c>
       <c r="T92">
-        <v>10.55932701772143</v>
+        <v>11.73258557524603</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1104839899660617</v>
+        <v>0.1092698801862148</v>
       </c>
       <c r="W92">
-        <v>0.1786148148148148</v>
+        <v>0.1788586080586081</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5524199498303084</v>
+        <v>0.5463494009310742</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9082,22 +9082,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2550265231588423</v>
+        <v>0.2565765231588424</v>
       </c>
       <c r="C93">
-        <v>-16.37434936328157</v>
+        <v>-16.90830288933741</v>
       </c>
       <c r="D93">
-        <v>18.21565063671843</v>
+        <v>18.0816971106626</v>
       </c>
       <c r="E93">
-        <v>8</v>
+        <v>8.400000000000006</v>
       </c>
       <c r="F93">
-        <v>36.4</v>
+        <v>36.8</v>
       </c>
       <c r="G93">
         <v>1.81</v>
@@ -9118,37 +9118,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M93">
-        <v>7.30912</v>
+        <v>7.389440000000001</v>
       </c>
       <c r="N93">
-        <v>-3.315786666666667</v>
+        <v>-3.396106666666668</v>
       </c>
       <c r="O93">
-        <v>-0.6631573333333334</v>
+        <v>-0.6792213333333337</v>
       </c>
       <c r="P93">
-        <v>-2.652629333333334</v>
+        <v>-2.716885333333335</v>
       </c>
       <c r="Q93">
-        <v>-1.562629333333334</v>
+        <v>-1.626885333333335</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.025168775838989</v>
+        <v>1.147589872818863</v>
       </c>
       <c r="T93">
-        <v>11.73258557524603</v>
+        <v>13.19915877215179</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1092698801862148</v>
+        <v>0.1080821640972342</v>
       </c>
       <c r="W93">
-        <v>0.1788586080586081</v>
+        <v>0.1790971014492754</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5463494009310742</v>
+        <v>0.5404108204861711</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9164,22 +9164,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2565765231588424</v>
+        <v>0.2581265231588424</v>
       </c>
       <c r="C94">
-        <v>-16.90830288933741</v>
+        <v>-17.44030067324385</v>
       </c>
       <c r="D94">
-        <v>18.0816971106626</v>
+        <v>17.94969932675615</v>
       </c>
       <c r="E94">
-        <v>8.400000000000006</v>
+        <v>8.800000000000004</v>
       </c>
       <c r="F94">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="G94">
         <v>1.81</v>
@@ -9200,37 +9200,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M94">
-        <v>7.389440000000001</v>
+        <v>7.469760000000001</v>
       </c>
       <c r="N94">
-        <v>-3.396106666666668</v>
+        <v>-3.476426666666668</v>
       </c>
       <c r="O94">
-        <v>-0.6792213333333337</v>
+        <v>-0.6952853333333335</v>
       </c>
       <c r="P94">
-        <v>-2.716885333333335</v>
+        <v>-2.781141333333334</v>
       </c>
       <c r="Q94">
-        <v>-1.626885333333335</v>
+        <v>-1.691141333333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.147589872818863</v>
+        <v>1.304988426078701</v>
       </c>
       <c r="T94">
-        <v>13.19915877215179</v>
+        <v>15.08475288245919</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1080821640972342</v>
+        <v>0.1069199902897371</v>
       </c>
       <c r="W94">
-        <v>0.1790971014492754</v>
+        <v>0.1793304659498208</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5404108204861711</v>
+        <v>0.5345999514486854</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9246,22 +9246,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2581265231588424</v>
+        <v>0.2596765231588424</v>
       </c>
       <c r="C95">
-        <v>-17.44030067324385</v>
+        <v>-17.97038523580151</v>
       </c>
       <c r="D95">
-        <v>17.94969932675615</v>
+        <v>17.81961476419849</v>
       </c>
       <c r="E95">
-        <v>8.800000000000004</v>
+        <v>9.200000000000003</v>
       </c>
       <c r="F95">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="G95">
         <v>1.81</v>
@@ -9282,37 +9282,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M95">
-        <v>7.469760000000001</v>
+        <v>7.55008</v>
       </c>
       <c r="N95">
-        <v>-3.476426666666668</v>
+        <v>-3.556746666666667</v>
       </c>
       <c r="O95">
-        <v>-0.6952853333333335</v>
+        <v>-0.7113493333333335</v>
       </c>
       <c r="P95">
-        <v>-2.781141333333334</v>
+        <v>-2.845397333333334</v>
       </c>
       <c r="Q95">
-        <v>-1.691141333333334</v>
+        <v>-1.755397333333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.304988426078701</v>
+        <v>1.514853163758485</v>
       </c>
       <c r="T95">
-        <v>15.08475288245919</v>
+        <v>17.59887836286906</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1069199902897371</v>
+        <v>0.1057825435845271</v>
       </c>
       <c r="W95">
-        <v>0.1793304659498208</v>
+        <v>0.179558865248227</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5345999514486854</v>
+        <v>0.5289127179226356</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9328,22 +9328,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2596765231588424</v>
+        <v>0.2612265231588424</v>
       </c>
       <c r="C96">
-        <v>-17.97038523580151</v>
+        <v>-18.49859787405749</v>
       </c>
       <c r="D96">
-        <v>17.81961476419849</v>
+        <v>17.69140212594251</v>
       </c>
       <c r="E96">
-        <v>9.200000000000003</v>
+        <v>9.600000000000001</v>
       </c>
       <c r="F96">
-        <v>37.6</v>
+        <v>38</v>
       </c>
       <c r="G96">
         <v>1.81</v>
@@ -9364,37 +9364,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M96">
-        <v>7.55008</v>
+        <v>7.6304</v>
       </c>
       <c r="N96">
-        <v>-3.556746666666667</v>
+        <v>-3.637066666666667</v>
       </c>
       <c r="O96">
-        <v>-0.7113493333333335</v>
+        <v>-0.7274133333333334</v>
       </c>
       <c r="P96">
-        <v>-2.845397333333334</v>
+        <v>-2.909653333333333</v>
       </c>
       <c r="Q96">
-        <v>-1.755397333333334</v>
+        <v>-1.819653333333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.514853163758485</v>
+        <v>1.808663796510183</v>
       </c>
       <c r="T96">
-        <v>17.59887836286906</v>
+        <v>21.11865403544288</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1057825435845271</v>
+        <v>0.1046690431257426</v>
       </c>
       <c r="W96">
-        <v>0.179558865248227</v>
+        <v>0.1797824561403509</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5289127179226356</v>
+        <v>0.5233452156287133</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9410,22 +9410,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2612265231588424</v>
+        <v>0.2627765231588424</v>
       </c>
       <c r="C97">
-        <v>-18.49859787405749</v>
+        <v>-19.02497870501558</v>
       </c>
       <c r="D97">
-        <v>17.69140212594251</v>
+        <v>17.56502129498443</v>
       </c>
       <c r="E97">
-        <v>9.600000000000001</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="F97">
-        <v>38</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="G97">
         <v>1.81</v>
@@ -9446,37 +9446,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M97">
-        <v>7.6304</v>
+        <v>7.710720000000001</v>
       </c>
       <c r="N97">
-        <v>-3.637066666666667</v>
+        <v>-3.717386666666668</v>
       </c>
       <c r="O97">
-        <v>-0.7274133333333334</v>
+        <v>-0.7434773333333337</v>
       </c>
       <c r="P97">
-        <v>-2.909653333333333</v>
+        <v>-2.973909333333334</v>
       </c>
       <c r="Q97">
-        <v>-1.819653333333334</v>
+        <v>-1.883909333333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.808663796510183</v>
+        <v>2.249379745637729</v>
       </c>
       <c r="T97">
-        <v>21.11865403544288</v>
+        <v>26.39831754430362</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1046690431257426</v>
+        <v>0.1035787405931828</v>
       </c>
       <c r="W97">
-        <v>0.1797824561403509</v>
+        <v>0.1800013888888889</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5233452156287133</v>
+        <v>0.5178937029659141</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9492,22 +9492,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2627765231588423</v>
+        <v>0.2643265231588424</v>
       </c>
       <c r="C98">
-        <v>-19.02497870501557</v>
+        <v>-19.54956670748626</v>
       </c>
       <c r="D98">
-        <v>17.56502129498443</v>
+        <v>17.44043329251374</v>
       </c>
       <c r="E98">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="F98">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="G98">
         <v>1.81</v>
@@ -9528,37 +9528,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M98">
-        <v>7.71072</v>
+        <v>7.79104</v>
       </c>
       <c r="N98">
-        <v>-3.717386666666667</v>
+        <v>-3.797706666666667</v>
       </c>
       <c r="O98">
-        <v>-0.7434773333333334</v>
+        <v>-0.7595413333333334</v>
       </c>
       <c r="P98">
-        <v>-2.973909333333334</v>
+        <v>-3.038165333333333</v>
       </c>
       <c r="Q98">
-        <v>-1.883909333333334</v>
+        <v>-1.948165333333333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.249379745637723</v>
+        <v>2.983906327516965</v>
       </c>
       <c r="T98">
-        <v>26.39831754430354</v>
+        <v>35.19775672573807</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1035787405931828</v>
+        <v>0.1025109185252119</v>
       </c>
       <c r="W98">
-        <v>0.1800013888888889</v>
+        <v>0.1802158075601375</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5178937029659141</v>
+        <v>0.5125545926260593</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9574,22 +9574,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2643265231588424</v>
+        <v>0.2658765231588424</v>
       </c>
       <c r="C99">
-        <v>-19.54956670748626</v>
+        <v>-20.07239976216827</v>
       </c>
       <c r="D99">
-        <v>17.44043329251374</v>
+        <v>17.31760023783173</v>
       </c>
       <c r="E99">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="F99">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="G99">
         <v>1.81</v>
@@ -9610,37 +9610,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M99">
-        <v>7.79104</v>
+        <v>7.871360000000001</v>
       </c>
       <c r="N99">
-        <v>-3.797706666666667</v>
+        <v>-3.878026666666668</v>
       </c>
       <c r="O99">
-        <v>-0.7595413333333334</v>
+        <v>-0.7756053333333336</v>
       </c>
       <c r="P99">
-        <v>-3.038165333333333</v>
+        <v>-3.102421333333334</v>
       </c>
       <c r="Q99">
-        <v>-1.948165333333333</v>
+        <v>-2.012421333333335</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.983906327516965</v>
+        <v>4.452959491275447</v>
       </c>
       <c r="T99">
-        <v>35.19775672573807</v>
+        <v>52.7966350886071</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1025109185252119</v>
+        <v>0.1014648887443423</v>
       </c>
       <c r="W99">
-        <v>0.1802158075601375</v>
+        <v>0.1804258503401361</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5125545926260593</v>
+        <v>0.5073244437217117</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9656,22 +9656,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2658765231588424</v>
+        <v>0.2674265231588424</v>
       </c>
       <c r="C100">
-        <v>-20.07239976216827</v>
+        <v>-20.5935146900481</v>
       </c>
       <c r="D100">
-        <v>17.31760023783173</v>
+        <v>17.19648530995191</v>
       </c>
       <c r="E100">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="F100">
-        <v>39.2</v>
+        <v>39.6</v>
       </c>
       <c r="G100">
         <v>1.81</v>
@@ -9692,37 +9692,37 @@
         <v>3.993333333333333</v>
       </c>
       <c r="M100">
-        <v>7.871360000000001</v>
+        <v>7.951680000000001</v>
       </c>
       <c r="N100">
-        <v>-3.878026666666668</v>
+        <v>-3.958346666666667</v>
       </c>
       <c r="O100">
-        <v>-0.7756053333333336</v>
+        <v>-0.7916693333333336</v>
       </c>
       <c r="P100">
-        <v>-3.102421333333334</v>
+        <v>-3.166677333333334</v>
       </c>
       <c r="Q100">
-        <v>-2.012421333333335</v>
+        <v>-2.076677333333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.452959491275447</v>
+        <v>8.860118982550894</v>
       </c>
       <c r="T100">
-        <v>52.7966350886071</v>
+        <v>105.5932701772142</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1014648887443423</v>
+        <v>0.1004399908782379</v>
       </c>
       <c r="W100">
-        <v>0.1804258503401361</v>
+        <v>0.1806316498316498</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9730,91 +9730,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5073244437217117</v>
+        <v>0.5021999543911895</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2674265231588424</v>
-      </c>
-      <c r="C101">
-        <v>-20.5935146900481</v>
-      </c>
-      <c r="D101">
-        <v>17.19648530995191</v>
-      </c>
-      <c r="E101">
-        <v>11.2</v>
-      </c>
-      <c r="F101">
-        <v>39.6</v>
-      </c>
-      <c r="G101">
-        <v>1.81</v>
-      </c>
-      <c r="H101">
-        <v>11.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.083333333333333</v>
-      </c>
-      <c r="K101">
-        <v>1.09</v>
-      </c>
-      <c r="L101">
-        <v>3.993333333333333</v>
-      </c>
-      <c r="M101">
-        <v>7.951680000000001</v>
-      </c>
-      <c r="N101">
-        <v>-3.958346666666667</v>
-      </c>
-      <c r="O101">
-        <v>-0.7916693333333336</v>
-      </c>
-      <c r="P101">
-        <v>-3.166677333333334</v>
-      </c>
-      <c r="Q101">
-        <v>-2.076677333333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.860118982550894</v>
-      </c>
-      <c r="T101">
-        <v>105.5932701772142</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1004399908782379</v>
-      </c>
-      <c r="W101">
-        <v>0.1806316498316498</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5021999543911895</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
